--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2680,27 +2680,27 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -4654,57 +4654,57 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -5666,47 +5666,47 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="DQ6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR6" t="inlineStr">
@@ -6663,109 +6663,109 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>-19392272.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>24180018.0</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>16192434.0</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>7987584.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>4436356.0</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>-6968332.0</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>-19392272.0</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>24180018.0</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>16192434.0</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>7987584.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>4436356.0</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>-6968332.0</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="BN7" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="DQ7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR7" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7695,22 +7695,22 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8697,22 +8697,22 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9699,22 +9699,22 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -10666,34 +10666,34 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AX11" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -10701,74 +10701,74 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>-4270931.0</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>4884000.0</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>102000.0</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>4782000.0</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>554085.0</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>1065154.0</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>-4270931.0</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>4884000.0</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>102000.0</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>4782000.0</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>554085.0</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>1065154.0</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
           <t>-2.0</t>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="DQ11" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7480.0</t>
+          <t>10797.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.021532789916250558</t>
+          <t>0.049948331082743706</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1538,47 +1538,47 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.025</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>150.0910685774231</t>
+          <t>150.1859083016421</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>141.9089314225769</t>
+          <t>141.8640916983579</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.05604203530716577</t>
+          <t>0.0569889854701885</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.0001712035610340612</t>
+          <t>0.0001712328767122795</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0002926170624176772</t>
+          <t>0.0006318811979635353</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.004435896489509261</t>
+          <t>0.01689714083000182</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.2103159233370619</t>
+          <t>0.2450168146790725</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.4159349627351613</t>
+          <t>0.4410213718718747</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1623,24 +1623,24 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AQ2" t="inlineStr">
         <is>
           <t>False</t>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>弱勢</t>
+          <t>盤整</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1718,32 +1718,32 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-4247384.0</t>
+          <t>-4053731.0</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>53547.0</t>
+          <t>49547.0</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>66587.0</t>
+          <t>58587.0</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-13040.0</t>
+          <t>-9040.0</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>64380.0</t>
+          <t>285782.0</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-4196044.0</t>
+          <t>-3776989.0</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>2025/10/02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>232.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>147</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1868,102 +1868,102 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>54.17</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>144.1</t>
+          <t>145.4</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>144.65</t>
+          <t>144.9</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.02</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>161.07</t>
+          <t>160.23</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>174.61</t>
+          <t>174.08</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>180.0791666666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>0.000694444444444331</t>
+          <t>0.009021512838306878</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>0.0006918021445865286</t>
+          <t>0.001728309713100673</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>-0.0001712035610340612</t>
+          <t>0.0001712328767122795</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>-0.005617977528089901</t>
+          <t>-0.00521512385919165</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>-0.003921988091417972</t>
+          <t>-0.003006765221748808</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>-0.002101131378434484</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>-128.51</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
@@ -1983,52 +1983,52 @@
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>2108024.944285714</t>
+          <t>2148748.814634146</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>1087549.0</t>
+          <t>1607944.0</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>902836.0</t>
+          <t>981794.4</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>922704.4</t>
+          <t>935088.3</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>865730.5333333333</t>
+          <t>892496.4666666667</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>1290966.04</t>
+          <t>1298064.78</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>1430081.9</t>
+          <t>1433039.425</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>-43209.26849213363</t>
+          <t>-28739.10783996583</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>-4350.599331998033</t>
+          <t>50846.77571685612</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>1087549.0</t>
+          <t>1607944.0</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-30.70</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>13.96</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>165699</t>
+          <t>169208</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
@@ -2158,22 +2158,22 @@
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
@@ -2198,42 +2198,42 @@
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】;【v】測試條件</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2557.802</t>
+          <t>2051.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2450.0</t>
+          <t>2415.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.016810838087647297</t>
+          <t>0.0814551394073437</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2525,79 +2525,79 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 10&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : True</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2312.75</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2658.224121203102</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1967.275878796898</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.2987561311885003</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.004669852302345845</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.004066685333286468</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.004600958172049086</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.2976373544326177</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.897704966136814</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 10&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : True</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2302.0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2647.457743626582</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1956.542256373418</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.3001370491977252</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.007770603042574153</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.005055312304909299</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.02028432390170209</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.2806687890794388</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.8854855990987329</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2026-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2625,24 +2625,24 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
       <c r="AQ3" t="inlineStr">
         <is>
           <t>False</t>
@@ -2660,104 +2660,104 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2172248.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>180000.0</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>3208000.0</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>-3028000.0</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>-11841.0</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>-867593.0</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>1766868.0</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>180000.0</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>2671000.0</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>-2491000.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>-7723.0</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>-731855.0</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BN3" t="inlineStr">
         <is>
           <t>-5.0</t>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>2026/01/14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>28.19</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -2855,117 +2855,117 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>44</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>2424.0</t>
+          <t>2404.0</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>2446.0</t>
+          <t>2458.0</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>2302.0</t>
+          <t>2312.75</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>1988.8</t>
+          <t>2008.9</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>1839.44</t>
+          <t>1847.69</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>1699.8125</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>-0.006557377049180357</t>
+          <t>-0.008250825082508295</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>0.01493775933609953</t>
+          <t>0.004905968928863524</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>0.007770603042574153</t>
+          <t>0.004669852302345845</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>0.01010716643811249</t>
+          <t>0.01010659694288019</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>0.003409362108349523</t>
+          <t>0.004485066766334755</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>0.003270826928988724</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>123.58</t>
+          <t>117.42</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
         <is>
-          <t>132.17</t>
+          <t>129.22</t>
         </is>
       </c>
       <c r="DD3" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>-10.09</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
@@ -2985,52 +2985,52 @@
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>4769096465.275714</t>
+          <t>5185413264.797561</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>6211785520.0</t>
+          <t>4966067050.0</t>
         </is>
       </c>
       <c r="DI3" t="inlineStr">
         <is>
-          <t>4866377544.8</t>
+          <t>5341808810.8</t>
         </is>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>4785922181.9</t>
+          <t>4939464075.9</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>3862942867.133333</t>
+          <t>3975691297.466667</t>
         </is>
       </c>
       <c r="DL3" t="inlineStr">
         <is>
-          <t>3610228603.88</t>
+          <t>3686789262.08</t>
         </is>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>2993282865.425</t>
+          <t>2998537601.1125</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>160959955.7202516</t>
+          <t>188830482.1340678</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>369433002.4145136</t>
+          <t>342118377.4014196</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>6211785520.0</t>
+          <t>4966067050.0</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
@@ -3095,22 +3095,22 @@
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>52.41</t>
+          <t>51.66</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>52.83</t>
+          <t>52.68</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>167955</t>
+          <t>165555</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
@@ -3160,27 +3160,27 @@
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>2350.0</t>
+          <t>2445.0</t>
         </is>
       </c>
       <c r="EQ3" t="inlineStr">
         <is>
-          <t>2510.0</t>
+          <t>2505.0</t>
         </is>
       </c>
       <c r="ER3" t="inlineStr">
         <is>
-          <t>2340.0</t>
+          <t>2380.0</t>
         </is>
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>2450.0</t>
+          <t>2415.0</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>445.0</t>
+          <t>1230.0</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
@@ -3200,67 +3200,67 @@
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FD3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="FF3" t="inlineStr">
         <is>
-          <t>1.259759129808542</t>
+          <t>1.343617602856598</t>
         </is>
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK3" t="inlineStr">
@@ -3447,12 +3447,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8838.953</t>
+          <t>18965.053</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>249.5</t>
+          <t>256.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.029324085836342183</t>
+          <t>0.3888267686087649</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -3537,52 +3537,52 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 20&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : True</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>232.3</t>
+          <t>232.925</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>247.9049924534975</t>
+          <t>251.1928175460225</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>216.6950075465026</t>
+          <t>214.6571824539776</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.1343520658932196</t>
+          <t>0.156855790885671</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.003455723542116651</t>
+          <t>0.002690486439948403</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.01238112856406515</t>
+          <t>0.0132624400177892</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.1628681125885392</t>
+          <t>0.1674981686573904</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.2304091351281695</t>
+          <t>0.3087268592049376</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.9987197981205235</t>
+          <t>1.149439309425715</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -3592,677 +3592,677 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2026-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2026-10-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>2026-10-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>2026-10-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>1392398.0</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>35000.0</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>504234.0</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>-469234.0</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>1276989.0</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>2200153.0</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>2026/07/03</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>258.0</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>233.5</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>237.0</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>2026-10-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>28.20</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>-4.88</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>LV.1-9｜網通｜網通設備｜</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>18965</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>-1.84</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>-2.86</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>243.0</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>238.3</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>232.92</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>237.3</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>244.28</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>0.01972303818715893</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>0.0121044807814823</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>0.002690486439948403</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>0.0005481300333094463</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>-0.0007158928206176807</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>282.42</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>-1.09</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>20.71</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>-105.26</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>2026/09/22</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>5842139799.753658</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>4953184984.0</t>
+        </is>
+      </c>
+      <c r="DI4" t="inlineStr">
+        <is>
+          <t>1764966472.6</t>
+        </is>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>1270832700.3</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>1002008415.733333</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
+        <is>
+          <t>1262085566.0</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>1933964781.9625</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>25488289.26955466</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>361206466.308176</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>4953184984.0</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>5.108921494159271</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>15.64526085950118</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>6.101014334309918</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>81.57</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>28.04</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>13.00%</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>5.25%</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>84.97</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>123761</t>
+        </is>
+      </c>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t>無線通訊產品96.85%、其他3.15% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN4" t="inlineStr">
+        <is>
+          <t>啟碁-通信網路業-上市</t>
+        </is>
+      </c>
+      <c r="EO4" t="inlineStr">
+        <is>
+          <t>通信網路業右上上市</t>
+        </is>
+      </c>
+      <c r="EP4" t="inlineStr">
+        <is>
+          <t>256.0</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
+          <t>270.0</t>
+        </is>
+      </c>
+      <c r="ER4" t="inlineStr">
+        <is>
+          <t>254.5</t>
+        </is>
+      </c>
+      <c r="ES4" t="inlineStr">
+        <is>
+          <t>256.0</t>
+        </is>
+      </c>
+      <c r="ET4" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="EU4" t="inlineStr">
+        <is>
+          <t>74.05</t>
+        </is>
+      </c>
+      <c r="EV4" t="inlineStr">
+        <is>
+          <t>** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 天線/射頻基頻</t>
+        </is>
+      </c>
+      <c r="EW4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>-382504.0</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>29000.0</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>500234.0</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>-471234.0</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>647785.0</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>-205953.0</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2026/07/03</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>258.0</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>2026/09/09</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>233.5</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>2026/08/20</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>237.0</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>2026-05-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>13.14</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>3.56</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>LV.1-9｜網通｜網通設備｜</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="CH4" t="inlineStr">
-        <is>
-          <t>8839</t>
-        </is>
-      </c>
-      <c r="CI4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CJ4" t="inlineStr">
-        <is>
-          <t>92.75</t>
-        </is>
-      </c>
-      <c r="CK4" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="CL4" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="CM4" t="inlineStr">
-        <is>
-          <t>-2.05</t>
-        </is>
-      </c>
-      <c r="CN4" t="inlineStr">
-        <is>
-          <t>-2.98</t>
-        </is>
-      </c>
-      <c r="CO4" t="inlineStr">
-        <is>
-          <t>238.3</t>
-        </is>
-      </c>
-      <c r="CP4" t="inlineStr">
-        <is>
-          <t>235.45</t>
-        </is>
-      </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>232.3</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>237.17</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>244.45</t>
-        </is>
-      </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>194.03375</t>
-        </is>
-      </c>
-      <c r="CU4" t="inlineStr">
-        <is>
-          <t>0.009745762711864447</t>
-        </is>
-      </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>0.00986489384516398</t>
-        </is>
-      </c>
-      <c r="CW4" t="inlineStr">
-        <is>
-          <t>0.003455723542116651</t>
-        </is>
-      </c>
-      <c r="CX4" t="inlineStr">
-        <is>
-          <t>-0.0007583737097114351</t>
-        </is>
-      </c>
-      <c r="CY4" t="inlineStr">
-        <is>
-          <t>-0.00188842954116264</t>
-        </is>
-      </c>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>0.002831818005625042</t>
-        </is>
-      </c>
-      <c r="DA4" t="inlineStr">
-        <is>
-          <t>122.84</t>
-        </is>
-      </c>
-      <c r="DB4" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="DC4" t="inlineStr">
-        <is>
-          <t>-1.86</t>
-        </is>
-      </c>
-      <c r="DD4" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="DE4" t="inlineStr">
-        <is>
-          <t>-108.98</t>
-        </is>
-      </c>
-      <c r="DF4" t="inlineStr">
-        <is>
-          <t>2026/09/22</t>
-        </is>
-      </c>
-      <c r="DG4" t="inlineStr">
-        <is>
-          <t>3631487406.651428</t>
-        </is>
-      </c>
-      <c r="DH4" t="inlineStr">
-        <is>
-          <t>2185318242.0</t>
-        </is>
-      </c>
-      <c r="DI4" t="inlineStr">
-        <is>
-          <t>903502564.0</t>
-        </is>
-      </c>
-      <c r="DJ4" t="inlineStr">
-        <is>
-          <t>877762967.4</t>
-        </is>
-      </c>
-      <c r="DK4" t="inlineStr">
-        <is>
-          <t>854433799.7333333</t>
-        </is>
-      </c>
-      <c r="DL4" t="inlineStr">
-        <is>
-          <t>1188889100.44</t>
-        </is>
-      </c>
-      <c r="DM4" t="inlineStr">
-        <is>
-          <t>1930388518.875</t>
-        </is>
-      </c>
-      <c r="DN4" t="inlineStr">
-        <is>
-          <t>-35551379.28471512</t>
-        </is>
-      </c>
-      <c r="DO4" t="inlineStr">
-        <is>
-          <t>72787027.35852993</t>
-        </is>
-      </c>
-      <c r="DP4" t="inlineStr">
-        <is>
-          <t>2185318242.0</t>
-        </is>
-      </c>
-      <c r="DQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR4" t="inlineStr">
-        <is>
-          <t>108.5</t>
-        </is>
-      </c>
-      <c r="DS4" t="inlineStr">
-        <is>
-          <t>2026/01/15</t>
-        </is>
-      </c>
-      <c r="DT4" t="inlineStr">
-        <is>
-          <t>129.95</t>
-        </is>
-      </c>
-      <c r="DU4" t="inlineStr">
-        <is>
-          <t>啟碁</t>
-        </is>
-      </c>
-      <c r="DV4" t="inlineStr">
-        <is>
-          <t>啟碁</t>
-        </is>
-      </c>
-      <c r="DW4" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="DX4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY4" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="DZ4" t="inlineStr">
-        <is>
-          <t>5.108921494159271</t>
-        </is>
-      </c>
-      <c r="EA4" t="inlineStr">
-        <is>
-          <t>15.64526085950118</t>
-        </is>
-      </c>
-      <c r="EB4" t="inlineStr">
-        <is>
-          <t>6.101014334309918</t>
-        </is>
-      </c>
-      <c r="EC4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="ED4" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="EE4" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="EF4" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EG4" t="inlineStr">
-        <is>
-          <t>81.57</t>
-        </is>
-      </c>
-      <c r="EH4" t="inlineStr">
-        <is>
-          <t>27.33</t>
-        </is>
-      </c>
-      <c r="EI4" t="inlineStr">
-        <is>
-          <t>13.00%</t>
-        </is>
-      </c>
-      <c r="EJ4" t="inlineStr">
-        <is>
-          <t>5.25%</t>
-        </is>
-      </c>
-      <c r="EK4" t="inlineStr">
-        <is>
-          <t>85.28</t>
-        </is>
-      </c>
-      <c r="EL4" t="inlineStr">
-        <is>
-          <t>120619</t>
-        </is>
-      </c>
-      <c r="EM4" t="inlineStr">
-        <is>
-          <t>無線通訊產品96.85%、其他3.15% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN4" t="inlineStr">
-        <is>
-          <t>啟碁-通信網路業-上市</t>
-        </is>
-      </c>
-      <c r="EO4" t="inlineStr">
-        <is>
-          <t>通信網路業右上上市</t>
-        </is>
-      </c>
-      <c r="EP4" t="inlineStr">
-        <is>
-          <t>242.0</t>
-        </is>
-      </c>
-      <c r="EQ4" t="inlineStr">
-        <is>
-          <t>250.5</t>
-        </is>
-      </c>
-      <c r="ER4" t="inlineStr">
-        <is>
-          <t>240.0</t>
-        </is>
-      </c>
-      <c r="ES4" t="inlineStr">
-        <is>
-          <t>249.5</t>
-        </is>
-      </c>
-      <c r="ET4" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
-      </c>
-      <c r="EU4" t="inlineStr">
-        <is>
-          <t>74.05</t>
-        </is>
-      </c>
-      <c r="EV4" t="inlineStr">
-        <is>
-          <t>** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 天線/射頻基頻</t>
-        </is>
-      </c>
-      <c r="EW4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="FA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FD4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="FF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.761428791302402</t>
         </is>
       </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FK4" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18711.413</t>
+          <t>23643.333</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>294.0</t>
+          <t>298.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.4423712687111939</t>
+          <t>-0.4199434884366448</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -4529,62 +4529,62 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>盤整偏多</t>
+          <t>轉強</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>TrendType : 盤整偏多&lt;br&gt;TrendScore : 40&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+          <t>TrendType : 轉強&lt;br&gt;TrendScore : 60&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>282.625</t>
+          <t>284.425</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>320.684337328635</t>
+          <t>321.7757908744567</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>244.565662671365</t>
+          <t>247.0742091255434</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.2693274645104645</t>
+          <t>0.2626407022902814</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.005872408577275445</t>
+          <t>0.006368863334807573</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.002729757412546885</t>
+          <t>0.003403513732272101</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0257281728244183</t>
+          <t>-0.02482762844974196</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.2392546400627794</t>
+          <t>0.2657328476024291</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1.11002271200257</t>
+          <t>1.071197084321407</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -4629,24 +4629,24 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AQ5" t="inlineStr">
         <is>
           <t>False</t>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -4694,17 +4694,17 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4724,32 +4724,32 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-22816713.0</t>
+          <t>-12882678.0</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>354000.0</t>
+          <t>248000.0</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>3163419.0</t>
+          <t>3393419.0</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-2809419.0</t>
+          <t>-3145419.0</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-1990202.0</t>
+          <t>-1336237.0</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-27616334.0</t>
+          <t>-17364334.0</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -4834,17 +4834,17 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -4859,127 +4859,127 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>679</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>18711</t>
+          <t>23643</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>294.9</t>
+          <t>295.6</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>299.95</t>
+          <t>300.6</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>282.62</t>
+          <t>284.42</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>260.8</t>
+          <t>261.34</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>278.01</t>
+          <t>278.33</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>267.7979166666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>-0.01139792155548114</t>
+          <t>0.002373685995252783</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>0.009762666217808302</t>
+          <t>0.002167027837973068</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>0.005872408577275445</t>
+          <t>0.006368863334807573</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>0.0006138735420504471</t>
+          <t>0.002070552147239058</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>0.0001349072512648597</t>
+          <t>0.001169038465861805</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>0.001893998441153455</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
         <is>
-          <t>-36.28</t>
+          <t>-33.19</t>
         </is>
       </c>
       <c r="DF5" t="inlineStr">
@@ -4989,52 +4989,52 @@
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>9806218858.045713</t>
+          <t>12241196453.6561</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>5560098682.0</t>
+          <t>7011116445.0</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
         <is>
-          <t>6006011581.6</t>
+          <t>5644546408.8</t>
         </is>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>10770627918.9</t>
+          <t>9731028436.5</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>7201182115.833333</t>
+          <t>7352267947.233334</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>6347272593.44</t>
+          <t>6406488320.12</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>7819535548.9</t>
+          <t>7797907918.2875</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>409897595.8110061</t>
+          <t>297367008.8976186</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>-335858103.8789577</t>
+          <t>-321551219.1740274</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>5560098682.0</t>
+          <t>7011116445.0</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
@@ -5099,22 +5099,22 @@
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>39.06</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>55.18</t>
+          <t>54.71</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>377461</t>
+          <t>382597</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
@@ -5164,27 +5164,27 @@
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t>300.5</t>
+          <t>297.0</t>
         </is>
       </c>
       <c r="EQ5" t="inlineStr">
         <is>
-          <t>303.5</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="ER5" t="inlineStr">
         <is>
-          <t>294.0</t>
+          <t>288.5</t>
         </is>
       </c>
       <c r="ES5" t="inlineStr">
         <is>
-          <t>294.0</t>
+          <t>298.0</t>
         </is>
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>203.5</t>
         </is>
       </c>
       <c r="EU5" t="inlineStr">
@@ -5199,47 +5199,47 @@
       </c>
       <c r="EW5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="FA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF5" t="inlineStr">
@@ -5249,22 +5249,22 @@
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK5" t="inlineStr">
@@ -5441,7 +5441,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>價_量;【b1】;【v】測試條件</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26800.187</t>
+          <t>20801.802</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5466,727 +5466,727 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>2585.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.08121936870854173</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>轉強</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>TrendType : 轉強&lt;br&gt;TrendScore : 60&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2466.25</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2576.172221305986</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2356.327778694014</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.08914118301549774</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.003560528992878842</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.008384577293415685</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.1262756276588333</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.1298123458528708</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>1.512251504617027</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2026-10-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>5977639.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2993805.0</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>814847.0</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>2178958.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>2206939.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>10363536.0</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>2320.0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>2380.0</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>2390.0</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>2026-07-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>19.85</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>LV.1-3｜AI晶片｜晶圓代工（先進）｜</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>2,387</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>20802</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>93.33</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>2530.0</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>2504.0</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>2466.25</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>2412.0</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>2409.62</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>0.00877192982456143</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>0.005017057997190433</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>0.003560528992878842</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>0.001952394799152435</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>0.001714820203699841</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>48.79</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
+          <t>36.98</t>
+        </is>
+      </c>
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>24.85</t>
+        </is>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>87.33</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>-71.54</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>2026/09/21</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>114294337220.8903</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>53639152613.0</t>
+        </is>
+      </c>
+      <c r="DI6" t="inlineStr">
+        <is>
+          <t>59807486630.0</t>
+        </is>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>55314849475.4</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>53123237698.56667</t>
+        </is>
+      </c>
+      <c r="DL6" t="inlineStr">
+        <is>
+          <t>61223421823.14</t>
+        </is>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>73855431058.2125</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>453692030.3686815</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>618030769.5409622</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>53639152613.0</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="DR6" t="inlineStr">
+        <is>
+          <t>2440.0</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>5.94</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="DV6" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>半導體業</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr">
+        <is>
+          <t>-1.075787644781405</t>
+        </is>
+      </c>
+      <c r="EA6" t="inlineStr">
+        <is>
+          <t>17.49541246663658</t>
+        </is>
+      </c>
+      <c r="EB6" t="inlineStr">
+        <is>
+          <t>29.94631425482932</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>10.42</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>48.99</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>29.96</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>67.72%</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>60.34%</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>54.71</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
+        <is>
+          <t>67035176</t>
+        </is>
+      </c>
+      <c r="EM6" t="inlineStr">
+        <is>
+          <t>晶圓-5奈米30.98%、晶圓-3奈米20.85%、其他14.08%、晶圓-7奈米12.06%、晶圓-28奈米5.91%、晶圓-16奈米5.66%、晶圓-65奈米3.16%、晶圓-40及45奈米2.51%、晶圓-0.15及0.18微米2.32%、晶圓-0.11及0.13微米1.28%、晶圓-90奈米0.56%、晶圓-0.25微米以上0.51%、晶圓-20奈米0.11% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN6" t="inlineStr">
+        <is>
+          <t>台積電-半導體業-上市</t>
+        </is>
+      </c>
+      <c r="EO6" t="inlineStr">
+        <is>
+          <t>半導體業右上上市</t>
+        </is>
+      </c>
+      <c r="EP6" t="inlineStr">
+        <is>
           <t>2575.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.04035785112232095</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>轉強</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>TrendType : 轉強&lt;br&gt;TrendScore : 70&lt;br&gt;HH : True&lt;br&gt;HL : False&lt;br&gt;MA : True&lt;br&gt;VOL : True</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2457.5</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>2554.75170814358</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2360.24829185642</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0.07914686318907824</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0.003778208924742232</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>0.008663297337036191</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>0.1457726778475976</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0.1211960385478044</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1.405943387189993</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2026-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>2026-10-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>2026-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>3913488.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>3353481.0</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>523847.0</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>2829634.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>1928461.0</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>8671583.0</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2026/08/04</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>2320.0</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>1495.0</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>2380.0</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>2026/09/03</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>2390.0</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>2026-07-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>25.58</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>LV.1-3｜AI晶片｜晶圓代工（先進）｜</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>2,791</t>
-        </is>
-      </c>
-      <c r="CH6" t="inlineStr">
-        <is>
-          <t>26800</t>
-        </is>
-      </c>
-      <c r="CI6" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CJ6" t="inlineStr">
-        <is>
-          <t>93.33</t>
-        </is>
-      </c>
-      <c r="CK6" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="CL6" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="CM6" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="CN6" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="CO6" t="inlineStr">
-        <is>
-          <t>2508.0</t>
-        </is>
-      </c>
-      <c r="CP6" t="inlineStr">
-        <is>
-          <t>2491.5</t>
-        </is>
-      </c>
-      <c r="CQ6" t="inlineStr">
-        <is>
-          <t>2457.5</t>
-        </is>
-      </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>2407.3</t>
-        </is>
-      </c>
-      <c r="CS6" t="inlineStr">
-        <is>
-          <t>2405.5</t>
-        </is>
-      </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>1997.104166666667</t>
-        </is>
-      </c>
-      <c r="CU6" t="inlineStr">
-        <is>
-          <t>0.008038585209003246</t>
-        </is>
-      </c>
-      <c r="CV6" t="inlineStr">
-        <is>
-          <t>0.006056935190793533</t>
-        </is>
-      </c>
-      <c r="CW6" t="inlineStr">
-        <is>
-          <t>0.003778208924742232</t>
-        </is>
-      </c>
-      <c r="CX6" t="inlineStr">
-        <is>
-          <t>0.001414368318149783</t>
-        </is>
-      </c>
-      <c r="CY6" t="inlineStr">
-        <is>
-          <t>0.001405005984284724</t>
-        </is>
-      </c>
-      <c r="CZ6" t="inlineStr">
-        <is>
-          <t>0.002384114270178594</t>
-        </is>
-      </c>
-      <c r="DA6" t="inlineStr">
-        <is>
-          <t>44.09</t>
-        </is>
-      </c>
-      <c r="DB6" t="inlineStr">
-        <is>
-          <t>31.44</t>
-        </is>
-      </c>
-      <c r="DC6" t="inlineStr">
-        <is>
-          <t>21.82</t>
-        </is>
-      </c>
-      <c r="DD6" t="inlineStr">
-        <is>
-          <t>87.32</t>
-        </is>
-      </c>
-      <c r="DE6" t="inlineStr">
-        <is>
-          <t>-75.01</t>
-        </is>
-      </c>
-      <c r="DF6" t="inlineStr">
-        <is>
-          <t>2026/09/21</t>
-        </is>
-      </c>
-      <c r="DG6" t="inlineStr">
-        <is>
-          <t>92829449508.27856</t>
-        </is>
-      </c>
-      <c r="DH6" t="inlineStr">
-        <is>
-          <t>68799148330.0</t>
-        </is>
-      </c>
-      <c r="DI6" t="inlineStr">
-        <is>
-          <t>62411422904.2</t>
-        </is>
-      </c>
-      <c r="DJ6" t="inlineStr">
-        <is>
-          <t>59990341628.0</t>
-        </is>
-      </c>
-      <c r="DK6" t="inlineStr">
-        <is>
-          <t>52844454693.06667</t>
-        </is>
-      </c>
-      <c r="DL6" t="inlineStr">
-        <is>
-          <t>61318784045.58</t>
-        </is>
-      </c>
-      <c r="DM6" t="inlineStr">
-        <is>
-          <t>74724274437.925</t>
-        </is>
-      </c>
-      <c r="DN6" t="inlineStr">
-        <is>
-          <t>423812259.5711397</t>
-        </is>
-      </c>
-      <c r="DO6" t="inlineStr">
-        <is>
-          <t>1057581359.314552</t>
-        </is>
-      </c>
-      <c r="DP6" t="inlineStr">
-        <is>
-          <t>68799148330.0</t>
-        </is>
-      </c>
-      <c r="DQ6" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="DR6" t="inlineStr">
-        <is>
-          <t>2440.0</t>
-        </is>
-      </c>
-      <c r="DS6" t="inlineStr">
-        <is>
-          <t>2026/09/01</t>
-        </is>
-      </c>
-      <c r="DT6" t="inlineStr">
-        <is>
-          <t>5.53</t>
-        </is>
-      </c>
-      <c r="DU6" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="DV6" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="DW6" t="inlineStr">
-        <is>
-          <t>半導體業</t>
-        </is>
-      </c>
-      <c r="DX6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY6" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="DZ6" t="inlineStr">
-        <is>
-          <t>-1.075787644781405</t>
-        </is>
-      </c>
-      <c r="EA6" t="inlineStr">
-        <is>
-          <t>17.49541246663658</t>
-        </is>
-      </c>
-      <c r="EB6" t="inlineStr">
-        <is>
-          <t>29.94631425482932</t>
-        </is>
-      </c>
-      <c r="EC6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED6" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="EE6" t="inlineStr">
-        <is>
-          <t>10.38</t>
-        </is>
-      </c>
-      <c r="EF6" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="EG6" t="inlineStr">
-        <is>
-          <t>48.99</t>
-        </is>
-      </c>
-      <c r="EH6" t="inlineStr">
-        <is>
-          <t>29.85</t>
-        </is>
-      </c>
-      <c r="EI6" t="inlineStr">
-        <is>
-          <t>67.72%</t>
-        </is>
-      </c>
-      <c r="EJ6" t="inlineStr">
-        <is>
-          <t>60.34%</t>
-        </is>
-      </c>
-      <c r="EK6" t="inlineStr">
-        <is>
-          <t>55.18</t>
-        </is>
-      </c>
-      <c r="EL6" t="inlineStr">
-        <is>
-          <t>66775853</t>
-        </is>
-      </c>
-      <c r="EM6" t="inlineStr">
-        <is>
-          <t>晶圓-5奈米30.98%、晶圓-3奈米20.85%、其他14.08%、晶圓-7奈米12.06%、晶圓-28奈米5.91%、晶圓-16奈米5.66%、晶圓-65奈米3.16%、晶圓-40及45奈米2.51%、晶圓-0.15及0.18微米2.32%、晶圓-0.11及0.13微米1.28%、晶圓-90奈米0.56%、晶圓-0.25微米以上0.51%、晶圓-20奈米0.11% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN6" t="inlineStr">
-        <is>
-          <t>台積電-半導體業-上市</t>
-        </is>
-      </c>
-      <c r="EO6" t="inlineStr">
-        <is>
-          <t>半導體業右上上市</t>
-        </is>
-      </c>
-      <c r="EP6" t="inlineStr">
-        <is>
-          <t>2550.0</t>
-        </is>
-      </c>
       <c r="EQ6" t="inlineStr">
         <is>
-          <t>2580.0</t>
+          <t>2590.0</t>
         </is>
       </c>
       <c r="ER6" t="inlineStr">
         <is>
-          <t>2545.0</t>
+          <t>2565.0</t>
         </is>
       </c>
       <c r="ES6" t="inlineStr">
         <is>
-          <t>2575.0</t>
+          <t>2585.0</t>
         </is>
       </c>
       <c r="ET6" t="inlineStr">
         <is>
-          <t>918.0</t>
+          <t>1410.0</t>
         </is>
       </c>
       <c r="EU6" t="inlineStr">
@@ -6206,42 +6206,42 @@
       </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="FA6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="FB6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="FC6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FD6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF6" t="inlineStr">
@@ -6251,22 +6251,22 @@
       </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK6" t="inlineStr">
@@ -6443,7 +6443,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>328772.084</t>
+          <t>310620.526</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.1599125265911622</t>
+          <t>0.05057371256730539</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -6548,47 +6548,47 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>148.775</t>
+          <t>149.65</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>167.5239648837091</t>
+          <t>166.2159765467478</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>130.0260351162909</t>
+          <t>133.0840234532523</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.2520445623755211</t>
+          <t>0.221396278606719</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.009328358208955168</t>
+          <t>0.005881364476558515</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.007790253140065095</t>
+          <t>-0.007807768505653789</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.1335671343132216</t>
+          <t>-0.1215986708062307</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.2379892700917605</t>
+          <t>0.3477300132485959</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.8966302176543282</t>
+          <t>0.778558830258302</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -6633,67 +6633,67 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -6728,32 +6728,32 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-65801207.0</t>
+          <t>-48298580.0</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>24053018.0</t>
+          <t>14315018.0</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>42524711.0</t>
+          <t>101675721.0</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-18471693.0</t>
+          <t>-87360703.0</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>799771.0</t>
+          <t>5070614.0</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-83473129.0</t>
+          <t>-130588669.0</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
@@ -6763,12 +6763,12 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -6813,24 +6813,24 @@
       </c>
       <c r="BW7" t="inlineStr">
         <is>
+          <t>2026/10/06</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
           <t>2026/07/03</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>170.5</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>2026/06/04</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="CA7" t="inlineStr">
         <is>
           <t>2026-09-04 00:00:00</t>
@@ -6838,17 +6838,17 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>48.03</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>9,213</t>
+          <t>6,031</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>328772</t>
+          <t>310621</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -6878,102 +6878,102 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>157.05</t>
+          <t>156.2</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>148.78</t>
+          <t>149.65</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>132.16</t>
+          <t>132.55</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>139.92</t>
+          <t>140.28</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>90.564375</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>-0.001910828025477818</t>
+          <t>-0.00765794511805995</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>0.003193867773874093</t>
+          <t>-0.005412289079910981</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>0.009328358208955168</t>
+          <t>0.005881364476558515</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>0.002123142250530785</t>
+          <t>0.002950968523002473</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>0.002238438465326675</t>
+          <t>0.00259078929736023</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>0.005002947670184721</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="DB7" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="DC7" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="DD7" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="DE7" t="inlineStr">
         <is>
-          <t>-53.26</t>
+          <t>-54.35</t>
         </is>
       </c>
       <c r="DF7" t="inlineStr">
@@ -6993,52 +6993,52 @@
       </c>
       <c r="DG7" t="inlineStr">
         <is>
-          <t>18821575336.35429</t>
+          <t>30300205457.48049</t>
         </is>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
-          <t>51160542375.0</t>
+          <t>45892521954.0</t>
         </is>
       </c>
       <c r="DI7" t="inlineStr">
         <is>
-          <t>23718562578.8</t>
+          <t>29452799780.6</t>
         </is>
       </c>
       <c r="DJ7" t="inlineStr">
         <is>
-          <t>28233443932.4</t>
+          <t>28034967397.6</t>
         </is>
       </c>
       <c r="DK7" t="inlineStr">
         <is>
-          <t>25428646748.96667</t>
+          <t>26732070011.66667</t>
         </is>
       </c>
       <c r="DL7" t="inlineStr">
         <is>
-          <t>23352705156.08</t>
+          <t>23868417425.0</t>
         </is>
       </c>
       <c r="DM7" t="inlineStr">
         <is>
-          <t>27587630296.2875</t>
+          <t>27628782855.325</t>
         </is>
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>222474118.3395361</t>
+          <t>509933970.2801684</t>
         </is>
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>818572532.6470337</t>
+          <t>2090963155.953381</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
         <is>
-          <t>51160542375.0</t>
+          <t>45892521954.0</t>
         </is>
       </c>
       <c r="DQ7" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="DT7" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="DU7" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="DY7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="DZ7" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
@@ -7113,12 +7113,12 @@
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
@@ -7143,12 +7143,12 @@
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>55.18</t>
+          <t>54.71</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>1916939</t>
+          <t>1854089</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
@@ -7168,27 +7168,27 @@
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="EQ7" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="ER7" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="ES7" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="ET7" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="EU7" t="inlineStr">
@@ -7208,42 +7208,42 @@
       </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="FA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE7" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="FF7" t="inlineStr">
@@ -7253,22 +7253,22 @@
       </c>
       <c r="FG7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FH7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK7" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>124.114</t>
+          <t>117.593</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.11525992495091307</t>
+          <t>-0.18053601228403385</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -7550,47 +7550,47 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>18.3425</t>
+          <t>18.2675</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>19.47167063183108</t>
+          <t>19.29566904200986</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>17.21332936816892</t>
+          <t>17.23933095799014</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.1231206904000087</t>
+          <t>0.112568117367988</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.003666485605649195</t>
+          <t>-0.004088864658579716</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.00594561408806582</t>
+          <t>-0.00903885409469718</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.03803315954036046</t>
+          <t>-0.08570917688754331</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.1065693621811401</t>
+          <t>0.1035312386432738</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1.186670708079863</t>
+          <t>1.056165787609653</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -7700,12 +7700,12 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-103253.0</t>
+          <t>-93000.0</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>2164.0</t>
+          <t>1880.0</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-101089.0</t>
+          <t>-91120.0</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -7840,17 +7840,17 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>118</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -7885,87 +7885,87 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.01</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>20.22583333333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
         <is>
-          <t>-0.002218524681087186</t>
+          <t>-0.001111728738187878</t>
         </is>
       </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>-0.0008303349017437789</t>
+          <t>-0.002216066481994572</t>
         </is>
       </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>-0.003666485605649195</t>
+          <t>-0.004088864658579716</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>-0.001016532020758798</t>
+          <t>-0.0008568980291345785</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>-0.0006306844586073668</t>
+          <t>-0.0006642973394891394</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>-0.0007102199623273409</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="DB8" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="DE8" t="inlineStr">
         <is>
-          <t>-158.32</t>
+          <t>-158.59</t>
         </is>
       </c>
       <c r="DF8" t="inlineStr">
@@ -7995,52 +7995,52 @@
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>11368285.61571429</t>
+          <t>9445477.873170732</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>2229615.0</t>
+          <t>2098284.0</t>
         </is>
       </c>
       <c r="DI8" t="inlineStr">
         <is>
-          <t>1998582.0</t>
+          <t>1873955.0</t>
         </is>
       </c>
       <c r="DJ8" t="inlineStr">
         <is>
-          <t>2258948.2</t>
+          <t>2286805.8</t>
         </is>
       </c>
       <c r="DK8" t="inlineStr">
         <is>
-          <t>3104844.3</t>
+          <t>3103339.9</t>
         </is>
       </c>
       <c r="DL8" t="inlineStr">
         <is>
-          <t>3243286.8</t>
+          <t>3213698.48</t>
         </is>
       </c>
       <c r="DM8" t="inlineStr">
         <is>
-          <t>3806025.15</t>
+          <t>3760089.7125</t>
         </is>
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>-208754.2034005576</t>
+          <t>-220570.6634650949</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>-313523.287057932</t>
+          <t>-285561.1939012608</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
         <is>
-          <t>2229615.0</t>
+          <t>2098284.0</t>
         </is>
       </c>
       <c r="DQ8" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE8" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
@@ -8170,29 +8170,29 @@
       </c>
       <c r="EP8" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="EQ8" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="ER8" t="inlineStr">
         <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="ES8" t="inlineStr">
+        <is>
           <t>17.9</t>
         </is>
       </c>
-      <c r="ES8" t="inlineStr">
+      <c r="ET8" t="inlineStr">
         <is>
           <t>17.9</t>
         </is>
       </c>
-      <c r="ET8" t="inlineStr">
-        <is>
-          <t>17.9</t>
-        </is>
-      </c>
       <c r="EU8" t="inlineStr">
         <is>
           <t>38.31</t>
@@ -8210,42 +8210,42 @@
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF8" t="inlineStr">
@@ -8255,22 +8255,22 @@
       </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK8" t="inlineStr">
@@ -8447,7 +8447,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8472,339 +8472,339 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.32056663168940186</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>23.1375</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>23.52666239338076</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>22.74833760661924</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.03363910477629489</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.0001080613788631002</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>-0.0001348365641442584</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-0.01447371662771313</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.0915115688352429</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.9291829226663929</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>2026-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2026-07-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>15000.0</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>-88.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>14912.0</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
           <t>23.1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.20381991814461115</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>23.135</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>23.52983507549263</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>22.74016492450736</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0.03413313814502988</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0.0001080730573868038</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>3.981561242216713e-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>-0.004051099863614516</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0.08824569141432974</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>0.9175013541318612</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>2026-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>2026-07-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>33.3</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>9000.0</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>-88.0</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>8912.0</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>2026/08/28</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>23.1</t>
-        </is>
-      </c>
       <c r="BU9" t="inlineStr">
         <is>
           <t>2026/08/04</t>
@@ -8817,24 +8817,24 @@
       </c>
       <c r="BW9" t="inlineStr">
         <is>
+          <t>2026/10/06</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>2026/08/12</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
       <c r="CA9" t="inlineStr">
         <is>
           <t>2026-07-28 00:00:00</t>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -8877,42 +8877,42 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
-        <is>
-          <t>66.67</t>
-        </is>
-      </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.085</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
@@ -8932,47 +8932,47 @@
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
         <is>
-          <t>0.0004332755632581176</t>
+          <t>-0.0004330879168470414</t>
         </is>
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0006493506493506773</t>
         </is>
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>0.0001080730573868038</t>
+          <t>0.0001080613788631002</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>0.000299798706582699</t>
+          <t>-0.0004709710566878078</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>-0.0004014452027297777</t>
+          <t>-0.0001606425702811443</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>-0.0008529624040416461</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="DB9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="DC9" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="DD9" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="DE9" t="inlineStr">
         <is>
-          <t>-105.89</t>
+          <t>-108.11</t>
         </is>
       </c>
       <c r="DF9" t="inlineStr">
@@ -8997,52 +8997,52 @@
       </c>
       <c r="DG9" t="inlineStr">
         <is>
-          <t>1700.794285714286</t>
+          <t>1712.458536585366</t>
         </is>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>413.0</t>
+          <t>421.0</t>
         </is>
       </c>
       <c r="DI9" t="inlineStr">
         <is>
-          <t>441.2</t>
+          <t>503.4</t>
         </is>
       </c>
       <c r="DJ9" t="inlineStr">
         <is>
-          <t>366.5</t>
+          <t>381.2</t>
         </is>
       </c>
       <c r="DK9" t="inlineStr">
         <is>
-          <t>460.1666666666667</t>
+          <t>456.8666666666667</t>
         </is>
       </c>
       <c r="DL9" t="inlineStr">
         <is>
-          <t>649.56</t>
+          <t>594.92</t>
         </is>
       </c>
       <c r="DM9" t="inlineStr">
         <is>
-          <t>1031.0625</t>
+          <t>1012.7</t>
         </is>
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>-27.86461879310948</t>
+          <t>-24.21559096339664</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>-3.717707311460401</t>
+          <t>-4.14593788126723</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
         <is>
-          <t>413.0</t>
+          <t>421.0</t>
         </is>
       </c>
       <c r="DQ9" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="DT9" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="DU9" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
@@ -9172,22 +9172,22 @@
       </c>
       <c r="EP9" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="EQ9" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="ER9" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="ES9" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="ET9" t="inlineStr">
@@ -9212,42 +9212,42 @@
       </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="FA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FD9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF9" t="inlineStr">
@@ -9257,22 +9257,22 @@
       </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK9" t="inlineStr">
@@ -9449,7 +9449,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】;【x】看好</t>
+          <t>【e】;【x】看好</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1102.674</t>
+          <t>1069.483</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.18847281497075596</t>
+          <t>0.19630277477315522</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-30.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -9554,47 +9554,47 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>709.3</t>
+          <t>706.8</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>744.5381372349485</t>
+          <t>737.9302864882752</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>674.0618627650514</t>
+          <t>675.6697135117247</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.0993603192864756</t>
+          <t>0.0880879640302073</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>-0.002180488147991988</t>
+          <t>-0.003524601720005682</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.001182620094147824</t>
+          <t>-0.008875100436384842</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.02156386259390231</t>
+          <t>-0.1134492656347283</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.2006690916235679</t>
+          <t>0.1998422307312608</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.9419753320704127</t>
+          <t>0.8482995784534684</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -9639,147 +9639,147 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>41.7</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>-556640.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>4157.0</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-4157.0</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>-23286.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>-584083.0</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>41.7</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>-1120225.0</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>35000.0</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>2157.0</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>32843.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>-18282.0</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>-1105664.0</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
@@ -9794,29 +9794,29 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
+          <t>2026/10/06</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>696.0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>2026/05/21</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>800.0</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>2026/03/26</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>894.0</t>
-        </is>
-      </c>
       <c r="BW10" t="inlineStr">
         <is>
           <t>2026/09/10</t>
@@ -9844,17 +9844,17 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -9869,127 +9869,127 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>91</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>18.48</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>690.4</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>700.6</t>
+          <t>698.1</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>709.3</t>
+          <t>706.8</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>709.16</t>
+          <t>709.14</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>726.94</t>
+          <t>725.75</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>792.6125</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
         <is>
-          <t>-0.002312138728323698</t>
+          <t>0.002317497103128563</t>
         </is>
       </c>
       <c r="CV10" t="inlineStr">
         <is>
-          <t>-0.00199430199430195</t>
+          <t>-0.003568369968598328</t>
         </is>
       </c>
       <c r="CW10" t="inlineStr">
         <is>
-          <t>-0.002180488147991988</t>
+          <t>-0.003524601720005682</t>
         </is>
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>-0.0003946774921065321</t>
+          <t>-2.820238028089506e-05</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>-0.002606891110844334</t>
+          <t>-0.001633565471584553</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>0.0006154331702696858</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>-40.97</t>
+          <t>-26.55</t>
         </is>
       </c>
       <c r="DB10" t="inlineStr">
         <is>
-          <t>-8.28</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="DC10" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="DD10" t="inlineStr">
         <is>
-          <t>65.14</t>
+          <t>64.73</t>
         </is>
       </c>
       <c r="DE10" t="inlineStr">
         <is>
-          <t>-109.01</t>
+          <t>-109.71</t>
         </is>
       </c>
       <c r="DF10" t="inlineStr">
@@ -9999,52 +9999,52 @@
       </c>
       <c r="DG10" t="inlineStr">
         <is>
-          <t>4289168980.667143</t>
+          <t>4408927902.234146</t>
         </is>
       </c>
       <c r="DH10" t="inlineStr">
         <is>
-          <t>764683058.0</t>
+          <t>741884216.0</t>
         </is>
       </c>
       <c r="DI10" t="inlineStr">
         <is>
-          <t>774182457.8</t>
+          <t>749375045.8</t>
         </is>
       </c>
       <c r="DJ10" t="inlineStr">
         <is>
-          <t>651409479.5</t>
+          <t>626409184.7</t>
         </is>
       </c>
       <c r="DK10" t="inlineStr">
         <is>
-          <t>1178669940.933333</t>
+          <t>1175966466.166667</t>
         </is>
       </c>
       <c r="DL10" t="inlineStr">
         <is>
-          <t>1115508188.8</t>
+          <t>1119466624.04</t>
         </is>
       </c>
       <c r="DM10" t="inlineStr">
         <is>
-          <t>1355912318.65</t>
+          <t>1334044569.225</t>
         </is>
       </c>
       <c r="DN10" t="inlineStr">
         <is>
-          <t>-109293573.081873</t>
+          <t>-101905087.0435813</t>
         </is>
       </c>
       <c r="DO10" t="inlineStr">
         <is>
-          <t>-71405340.569911</t>
+          <t>-61268413.86174846</t>
         </is>
       </c>
       <c r="DP10" t="inlineStr">
         <is>
-          <t>764683058.0</t>
+          <t>741884216.0</t>
         </is>
       </c>
       <c r="DQ10" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="DT10" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="DU10" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
@@ -10119,12 +10119,12 @@
       </c>
       <c r="EE10" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>23.88</t>
         </is>
       </c>
       <c r="EF10" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EG10" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="EI10" t="inlineStr">
@@ -10149,12 +10149,12 @@
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>34.59</t>
+          <t>34.52</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
         <is>
-          <t>240100</t>
+          <t>241838</t>
         </is>
       </c>
       <c r="EM10" t="inlineStr">
@@ -10169,32 +10169,32 @@
       </c>
       <c r="EO10" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械右下上市</t>
         </is>
       </c>
       <c r="EP10" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="EQ10" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>699.0</t>
         </is>
       </c>
       <c r="ER10" t="inlineStr">
         <is>
-          <t>690.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="ES10" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="ET10" t="inlineStr">
         <is>
-          <t>443.0</t>
+          <t>653.0</t>
         </is>
       </c>
       <c r="EU10" t="inlineStr">
@@ -10214,42 +10214,42 @@
       </c>
       <c r="EX10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="EY10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="FA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF10" t="inlineStr">
@@ -10259,22 +10259,22 @@
       </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK10" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>35720.704</t>
+          <t>26891.285</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -10476,727 +10476,727 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.017754967883819743</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 10&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : True</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>24.775</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>26.09309272096187</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>23.45690727903813</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.1064050632461652</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0.001212366134572651</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0.001669334205679052</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.009113413019289363</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0.09584147072906245</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>1.50152093248736</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2026-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>2026-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>-4222722.0</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>4878000.0</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>242000.0</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>4636000.0</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>1310990.0</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>1724268.0</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>2026/06/05</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>24.4</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>2026/03/23</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>24.3</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>2026-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>4.83</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>NA｜水泥｜水泥製造｜台灣水泥龍頭，跨足綠能</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>26891</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>37.14</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>44.16</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>25.48</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
+        <is>
+          <t>25.23</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>24.78</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>24.54</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
+          <t>24.28</t>
+        </is>
+      </c>
+      <c r="CT11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CU11" t="inlineStr">
+        <is>
+          <t>-0.0007843137254901489</t>
+        </is>
+      </c>
+      <c r="CV11" t="inlineStr">
+        <is>
+          <t>0.003380393716444718</t>
+        </is>
+      </c>
+      <c r="CW11" t="inlineStr">
+        <is>
+          <t>0.001212366134572651</t>
+        </is>
+      </c>
+      <c r="CX11" t="inlineStr">
+        <is>
+          <t>0.001142297650130297</t>
+        </is>
+      </c>
+      <c r="CY11" t="inlineStr">
+        <is>
+          <t>0.0006696716033482986</t>
+        </is>
+      </c>
+      <c r="CZ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DA11" t="inlineStr">
+        <is>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="DB11" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="DC11" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="DD11" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="DE11" t="inlineStr">
+        <is>
+          <t>-71.30</t>
+        </is>
+      </c>
+      <c r="DF11" t="inlineStr">
+        <is>
+          <t>2026/09/23</t>
+        </is>
+      </c>
+      <c r="DG11" t="inlineStr">
+        <is>
+          <t>1271874745.909756</t>
+        </is>
+      </c>
+      <c r="DH11" t="inlineStr">
+        <is>
+          <t>674559882.0</t>
+        </is>
+      </c>
+      <c r="DI11" t="inlineStr">
+        <is>
+          <t>1274887612.4</t>
+        </is>
+      </c>
+      <c r="DJ11" t="inlineStr">
+        <is>
+          <t>1252646906.8</t>
+        </is>
+      </c>
+      <c r="DK11" t="inlineStr">
+        <is>
+          <t>1342508855.633333</t>
+        </is>
+      </c>
+      <c r="DL11" t="inlineStr">
+        <is>
+          <t>1080101378.82</t>
+        </is>
+      </c>
+      <c r="DM11" t="inlineStr">
+        <is>
+          <t>943311753.775</t>
+        </is>
+      </c>
+      <c r="DN11" t="inlineStr">
+        <is>
+          <t>2096006.000254787</t>
+        </is>
+      </c>
+      <c r="DO11" t="inlineStr">
+        <is>
+          <t>-25707927.9922545</t>
+        </is>
+      </c>
+      <c r="DP11" t="inlineStr">
+        <is>
+          <t>674559882.0</t>
+        </is>
+      </c>
+      <c r="DQ11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="DR11" t="inlineStr">
+        <is>
+          <t>24.65</t>
+        </is>
+      </c>
+      <c r="DS11" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="DT11" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DU11" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="DV11" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="DW11" t="inlineStr">
+        <is>
+          <t>水泥工業</t>
+        </is>
+      </c>
+      <c r="DX11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY11" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="DZ11" t="inlineStr">
+        <is>
+          <t>-1.608351096530149</t>
+        </is>
+      </c>
+      <c r="EA11" t="inlineStr">
+        <is>
+          <t>-3.691438066611057</t>
+        </is>
+      </c>
+      <c r="EB11" t="inlineStr">
+        <is>
+          <t>-4.576639672381974</t>
+        </is>
+      </c>
+      <c r="EC11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED11" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="EE11" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="EF11" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EG11" t="inlineStr">
+        <is>
+          <t>4.96</t>
+        </is>
+      </c>
+      <c r="EH11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EI11" t="inlineStr">
+        <is>
+          <t>17.79%</t>
+        </is>
+      </c>
+      <c r="EJ11" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
+      <c r="EK11" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="EL11" t="inlineStr">
+        <is>
+          <t>189584</t>
+        </is>
+      </c>
+      <c r="EM11" t="inlineStr">
+        <is>
+          <t>水泥,預拌混擬土80.05%、電力供給及儲能,可充式鋰離16.70%、海陸運輸3.25% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN11" t="inlineStr">
+        <is>
+          <t>台泥-水泥工業-上市</t>
+        </is>
+      </c>
+      <c r="EO11" t="inlineStr">
+        <is>
+          <t>水泥工業右上上市</t>
+        </is>
+      </c>
+      <c r="EP11" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.04837457019173518</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>空頭</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>TrendType : 空頭&lt;br&gt;TrendScore : 10&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : True</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>24.745</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>26.04960722058418</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>23.44039277941582</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0.1054441075436797</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0.0011125720643268</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>0.001035459163432062</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>-0.00153578875618543</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>0.1066543550447598</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>1.5463842090306</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2026-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>2026-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>2026-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>-3548811.0</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>4884000.0</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>189000.0</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>4695000.0</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>1006909.0</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>2153098.0</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>2026/06/05</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>2026/03/23</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>24.3</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>2026/08/27</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>2026-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>6.41</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>-2.40</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>NA｜水泥｜水泥製造｜台灣水泥龍頭，跨足綠能</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
-        <is>
-          <t>35721</t>
-        </is>
-      </c>
-      <c r="CI11" t="inlineStr">
-        <is>
-          <t>39.53</t>
-        </is>
-      </c>
-      <c r="CJ11" t="inlineStr">
-        <is>
-          <t>53.49</t>
-        </is>
-      </c>
-      <c r="CK11" t="inlineStr">
-        <is>
-          <t>-1.96</t>
-        </is>
-      </c>
-      <c r="CL11" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
-      <c r="CM11" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="CN11" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="CO11" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="CP11" t="inlineStr">
-        <is>
-          <t>25.145</t>
-        </is>
-      </c>
-      <c r="CQ11" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
-      </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>24.51</t>
-        </is>
-      </c>
-      <c r="CS11" t="inlineStr">
-        <is>
-          <t>24.27</t>
-        </is>
-      </c>
-      <c r="CT11" t="inlineStr">
-        <is>
-          <t>23.991875</t>
-        </is>
-      </c>
-      <c r="CU11" t="inlineStr">
-        <is>
-          <t>-0.00195694716242667</t>
-        </is>
-      </c>
-      <c r="CV11" t="inlineStr">
-        <is>
-          <t>0.002192108409725169</t>
-        </is>
-      </c>
-      <c r="CW11" t="inlineStr">
-        <is>
-          <t>0.0011125720643268</t>
-        </is>
-      </c>
-      <c r="CX11" t="inlineStr">
-        <is>
-          <t>0.0008165931732810883</t>
-        </is>
-      </c>
-      <c r="CY11" t="inlineStr">
-        <is>
-          <t>0.0005411813215132621</t>
-        </is>
-      </c>
-      <c r="CZ11" t="inlineStr">
-        <is>
-          <t>0.0002431969982543691</t>
-        </is>
-      </c>
-      <c r="DA11" t="inlineStr">
-        <is>
-          <t>34.55</t>
-        </is>
-      </c>
-      <c r="DB11" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="DC11" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="DD11" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="DE11" t="inlineStr">
-        <is>
-          <t>-74.38</t>
-        </is>
-      </c>
-      <c r="DF11" t="inlineStr">
-        <is>
-          <t>2026/09/23</t>
-        </is>
-      </c>
-      <c r="DG11" t="inlineStr">
-        <is>
-          <t>1191382610.161891</t>
-        </is>
-      </c>
-      <c r="DH11" t="inlineStr">
-        <is>
-          <t>900036992.0</t>
-        </is>
-      </c>
-      <c r="DI11" t="inlineStr">
-        <is>
-          <t>1299287448.6</t>
-        </is>
-      </c>
-      <c r="DJ11" t="inlineStr">
-        <is>
-          <t>1239335143.7</t>
-        </is>
-      </c>
-      <c r="DK11" t="inlineStr">
-        <is>
-          <t>1349256183.933333</t>
-        </is>
-      </c>
-      <c r="DL11" t="inlineStr">
-        <is>
-          <t>1072378767.98</t>
-        </is>
-      </c>
-      <c r="DM11" t="inlineStr">
-        <is>
-          <t>944467372.95</t>
-        </is>
-      </c>
-      <c r="DN11" t="inlineStr">
-        <is>
-          <t>7151266.727360797</t>
-        </is>
-      </c>
-      <c r="DO11" t="inlineStr">
-        <is>
-          <t>14261573.1814146</t>
-        </is>
-      </c>
-      <c r="DP11" t="inlineStr">
-        <is>
-          <t>900036992.0</t>
-        </is>
-      </c>
-      <c r="DQ11" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="DR11" t="inlineStr">
-        <is>
-          <t>24.65</t>
-        </is>
-      </c>
-      <c r="DS11" t="inlineStr">
-        <is>
-          <t>2026/08/11</t>
-        </is>
-      </c>
-      <c r="DT11" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="DU11" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="DV11" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="DW11" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="DX11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY11" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="DZ11" t="inlineStr">
-        <is>
-          <t>-1.608351096530149</t>
-        </is>
-      </c>
-      <c r="EA11" t="inlineStr">
-        <is>
-          <t>-3.691438066611057</t>
-        </is>
-      </c>
-      <c r="EB11" t="inlineStr">
-        <is>
-          <t>-4.576639672381974</t>
-        </is>
-      </c>
-      <c r="EC11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="ED11" t="inlineStr">
-        <is>
-          <t>價跌量縮</t>
-        </is>
-      </c>
-      <c r="EE11" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="EF11" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="EG11" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="EH11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="EI11" t="inlineStr">
-        <is>
-          <t>17.79%</t>
-        </is>
-      </c>
-      <c r="EJ11" t="inlineStr">
-        <is>
-          <t>6.24%</t>
-        </is>
-      </c>
-      <c r="EK11" t="inlineStr">
-        <is>
-          <t>14.63</t>
-        </is>
-      </c>
-      <c r="EL11" t="inlineStr">
-        <is>
-          <t>188080</t>
-        </is>
-      </c>
-      <c r="EM11" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土80.05%、電力供給及儲能,可充式鋰離16.70%、海陸運輸3.25% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN11" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="EO11" t="inlineStr">
-        <is>
-          <t>水泥工業平上市</t>
-        </is>
-      </c>
-      <c r="EP11" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
       <c r="EQ11" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="ER11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="ES11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="ET11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="EU11" t="inlineStr">
@@ -11216,42 +11216,42 @@
       </c>
       <c r="EX11" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EY11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EZ11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="FA11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="FB11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="FC11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FD11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FE11" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="FF11" t="inlineStr">
@@ -11261,22 +11261,22 @@
       </c>
       <c r="FG11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="FH11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="FI11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK11" t="inlineStr">

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GR11"/>
+  <dimension ref="A1:GS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,610 +821,615 @@
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
+          <t>voc_cross</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
           <t>voc_cross_d</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>MA_5</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>MA_10</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>MA_20</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>MA_50</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>MA_80</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>MA_240</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>MA_5_斜率</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>MA_10_斜率</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>MA_20_斜率</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>MA_50_斜率</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>MA_80_斜率</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>MA_240_斜率</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_5</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_10</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_30</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_50</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_80</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>成交金額_補值</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>最小收盤價</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>盤整震盪_前15日次數</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>多頭排列_前5日次數</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>下跌帶量_前15日次數</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>MA_break_前15日次數</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>抄底訊號_前15日次數</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>黃金交叉_前15日次數</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>量起點_前15日次數</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>價過5日_前15日次數</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>量短5長30比</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前10日次數</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前5日次數</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前2日次數</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前1日次數</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>季別</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>營業收入</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>營業成本</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>營業毛利</t>
         </is>
       </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>毛利率</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>營業利益</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>營益率</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>業外收支</t>
         </is>
       </c>
-      <c r="FS1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>稅前淨利</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>稅後淨利</t>
         </is>
       </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>EPS(元)</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>EPS_前8季全為正</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>去年同季比較</t>
         </is>
       </c>
-      <c r="FX1" s="1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>EPS_MA_8</t>
         </is>
       </c>
-      <c r="FY1" s="1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>GM_MA_8</t>
         </is>
       </c>
-      <c r="FZ1" s="1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>EPS_維持</t>
         </is>
       </c>
-      <c r="GA1" s="1" t="inlineStr">
+      <c r="GB1" s="1" t="inlineStr">
         <is>
           <t>毛利率_維持</t>
         </is>
       </c>
-      <c r="GB1" s="1" t="inlineStr">
+      <c r="GC1" s="1" t="inlineStr">
         <is>
           <t>EPS_創新高</t>
         </is>
       </c>
-      <c r="GC1" s="1" t="inlineStr">
+      <c r="GD1" s="1" t="inlineStr">
         <is>
           <t>毛利率_創新高</t>
         </is>
       </c>
-      <c r="GD1" s="1" t="inlineStr">
+      <c r="GE1" s="1" t="inlineStr">
         <is>
           <t>財報健康</t>
         </is>
       </c>
-      <c r="GE1" s="1" t="inlineStr">
+      <c r="GF1" s="1" t="inlineStr">
         <is>
           <t>財報強勢</t>
         </is>
       </c>
-      <c r="GF1" s="1" t="inlineStr">
+      <c r="GG1" s="1" t="inlineStr">
         <is>
           <t>EPS_QoQ</t>
         </is>
       </c>
-      <c r="GG1" s="1" t="inlineStr">
+      <c r="GH1" s="1" t="inlineStr">
         <is>
           <t>EPS_QoQ_%</t>
         </is>
       </c>
-      <c r="GH1" s="1" t="inlineStr">
+      <c r="GI1" s="1" t="inlineStr">
         <is>
           <t>GM_QoQ</t>
         </is>
       </c>
-      <c r="GI1" s="1" t="inlineStr">
+      <c r="GJ1" s="1" t="inlineStr">
         <is>
           <t>GM_QoQ_%</t>
         </is>
       </c>
-      <c r="GJ1" s="1" t="inlineStr">
+      <c r="GK1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY</t>
         </is>
       </c>
-      <c r="GK1" s="1" t="inlineStr">
+      <c r="GL1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY_%</t>
         </is>
       </c>
-      <c r="GL1" s="1" t="inlineStr">
+      <c r="GM1" s="1" t="inlineStr">
         <is>
           <t>GM_YoY</t>
         </is>
       </c>
-      <c r="GM1" s="1" t="inlineStr">
+      <c r="GN1" s="1" t="inlineStr">
         <is>
           <t>GM_YoY_%</t>
         </is>
       </c>
-      <c r="GN1" s="1" t="inlineStr">
+      <c r="GO1" s="1" t="inlineStr">
         <is>
           <t>EPS_成長</t>
         </is>
       </c>
-      <c r="GO1" s="1" t="inlineStr">
+      <c r="GP1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY成長</t>
         </is>
       </c>
-      <c r="GP1" s="1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>毛利率成長</t>
         </is>
       </c>
-      <c r="GQ1" s="1" t="inlineStr">
+      <c r="GR1" s="1" t="inlineStr">
         <is>
           <t>毛利率YoY成長</t>
         </is>
       </c>
-      <c r="GR1" s="1" t="inlineStr">
+      <c r="GS1" s="1" t="inlineStr">
         <is>
           <t>財報動能強</t>
         </is>
@@ -1823,399 +1828,399 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
           <t>2026-08-07 00:00:00</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>5.56</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>-2.08</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>NA｜電子紙｜電子紙材料｜</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>6506</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>23.08</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>53.85</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>-1.1</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="CM2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
           <t>-8.35</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>-8.10</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>145.6</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>144.85</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>145.6</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>158.86</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>172.86</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
           <t>-0.0006898930665746317</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>-0.001029159519725598</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>-0.003637732062217625</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>-0.003746127800590582</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
           <t>23.72</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>-3.58</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>-4.69</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>19.75</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>-123.77</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>2026/09/10</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>2138504.297101449</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>499905.0</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>996149.6</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>920157.6</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>900315.9333333333</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>1293066.34</t>
         </is>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>1414677.2625</t>
         </is>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>-16146.3243821654</t>
         </is>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>-4177.676415804424</t>
         </is>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>499905.0</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
           <t>215.0</t>
         </is>
       </c>
-      <c r="DS2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>2026/05/13</t>
         </is>
       </c>
-      <c r="DT2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>-33.02</t>
         </is>
       </c>
-      <c r="DU2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>元太</t>
         </is>
       </c>
-      <c r="DV2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>元太</t>
         </is>
       </c>
-      <c r="DW2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>0.71</t>
         </is>
       </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>-10.92428622334589</t>
         </is>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>-12.55445557714831</t>
         </is>
       </c>
-      <c r="EB2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>1.393765396179179</t>
         </is>
       </c>
-      <c r="EC2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="EF2" t="inlineStr">
+      <c r="EG2" t="inlineStr">
         <is>
           <t>4.09</t>
         </is>
       </c>
-      <c r="EG2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>8.85</t>
         </is>
       </c>
-      <c r="EH2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>14.11</t>
         </is>
       </c>
-      <c r="EI2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>58.72%</t>
         </is>
       </c>
-      <c r="EJ2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>34.67%</t>
         </is>
       </c>
-      <c r="EK2" t="inlineStr">
+      <c r="EL2" t="inlineStr">
         <is>
           <t>35.91</t>
         </is>
       </c>
-      <c r="EL2" t="inlineStr">
+      <c r="EM2" t="inlineStr">
         <is>
           <t>167475</t>
         </is>
       </c>
-      <c r="EM2" t="inlineStr">
+      <c r="EN2" t="inlineStr">
         <is>
           <t>消費性電子產品56.39%、物聯網應用43.61% (2025年)</t>
         </is>
       </c>
-      <c r="EN2" t="inlineStr">
+      <c r="EO2" t="inlineStr">
         <is>
           <t>元太-光電業-上櫃</t>
         </is>
       </c>
-      <c r="EO2" t="inlineStr">
+      <c r="EP2" t="inlineStr">
         <is>
           <t>光電業右下上櫃</t>
         </is>
       </c>
-      <c r="EP2" t="inlineStr">
+      <c r="EQ2" t="inlineStr">
         <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="EQ2" t="inlineStr">
+      <c r="ER2" t="inlineStr">
         <is>
           <t>147.0</t>
         </is>
       </c>
-      <c r="ER2" t="inlineStr">
+      <c r="ES2" t="inlineStr">
         <is>
           <t>144.0</t>
         </is>
       </c>
-      <c r="ES2" t="inlineStr">
+      <c r="ET2" t="inlineStr">
         <is>
           <t>144.0</t>
         </is>
       </c>
-      <c r="ET2" t="inlineStr">
+      <c r="EU2" t="inlineStr">
         <is>
           <t>136.5</t>
         </is>
       </c>
-      <c r="EU2" t="inlineStr">
+      <c r="EV2" t="inlineStr">
         <is>
           <t>65.6</t>
         </is>
       </c>
-      <c r="EV2" t="inlineStr">
+      <c r="EW2" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 面板、電子書</t>
         </is>
       </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX2" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="FA2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2238,12 +2243,12 @@
       </c>
       <c r="FF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
@@ -2263,94 +2268,94 @@
       </c>
       <c r="FK2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL2" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL2" t="inlineStr">
+      <c r="FM2" t="inlineStr">
         <is>
           <t>10216.0</t>
         </is>
       </c>
-      <c r="FM2" t="inlineStr">
+      <c r="FN2" t="inlineStr">
         <is>
           <t>4217.0</t>
         </is>
       </c>
-      <c r="FN2" t="inlineStr">
+      <c r="FO2" t="inlineStr">
         <is>
           <t>5999.0</t>
         </is>
       </c>
-      <c r="FO2" t="inlineStr">
+      <c r="FP2" t="inlineStr">
         <is>
           <t>58.72</t>
         </is>
       </c>
-      <c r="FP2" t="inlineStr">
+      <c r="FQ2" t="inlineStr">
         <is>
           <t>3542.0</t>
         </is>
       </c>
-      <c r="FQ2" t="inlineStr">
+      <c r="FR2" t="inlineStr">
         <is>
           <t>34.67%</t>
         </is>
       </c>
-      <c r="FR2" t="inlineStr">
+      <c r="FS2" t="inlineStr">
         <is>
           <t>1033.0</t>
         </is>
       </c>
-      <c r="FS2" t="inlineStr">
+      <c r="FT2" t="inlineStr">
         <is>
           <t>4575.0</t>
         </is>
       </c>
-      <c r="FT2" t="inlineStr">
+      <c r="FU2" t="inlineStr">
         <is>
           <t>3733.0</t>
         </is>
       </c>
-      <c r="FU2" t="inlineStr">
+      <c r="FV2" t="inlineStr">
         <is>
           <t>3.23</t>
         </is>
       </c>
-      <c r="FV2" t="inlineStr">
+      <c r="FW2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW2" t="inlineStr">
+      <c r="FX2" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率衰退</t>
         </is>
       </c>
-      <c r="FX2" t="inlineStr">
+      <c r="FY2" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="FY2" t="inlineStr">
+      <c r="FZ2" t="inlineStr">
         <is>
           <t>54.665</t>
         </is>
       </c>
-      <c r="FZ2" t="inlineStr">
+      <c r="GA2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA2" t="inlineStr">
+      <c r="GB2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GC2" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2358,75 +2363,80 @@
       </c>
       <c r="GD2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE2" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG2" t="inlineStr">
+        <is>
           <t>0.8199999999999998</t>
         </is>
       </c>
-      <c r="GG2" t="inlineStr">
+      <c r="GH2" t="inlineStr">
         <is>
           <t>0.3402489626556016</t>
         </is>
       </c>
-      <c r="GH2" t="inlineStr">
+      <c r="GI2" t="inlineStr">
         <is>
           <t>-0.9299999999999997</t>
         </is>
       </c>
-      <c r="GI2" t="inlineStr">
+      <c r="GJ2" t="inlineStr">
         <is>
           <t>-0.01559094719195309</t>
         </is>
       </c>
-      <c r="GJ2" t="inlineStr">
+      <c r="GK2" t="inlineStr">
         <is>
           <t>0.6499999999999999</t>
         </is>
       </c>
-      <c r="GK2" t="inlineStr">
+      <c r="GL2" t="inlineStr">
         <is>
           <t>0.251937984496124</t>
         </is>
       </c>
-      <c r="GL2" t="inlineStr">
+      <c r="GM2" t="inlineStr">
         <is>
           <t>-1.57</t>
         </is>
       </c>
-      <c r="GM2" t="inlineStr">
+      <c r="GN2" t="inlineStr">
         <is>
           <t>-0.02604080278653176</t>
         </is>
       </c>
-      <c r="GN2" t="inlineStr">
+      <c r="GO2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO2" t="inlineStr">
+      <c r="GP2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
       <c r="GR2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GS2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -2825,434 +2835,434 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
           <t>2026-09-22 00:00:00</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>23.19</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>0.28</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>LV.3-2｜AI伺服器｜散熱-液冷系統｜液冷需求快速擴大</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>1687</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>27.27</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>37.83</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>-1.25</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>2.87</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>13.83</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>9.99</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>2400.0</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>2449.0</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>2333.0</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>2049.5</t>
         </is>
       </c>
-      <c r="CS3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>1863.31</t>
         </is>
       </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
           <t>-0.001663893510815306</t>
         </is>
       </c>
-      <c r="CV3" t="inlineStr">
+      <c r="CW3" t="inlineStr">
         <is>
           <t>-0.005280259951259136</t>
         </is>
       </c>
-      <c r="CW3" t="inlineStr">
+      <c r="CX3" t="inlineStr">
         <is>
           <t>0.004629131230487582</t>
         </is>
       </c>
-      <c r="CX3" t="inlineStr">
+      <c r="CY3" t="inlineStr">
         <is>
           <t>0.01015328503129775</t>
         </is>
       </c>
-      <c r="CY3" t="inlineStr">
+      <c r="CZ3" t="inlineStr">
         <is>
           <t>0.003669539455965598</t>
         </is>
       </c>
-      <c r="CZ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
           <t>-14.59</t>
         </is>
       </c>
-      <c r="DB3" t="inlineStr">
+      <c r="DC3" t="inlineStr">
         <is>
           <t>104.05</t>
         </is>
       </c>
-      <c r="DC3" t="inlineStr">
+      <c r="DD3" t="inlineStr">
         <is>
           <t>121.82</t>
         </is>
       </c>
-      <c r="DD3" t="inlineStr">
+      <c r="DE3" t="inlineStr">
         <is>
           <t>147.01</t>
         </is>
       </c>
-      <c r="DE3" t="inlineStr">
+      <c r="DF3" t="inlineStr">
         <is>
           <t>-17.13</t>
         </is>
       </c>
-      <c r="DF3" t="inlineStr">
+      <c r="DG3" t="inlineStr">
         <is>
           <t>2026/09/22</t>
         </is>
       </c>
-      <c r="DG3" t="inlineStr">
+      <c r="DH3" t="inlineStr">
         <is>
           <t>5180831435.710145</t>
         </is>
       </c>
-      <c r="DH3" t="inlineStr">
+      <c r="DI3" t="inlineStr">
         <is>
           <t>3993048955.0</t>
         </is>
       </c>
-      <c r="DI3" t="inlineStr">
+      <c r="DJ3" t="inlineStr">
         <is>
           <t>4357077257.8</t>
         </is>
       </c>
-      <c r="DJ3" t="inlineStr">
+      <c r="DK3" t="inlineStr">
         <is>
           <t>4497214113.3</t>
         </is>
       </c>
-      <c r="DK3" t="inlineStr">
+      <c r="DL3" t="inlineStr">
         <is>
           <t>4067378248.433333</t>
         </is>
       </c>
-      <c r="DL3" t="inlineStr">
+      <c r="DM3" t="inlineStr">
         <is>
           <t>3761400442.86</t>
         </is>
       </c>
-      <c r="DM3" t="inlineStr">
+      <c r="DN3" t="inlineStr">
         <is>
           <t>3015543453.5375</t>
         </is>
       </c>
-      <c r="DN3" t="inlineStr">
+      <c r="DO3" t="inlineStr">
         <is>
           <t>162096002.3813558</t>
         </is>
       </c>
-      <c r="DO3" t="inlineStr">
+      <c r="DP3" t="inlineStr">
         <is>
           <t>78686800.11820316</t>
         </is>
       </c>
-      <c r="DP3" t="inlineStr">
+      <c r="DQ3" t="inlineStr">
         <is>
           <t>3993048955.0</t>
         </is>
       </c>
-      <c r="DQ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
           <t>1800.0</t>
         </is>
       </c>
-      <c r="DS3" t="inlineStr">
+      <c r="DT3" t="inlineStr">
         <is>
           <t>2026/08/19</t>
         </is>
       </c>
-      <c r="DT3" t="inlineStr">
+      <c r="DU3" t="inlineStr">
         <is>
           <t>31.67</t>
         </is>
       </c>
-      <c r="DU3" t="inlineStr">
+      <c r="DV3" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="DV3" t="inlineStr">
+      <c r="DW3" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="DW3" t="inlineStr">
+      <c r="DX3" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="DX3" t="inlineStr">
+      <c r="DY3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY3" t="inlineStr">
+      <c r="DZ3" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="DZ3" t="inlineStr">
+      <c r="EA3" t="inlineStr">
         <is>
           <t>-15.44126147733529</t>
         </is>
       </c>
-      <c r="EA3" t="inlineStr">
+      <c r="EB3" t="inlineStr">
         <is>
           <t>59.0506505428733</t>
         </is>
       </c>
-      <c r="EB3" t="inlineStr">
+      <c r="EC3" t="inlineStr">
         <is>
           <t>78.47048569813265</t>
         </is>
       </c>
-      <c r="EC3" t="inlineStr">
+      <c r="ED3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED3" t="inlineStr">
+      <c r="EE3" t="inlineStr">
         <is>
           <t>價跌量縮</t>
         </is>
       </c>
-      <c r="EE3" t="inlineStr">
+      <c r="EF3" t="inlineStr">
         <is>
           <t>19.45</t>
         </is>
       </c>
-      <c r="EF3" t="inlineStr">
+      <c r="EG3" t="inlineStr">
         <is>
           <t>0.53</t>
         </is>
       </c>
-      <c r="EG3" t="inlineStr">
+      <c r="EH3" t="inlineStr">
         <is>
           <t>54.55</t>
         </is>
       </c>
-      <c r="EH3" t="inlineStr">
+      <c r="EI3" t="inlineStr">
         <is>
           <t>50.7</t>
         </is>
       </c>
-      <c r="EI3" t="inlineStr">
+      <c r="EJ3" t="inlineStr">
         <is>
           <t>34.05%</t>
         </is>
       </c>
-      <c r="EJ3" t="inlineStr">
+      <c r="EK3" t="inlineStr">
         <is>
           <t>27.90%</t>
         </is>
       </c>
-      <c r="EK3" t="inlineStr">
+      <c r="EL3" t="inlineStr">
         <is>
           <t>52.54</t>
         </is>
       </c>
-      <c r="EL3" t="inlineStr">
+      <c r="EM3" t="inlineStr">
         <is>
           <t>162471</t>
         </is>
       </c>
-      <c r="EM3" t="inlineStr">
+      <c r="EN3" t="inlineStr">
         <is>
           <t>折疊式手機轉軸56.42%、伺服器產品組件36.29%、筆記型電腦轉軸6.41%、其他0.88% (2025年)</t>
         </is>
       </c>
-      <c r="EN3" t="inlineStr">
+      <c r="EO3" t="inlineStr">
         <is>
           <t>富世達-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="EO3" t="inlineStr">
+      <c r="EP3" t="inlineStr">
         <is>
           <t>電子零組件業右上上市</t>
         </is>
       </c>
-      <c r="EP3" t="inlineStr">
+      <c r="EQ3" t="inlineStr">
         <is>
           <t>2330.0</t>
         </is>
       </c>
-      <c r="EQ3" t="inlineStr">
+      <c r="ER3" t="inlineStr">
         <is>
           <t>2425.0</t>
         </is>
       </c>
-      <c r="ER3" t="inlineStr">
+      <c r="ES3" t="inlineStr">
         <is>
           <t>2310.0</t>
         </is>
       </c>
-      <c r="ES3" t="inlineStr">
+      <c r="ET3" t="inlineStr">
         <is>
           <t>2370.0</t>
         </is>
       </c>
-      <c r="ET3" t="inlineStr">
+      <c r="EU3" t="inlineStr">
         <is>
           <t>1230.0</t>
         </is>
       </c>
-      <c r="EU3" t="inlineStr">
+      <c r="EV3" t="inlineStr">
         <is>
           <t>121.86</t>
         </is>
       </c>
-      <c r="EV3" t="inlineStr">
+      <c r="EW3" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 機構樞紐</t>
         </is>
       </c>
-      <c r="EW3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ3" t="inlineStr">
+      <c r="FA3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="FA3" t="inlineStr">
+      <c r="FB3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FB3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FC3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FD3" t="inlineStr">
+      <c r="FE3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE3" t="inlineStr">
+      <c r="FF3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="FF3" t="inlineStr">
+      <c r="FG3" t="inlineStr">
         <is>
           <t>1.071224998431914</t>
         </is>
       </c>
-      <c r="FG3" t="inlineStr">
+      <c r="FH3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="FH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FI3" t="inlineStr">
         <is>
           <t>0</t>
@@ -3265,170 +3275,175 @@
       </c>
       <c r="FK3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL3" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL3" t="inlineStr">
+      <c r="FM3" t="inlineStr">
         <is>
           <t>3740.0</t>
         </is>
       </c>
-      <c r="FM3" t="inlineStr">
+      <c r="FN3" t="inlineStr">
         <is>
           <t>2467.0</t>
         </is>
       </c>
-      <c r="FN3" t="inlineStr">
+      <c r="FO3" t="inlineStr">
         <is>
           <t>1273.0</t>
         </is>
       </c>
-      <c r="FO3" t="inlineStr">
+      <c r="FP3" t="inlineStr">
         <is>
           <t>34.05</t>
         </is>
       </c>
-      <c r="FP3" t="inlineStr">
+      <c r="FQ3" t="inlineStr">
         <is>
           <t>1043.0</t>
         </is>
       </c>
-      <c r="FQ3" t="inlineStr">
+      <c r="FR3" t="inlineStr">
         <is>
           <t>27.90%</t>
         </is>
       </c>
-      <c r="FR3" t="inlineStr">
+      <c r="FS3" t="inlineStr">
         <is>
           <t>32.0</t>
         </is>
       </c>
-      <c r="FS3" t="inlineStr">
+      <c r="FT3" t="inlineStr">
         <is>
           <t>1075.0</t>
         </is>
       </c>
-      <c r="FT3" t="inlineStr">
+      <c r="FU3" t="inlineStr">
         <is>
           <t>849.0</t>
         </is>
       </c>
-      <c r="FU3" t="inlineStr">
+      <c r="FV3" t="inlineStr">
         <is>
           <t>12.39</t>
         </is>
       </c>
-      <c r="FV3" t="inlineStr">
+      <c r="FW3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW3" t="inlineStr">
+      <c r="FX3" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX3" t="inlineStr">
+      <c r="FY3" t="inlineStr">
         <is>
           <t>8.457500000000001</t>
         </is>
       </c>
-      <c r="FY3" t="inlineStr">
+      <c r="FZ3" t="inlineStr">
         <is>
           <t>26.60125</t>
         </is>
       </c>
-      <c r="FZ3" t="inlineStr">
+      <c r="GA3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA3" t="inlineStr">
+      <c r="GB3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GC3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GD3" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GD3" t="inlineStr">
+      <c r="GE3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG3" t="inlineStr">
+        <is>
           <t>-0.9900000000000002</t>
         </is>
       </c>
-      <c r="GG3" t="inlineStr">
+      <c r="GH3" t="inlineStr">
         <is>
           <t>-0.07399103139013452</t>
         </is>
       </c>
-      <c r="GH3" t="inlineStr">
+      <c r="GI3" t="inlineStr">
         <is>
           <t>1.739999999999995</t>
         </is>
       </c>
-      <c r="GI3" t="inlineStr">
+      <c r="GJ3" t="inlineStr">
         <is>
           <t>0.05385329619312884</t>
         </is>
       </c>
-      <c r="GJ3" t="inlineStr">
+      <c r="GK3" t="inlineStr">
         <is>
           <t>7.57</t>
         </is>
       </c>
-      <c r="GK3" t="inlineStr">
+      <c r="GL3" t="inlineStr">
         <is>
           <t>1.570539419087137</t>
         </is>
       </c>
-      <c r="GL3" t="inlineStr">
+      <c r="GM3" t="inlineStr">
         <is>
           <t>9.979999999999997</t>
         </is>
       </c>
-      <c r="GM3" t="inlineStr">
+      <c r="GN3" t="inlineStr">
         <is>
           <t>0.4146240132945573</t>
         </is>
       </c>
-      <c r="GN3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GO3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GP3" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP3" t="inlineStr">
+      <c r="GQ3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GQ3" t="inlineStr">
+      <c r="GR3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR3" t="inlineStr">
+      <c r="GS3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -3827,219 +3842,219 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
           <t>2026-10-06 00:00:00</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>5.20</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>0.61</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>LV.1-9｜網通｜網通設備｜</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>3496</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>96.0</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>98.67</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>1.99</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>7.09</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>-1.32</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>-2.43</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>251.5</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>242.95</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>234.85</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>237.99</t>
         </is>
       </c>
-      <c r="CS4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>243.92</t>
         </is>
       </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
           <t>0.01698342094621919</t>
         </is>
       </c>
-      <c r="CV4" t="inlineStr">
+      <c r="CW4" t="inlineStr">
         <is>
           <t>0.0095574485767711</t>
         </is>
       </c>
-      <c r="CW4" t="inlineStr">
+      <c r="CX4" t="inlineStr">
         <is>
           <t>0.004383620228803675</t>
         </is>
       </c>
-      <c r="CX4" t="inlineStr">
+      <c r="CY4" t="inlineStr">
         <is>
           <t>0.002231954855554719</t>
         </is>
       </c>
-      <c r="CY4" t="inlineStr">
+      <c r="CZ4" t="inlineStr">
         <is>
           <t>-0.0006913504378553981</t>
         </is>
       </c>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
           <t>523.86</t>
         </is>
       </c>
-      <c r="DB4" t="inlineStr">
+      <c r="DC4" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="DC4" t="inlineStr">
+      <c r="DD4" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="DD4" t="inlineStr">
+      <c r="DE4" t="inlineStr">
         <is>
           <t>20.71</t>
         </is>
       </c>
-      <c r="DE4" t="inlineStr">
+      <c r="DF4" t="inlineStr">
         <is>
           <t>-96.73</t>
         </is>
       </c>
-      <c r="DF4" t="inlineStr">
+      <c r="DG4" t="inlineStr">
         <is>
           <t>2026/09/22</t>
         </is>
       </c>
-      <c r="DG4" t="inlineStr">
+      <c r="DH4" t="inlineStr">
         <is>
           <t>5813412453.637681</t>
         </is>
       </c>
-      <c r="DH4" t="inlineStr">
+      <c r="DI4" t="inlineStr">
         <is>
           <t>894577536.0</t>
         </is>
       </c>
-      <c r="DI4" t="inlineStr">
+      <c r="DJ4" t="inlineStr">
         <is>
           <t>2336698170.6</t>
         </is>
       </c>
-      <c r="DJ4" t="inlineStr">
+      <c r="DK4" t="inlineStr">
         <is>
           <t>1509129406.2</t>
         </is>
       </c>
-      <c r="DK4" t="inlineStr">
+      <c r="DL4" t="inlineStr">
         <is>
           <t>1091599138.133333</t>
         </is>
       </c>
-      <c r="DL4" t="inlineStr">
+      <c r="DM4" t="inlineStr">
         <is>
           <t>1283709533.06</t>
         </is>
       </c>
-      <c r="DM4" t="inlineStr">
+      <c r="DN4" t="inlineStr">
         <is>
           <t>1834886292.1375</t>
         </is>
       </c>
-      <c r="DN4" t="inlineStr">
+      <c r="DO4" t="inlineStr">
         <is>
           <t>111926255.4605257</t>
         </is>
       </c>
-      <c r="DO4" t="inlineStr">
+      <c r="DP4" t="inlineStr">
         <is>
           <t>268432054.5474508</t>
         </is>
       </c>
-      <c r="DP4" t="inlineStr">
+      <c r="DQ4" t="inlineStr">
         <is>
           <t>894577536.0</t>
         </is>
       </c>
-      <c r="DQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR4" t="inlineStr">
         <is>
           <t>0</t>
@@ -4057,169 +4072,169 @@
       </c>
       <c r="DU4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
           <t>啟碁</t>
         </is>
       </c>
-      <c r="DV4" t="inlineStr">
+      <c r="DW4" t="inlineStr">
         <is>
           <t>啟碁</t>
         </is>
       </c>
-      <c r="DW4" t="inlineStr">
+      <c r="DX4" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="DX4" t="inlineStr">
+      <c r="DY4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY4" t="inlineStr">
+      <c r="DZ4" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="DZ4" t="inlineStr">
+      <c r="EA4" t="inlineStr">
         <is>
           <t>5.108921494159271</t>
         </is>
       </c>
-      <c r="EA4" t="inlineStr">
+      <c r="EB4" t="inlineStr">
         <is>
           <t>15.64526085950118</t>
         </is>
       </c>
-      <c r="EB4" t="inlineStr">
+      <c r="EC4" t="inlineStr">
         <is>
           <t>6.101014334309918</t>
         </is>
       </c>
-      <c r="EC4" t="inlineStr">
+      <c r="ED4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED4" t="inlineStr">
+      <c r="EE4" t="inlineStr">
         <is>
           <t>價跌量-</t>
         </is>
       </c>
-      <c r="EE4" t="inlineStr">
+      <c r="EF4" t="inlineStr">
         <is>
           <t>3.46</t>
         </is>
       </c>
-      <c r="EF4" t="inlineStr">
+      <c r="EG4" t="inlineStr">
         <is>
           <t>1.68</t>
         </is>
       </c>
-      <c r="EG4" t="inlineStr">
+      <c r="EH4" t="inlineStr">
         <is>
           <t>81.57</t>
         </is>
       </c>
-      <c r="EH4" t="inlineStr">
+      <c r="EI4" t="inlineStr">
         <is>
           <t>28.09</t>
         </is>
       </c>
-      <c r="EI4" t="inlineStr">
+      <c r="EJ4" t="inlineStr">
         <is>
           <t>13.00%</t>
         </is>
       </c>
-      <c r="EJ4" t="inlineStr">
+      <c r="EK4" t="inlineStr">
         <is>
           <t>5.25%</t>
         </is>
       </c>
-      <c r="EK4" t="inlineStr">
+      <c r="EL4" t="inlineStr">
         <is>
           <t>84.4</t>
         </is>
       </c>
-      <c r="EL4" t="inlineStr">
+      <c r="EM4" t="inlineStr">
         <is>
           <t>124003</t>
         </is>
       </c>
-      <c r="EM4" t="inlineStr">
+      <c r="EN4" t="inlineStr">
         <is>
           <t>無線通訊產品96.85%、其他3.15% (2025年)</t>
         </is>
       </c>
-      <c r="EN4" t="inlineStr">
+      <c r="EO4" t="inlineStr">
         <is>
           <t>啟碁-通信網路業-上市</t>
         </is>
       </c>
-      <c r="EO4" t="inlineStr">
+      <c r="EP4" t="inlineStr">
         <is>
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="EP4" t="inlineStr">
+      <c r="EQ4" t="inlineStr">
         <is>
           <t>253.0</t>
         </is>
       </c>
-      <c r="EQ4" t="inlineStr">
+      <c r="ER4" t="inlineStr">
         <is>
           <t>259.0</t>
         </is>
       </c>
-      <c r="ER4" t="inlineStr">
+      <c r="ES4" t="inlineStr">
         <is>
           <t>252.5</t>
         </is>
       </c>
-      <c r="ES4" t="inlineStr">
+      <c r="ET4" t="inlineStr">
         <is>
           <t>256.5</t>
         </is>
       </c>
-      <c r="ET4" t="inlineStr">
+      <c r="EU4" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="EU4" t="inlineStr">
+      <c r="EV4" t="inlineStr">
         <is>
           <t>74.05</t>
         </is>
       </c>
-      <c r="EV4" t="inlineStr">
+      <c r="EW4" t="inlineStr">
         <is>
           <t>** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 天線/射頻基頻</t>
         </is>
       </c>
-      <c r="EW4" t="inlineStr">
+      <c r="EX4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="EX4" t="inlineStr">
+      <c r="EY4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="EY4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FA4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB4" t="inlineStr">
         <is>
           <t>0</t>
@@ -4227,210 +4242,215 @@
       </c>
       <c r="FC4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FD4" t="inlineStr">
+      <c r="FE4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE4" t="inlineStr">
+      <c r="FF4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="FF4" t="inlineStr">
+      <c r="FG4" t="inlineStr">
         <is>
           <t>2.140619288684876</t>
         </is>
       </c>
-      <c r="FG4" t="inlineStr">
+      <c r="FH4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FH4" t="inlineStr">
+      <c r="FI4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FI4" t="inlineStr">
+      <c r="FJ4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="FJ4" t="inlineStr">
+      <c r="FK4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FK4" t="inlineStr">
+      <c r="FL4" t="inlineStr">
         <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL4" t="inlineStr">
+      <c r="FM4" t="inlineStr">
         <is>
           <t>39438.0</t>
         </is>
       </c>
-      <c r="FM4" t="inlineStr">
+      <c r="FN4" t="inlineStr">
         <is>
           <t>34311.0</t>
         </is>
       </c>
-      <c r="FN4" t="inlineStr">
+      <c r="FO4" t="inlineStr">
         <is>
           <t>5127.0</t>
         </is>
       </c>
-      <c r="FO4" t="inlineStr">
+      <c r="FP4" t="inlineStr">
         <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="FP4" t="inlineStr">
+      <c r="FQ4" t="inlineStr">
         <is>
           <t>2069.0</t>
         </is>
       </c>
-      <c r="FQ4" t="inlineStr">
+      <c r="FR4" t="inlineStr">
         <is>
           <t>5.25%</t>
         </is>
       </c>
-      <c r="FR4" t="inlineStr">
+      <c r="FS4" t="inlineStr">
         <is>
           <t>-43.0</t>
         </is>
       </c>
-      <c r="FS4" t="inlineStr">
+      <c r="FT4" t="inlineStr">
         <is>
           <t>2027.0</t>
         </is>
       </c>
-      <c r="FT4" t="inlineStr">
+      <c r="FU4" t="inlineStr">
         <is>
           <t>1630.0</t>
         </is>
       </c>
-      <c r="FU4" t="inlineStr">
+      <c r="FV4" t="inlineStr">
         <is>
           <t>3.39</t>
         </is>
       </c>
-      <c r="FV4" t="inlineStr">
+      <c r="FW4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW4" t="inlineStr">
+      <c r="FX4" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX4" t="inlineStr">
+      <c r="FY4" t="inlineStr">
         <is>
           <t>1.92375</t>
         </is>
       </c>
-      <c r="FY4" t="inlineStr">
+      <c r="FZ4" t="inlineStr">
         <is>
           <t>12.61875</t>
         </is>
       </c>
-      <c r="FZ4" t="inlineStr">
+      <c r="GA4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA4" t="inlineStr">
+      <c r="GB4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB4" t="inlineStr">
+      <c r="GC4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE4" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG4" t="inlineStr">
+        <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="GG4" t="inlineStr">
+      <c r="GH4" t="inlineStr">
         <is>
           <t>0.4364406779661019</t>
         </is>
       </c>
-      <c r="GH4" t="inlineStr">
+      <c r="GI4" t="inlineStr">
         <is>
           <t>-0.7599999999999998</t>
         </is>
       </c>
-      <c r="GI4" t="inlineStr">
+      <c r="GJ4" t="inlineStr">
         <is>
           <t>-0.05523255813953487</t>
         </is>
       </c>
-      <c r="GJ4" t="inlineStr">
+      <c r="GK4" t="inlineStr">
         <is>
           <t>2.36</t>
         </is>
       </c>
-      <c r="GK4" t="inlineStr">
+      <c r="GL4" t="inlineStr">
         <is>
           <t>2.29126213592233</t>
         </is>
       </c>
-      <c r="GL4" t="inlineStr">
+      <c r="GM4" t="inlineStr">
         <is>
           <t>1.449999999999999</t>
         </is>
       </c>
-      <c r="GM4" t="inlineStr">
+      <c r="GN4" t="inlineStr">
         <is>
           <t>0.1255411255411254</t>
         </is>
       </c>
-      <c r="GN4" t="inlineStr">
+      <c r="GO4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO4" t="inlineStr">
+      <c r="GP4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GR4" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR4" t="inlineStr">
+      <c r="GS4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -4829,399 +4849,399 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
           <t>2026-09-21 00:00:00</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>43.16</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>5.41</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>LV.1-5｜封裝測試｜AI測試（前段）｜</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>1,610</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>52164</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>61.76</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>37.17</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>2.08</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>3.74</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>9.26</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>-5.66</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>298.3</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>299.15</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>287.55</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>263.18</t>
         </is>
       </c>
-      <c r="CS5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>278.96</t>
         </is>
       </c>
-      <c r="CT5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
           <t>0.005731625084288483</t>
         </is>
       </c>
-      <c r="CV5" t="inlineStr">
+      <c r="CW5" t="inlineStr">
         <is>
           <t>-0.004161118508655082</t>
         </is>
       </c>
-      <c r="CW5" t="inlineStr">
+      <c r="CX5" t="inlineStr">
         <is>
           <t>0.006299212598425141</t>
         </is>
       </c>
-      <c r="CX5" t="inlineStr">
+      <c r="CY5" t="inlineStr">
         <is>
           <t>0.005232802413964288</t>
         </is>
       </c>
-      <c r="CY5" t="inlineStr">
+      <c r="CZ5" t="inlineStr">
         <is>
           <t>0.001009240154301594</t>
         </is>
       </c>
-      <c r="CZ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
           <t>1.64</t>
         </is>
       </c>
-      <c r="DB5" t="inlineStr">
+      <c r="DC5" t="inlineStr">
         <is>
           <t>9.91</t>
         </is>
       </c>
-      <c r="DC5" t="inlineStr">
+      <c r="DD5" t="inlineStr">
         <is>
           <t>9.75</t>
         </is>
       </c>
-      <c r="DD5" t="inlineStr">
+      <c r="DE5" t="inlineStr">
         <is>
           <t>14.5</t>
         </is>
       </c>
-      <c r="DE5" t="inlineStr">
+      <c r="DF5" t="inlineStr">
         <is>
           <t>-32.81</t>
         </is>
       </c>
-      <c r="DF5" t="inlineStr">
+      <c r="DG5" t="inlineStr">
         <is>
           <t>2026/08/10</t>
         </is>
       </c>
-      <c r="DG5" t="inlineStr">
+      <c r="DH5" t="inlineStr">
         <is>
           <t>12286345563.71739</t>
         </is>
       </c>
-      <c r="DH5" t="inlineStr">
+      <c r="DI5" t="inlineStr">
         <is>
           <t>15426131196.0</t>
         </is>
       </c>
-      <c r="DI5" t="inlineStr">
+      <c r="DJ5" t="inlineStr">
         <is>
           <t>7846187787.6</t>
         </is>
       </c>
-      <c r="DJ5" t="inlineStr">
+      <c r="DK5" t="inlineStr">
         <is>
           <t>7965591680.6</t>
         </is>
       </c>
-      <c r="DK5" t="inlineStr">
+      <c r="DL5" t="inlineStr">
         <is>
           <t>7908518481.933333</t>
         </is>
       </c>
-      <c r="DL5" t="inlineStr">
+      <c r="DM5" t="inlineStr">
         <is>
           <t>6638975137.38</t>
         </is>
       </c>
-      <c r="DM5" t="inlineStr">
+      <c r="DN5" t="inlineStr">
         <is>
           <t>7953036982.9375</t>
         </is>
       </c>
-      <c r="DN5" t="inlineStr">
+      <c r="DO5" t="inlineStr">
         <is>
           <t>228932223.802081</t>
         </is>
       </c>
-      <c r="DO5" t="inlineStr">
+      <c r="DP5" t="inlineStr">
         <is>
           <t>353671516.2094469</t>
         </is>
       </c>
-      <c r="DP5" t="inlineStr">
+      <c r="DQ5" t="inlineStr">
         <is>
           <t>15426131196.0</t>
         </is>
       </c>
-      <c r="DQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
           <t>291.5</t>
         </is>
       </c>
-      <c r="DS5" t="inlineStr">
+      <c r="DT5" t="inlineStr">
         <is>
           <t>2026/09/18</t>
         </is>
       </c>
-      <c r="DT5" t="inlineStr">
+      <c r="DU5" t="inlineStr">
         <is>
           <t>4.46</t>
         </is>
       </c>
-      <c r="DU5" t="inlineStr">
+      <c r="DV5" t="inlineStr">
         <is>
           <t>京元電子</t>
         </is>
       </c>
-      <c r="DV5" t="inlineStr">
+      <c r="DW5" t="inlineStr">
         <is>
           <t>京元電子</t>
         </is>
       </c>
-      <c r="DW5" t="inlineStr">
+      <c r="DX5" t="inlineStr">
         <is>
           <t>半導體業</t>
         </is>
       </c>
-      <c r="DX5" t="inlineStr">
+      <c r="DY5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY5" t="inlineStr">
+      <c r="DZ5" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="DZ5" t="inlineStr">
+      <c r="EA5" t="inlineStr">
         <is>
           <t>4.034160173480228</t>
         </is>
       </c>
-      <c r="EA5" t="inlineStr">
+      <c r="EB5" t="inlineStr">
         <is>
           <t>34.55584561992811</t>
         </is>
       </c>
-      <c r="EB5" t="inlineStr">
+      <c r="EC5" t="inlineStr">
         <is>
           <t>38.00751452276898</t>
         </is>
       </c>
-      <c r="EC5" t="inlineStr">
+      <c r="ED5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
-      <c r="ED5" t="inlineStr">
+      <c r="EE5" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="EE5" t="inlineStr">
+      <c r="EF5" t="inlineStr">
         <is>
           <t>5.94</t>
         </is>
       </c>
-      <c r="EF5" t="inlineStr">
+      <c r="EG5" t="inlineStr">
         <is>
           <t>0.49</t>
         </is>
       </c>
-      <c r="EG5" t="inlineStr">
+      <c r="EH5" t="inlineStr">
         <is>
           <t>8.68</t>
         </is>
       </c>
-      <c r="EH5" t="inlineStr">
+      <c r="EI5" t="inlineStr">
         <is>
           <t>39.91</t>
         </is>
       </c>
-      <c r="EI5" t="inlineStr">
+      <c r="EJ5" t="inlineStr">
         <is>
           <t>39.49%</t>
         </is>
       </c>
-      <c r="EJ5" t="inlineStr">
+      <c r="EK5" t="inlineStr">
         <is>
           <t>25.38%</t>
         </is>
       </c>
-      <c r="EK5" t="inlineStr">
+      <c r="EL5" t="inlineStr">
         <is>
           <t>54.58</t>
         </is>
       </c>
-      <c r="EL5" t="inlineStr">
+      <c r="EM5" t="inlineStr">
         <is>
           <t>390942</t>
         </is>
       </c>
-      <c r="EM5" t="inlineStr">
+      <c r="EN5" t="inlineStr">
         <is>
           <t>積體電路(IC)測試66.43%、晶圓測試30.56%、其他3.01% (2025年)</t>
         </is>
       </c>
-      <c r="EN5" t="inlineStr">
+      <c r="EO5" t="inlineStr">
         <is>
           <t>京元電子-半導體業-上市</t>
         </is>
       </c>
-      <c r="EO5" t="inlineStr">
+      <c r="EP5" t="inlineStr">
         <is>
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="EP5" t="inlineStr">
+      <c r="EQ5" t="inlineStr">
         <is>
           <t>295.5</t>
         </is>
       </c>
-      <c r="EQ5" t="inlineStr">
+      <c r="ER5" t="inlineStr">
         <is>
           <t>310.0</t>
         </is>
       </c>
-      <c r="ER5" t="inlineStr">
+      <c r="ES5" t="inlineStr">
         <is>
           <t>284.0</t>
         </is>
       </c>
-      <c r="ES5" t="inlineStr">
+      <c r="ET5" t="inlineStr">
         <is>
           <t>304.5</t>
         </is>
       </c>
-      <c r="ET5" t="inlineStr">
+      <c r="EU5" t="inlineStr">
         <is>
           <t>203.5</t>
         </is>
       </c>
-      <c r="EU5" t="inlineStr">
+      <c r="EV5" t="inlineStr">
         <is>
           <t>51.25</t>
         </is>
       </c>
-      <c r="EV5" t="inlineStr">
+      <c r="EW5" t="inlineStr">
         <is>
           <t>** 半導體 - IC封裝測試</t>
         </is>
       </c>
-      <c r="EW5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EZ5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ5" t="inlineStr">
+      <c r="FA5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="FA5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB5" t="inlineStr">
         <is>
           <t>0</t>
@@ -5234,29 +5254,29 @@
       </c>
       <c r="FD5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FE5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE5" t="inlineStr">
+      <c r="FF5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="FF5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="FH5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FI5" t="inlineStr">
         <is>
           <t>0</t>
@@ -5269,94 +5289,94 @@
       </c>
       <c r="FK5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL5" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL5" t="inlineStr">
+      <c r="FM5" t="inlineStr">
         <is>
           <t>11142.0</t>
         </is>
       </c>
-      <c r="FM5" t="inlineStr">
+      <c r="FN5" t="inlineStr">
         <is>
           <t>6741.0</t>
         </is>
       </c>
-      <c r="FN5" t="inlineStr">
+      <c r="FO5" t="inlineStr">
         <is>
           <t>4400.0</t>
         </is>
       </c>
-      <c r="FO5" t="inlineStr">
+      <c r="FP5" t="inlineStr">
         <is>
           <t>39.49</t>
         </is>
       </c>
-      <c r="FP5" t="inlineStr">
+      <c r="FQ5" t="inlineStr">
         <is>
           <t>2828.0</t>
         </is>
       </c>
-      <c r="FQ5" t="inlineStr">
+      <c r="FR5" t="inlineStr">
         <is>
           <t>25.38%</t>
         </is>
       </c>
-      <c r="FR5" t="inlineStr">
+      <c r="FS5" t="inlineStr">
         <is>
           <t>248.0</t>
         </is>
       </c>
-      <c r="FS5" t="inlineStr">
+      <c r="FT5" t="inlineStr">
         <is>
           <t>3076.0</t>
         </is>
       </c>
-      <c r="FT5" t="inlineStr">
+      <c r="FU5" t="inlineStr">
         <is>
           <t>2492.0</t>
         </is>
       </c>
-      <c r="FU5" t="inlineStr">
+      <c r="FV5" t="inlineStr">
         <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="FV5" t="inlineStr">
+      <c r="FW5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW5" t="inlineStr">
+      <c r="FX5" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX5" t="inlineStr">
+      <c r="FY5" t="inlineStr">
         <is>
           <t>2.07625</t>
         </is>
       </c>
-      <c r="FY5" t="inlineStr">
+      <c r="FZ5" t="inlineStr">
         <is>
           <t>36.5775</t>
         </is>
       </c>
-      <c r="FZ5" t="inlineStr">
+      <c r="GA5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA5" t="inlineStr">
+      <c r="GB5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GC5" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5364,75 +5384,80 @@
       </c>
       <c r="GD5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE5" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG5" t="inlineStr">
+        <is>
           <t>0.1699999999999999</t>
         </is>
       </c>
-      <c r="GG5" t="inlineStr">
+      <c r="GH5" t="inlineStr">
         <is>
           <t>0.09090909090909083</t>
         </is>
       </c>
-      <c r="GH5" t="inlineStr">
+      <c r="GI5" t="inlineStr">
         <is>
           <t>-0.25</t>
         </is>
       </c>
-      <c r="GI5" t="inlineStr">
+      <c r="GJ5" t="inlineStr">
         <is>
           <t>-0.006290890790135895</t>
         </is>
       </c>
-      <c r="GJ5" t="inlineStr">
+      <c r="GK5" t="inlineStr">
         <is>
           <t>0.26</t>
         </is>
       </c>
-      <c r="GK5" t="inlineStr">
+      <c r="GL5" t="inlineStr">
         <is>
           <t>0.146067415730337</t>
         </is>
       </c>
-      <c r="GL5" t="inlineStr">
+      <c r="GM5" t="inlineStr">
         <is>
           <t>3.950000000000003</t>
         </is>
       </c>
-      <c r="GM5" t="inlineStr">
+      <c r="GN5" t="inlineStr">
         <is>
           <t>0.1111423747889702</t>
         </is>
       </c>
-      <c r="GN5" t="inlineStr">
+      <c r="GO5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO5" t="inlineStr">
+      <c r="GP5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GR5" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR5" t="inlineStr">
+      <c r="GS5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -5831,414 +5856,414 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
           <t>2026-07-20 00:00:00</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>22.09</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>-0.98</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>LV.1-3｜AI晶片｜晶圓代工（先進）｜</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>2,911</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>23145</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>68.18</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>89.39</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>-0.35</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>3.33</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>0.22</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>2559.0</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>2523.5</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>2476.5</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>2422.1</t>
         </is>
       </c>
-      <c r="CS6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>2416.81</t>
         </is>
       </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
           <t>0.003136025088200656</t>
         </is>
       </c>
-      <c r="CV6" t="inlineStr">
+      <c r="CW6" t="inlineStr">
         <is>
           <t>0.003579240405647166</t>
         </is>
       </c>
-      <c r="CW6" t="inlineStr">
+      <c r="CX6" t="inlineStr">
         <is>
           <t>0.001617795753286133</t>
         </is>
       </c>
-      <c r="CX6" t="inlineStr">
+      <c r="CY6" t="inlineStr">
         <is>
           <t>0.002234451938593951</t>
         </is>
       </c>
-      <c r="CY6" t="inlineStr">
+      <c r="CZ6" t="inlineStr">
         <is>
           <t>0.00124284715569245</t>
         </is>
       </c>
-      <c r="CZ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
           <t>33.06</t>
         </is>
       </c>
-      <c r="DB6" t="inlineStr">
+      <c r="DC6" t="inlineStr">
         <is>
           <t>40.7</t>
         </is>
       </c>
-      <c r="DC6" t="inlineStr">
+      <c r="DD6" t="inlineStr">
         <is>
           <t>30.59</t>
         </is>
       </c>
-      <c r="DD6" t="inlineStr">
+      <c r="DE6" t="inlineStr">
         <is>
           <t>87.33</t>
         </is>
       </c>
-      <c r="DE6" t="inlineStr">
+      <c r="DF6" t="inlineStr">
         <is>
           <t>-64.97</t>
         </is>
       </c>
-      <c r="DF6" t="inlineStr">
+      <c r="DG6" t="inlineStr">
         <is>
           <t>2026/09/21</t>
         </is>
       </c>
-      <c r="DG6" t="inlineStr">
+      <c r="DH6" t="inlineStr">
         <is>
           <t>113935051174.2754</t>
         </is>
       </c>
-      <c r="DH6" t="inlineStr">
+      <c r="DI6" t="inlineStr">
         <is>
           <t>59167379273.0</t>
         </is>
       </c>
-      <c r="DI6" t="inlineStr">
+      <c r="DJ6" t="inlineStr">
         <is>
           <t>52951487087.0</t>
         </is>
       </c>
-      <c r="DJ6" t="inlineStr">
+      <c r="DK6" t="inlineStr">
         <is>
           <t>56150824885.2</t>
         </is>
       </c>
-      <c r="DK6" t="inlineStr">
+      <c r="DL6" t="inlineStr">
         <is>
           <t>54438114953.06667</t>
         </is>
       </c>
-      <c r="DL6" t="inlineStr">
+      <c r="DM6" t="inlineStr">
         <is>
           <t>59849452930.32</t>
         </is>
       </c>
-      <c r="DM6" t="inlineStr">
+      <c r="DN6" t="inlineStr">
         <is>
           <t>73081087977.6</t>
         </is>
       </c>
-      <c r="DN6" t="inlineStr">
+      <c r="DO6" t="inlineStr">
         <is>
           <t>261003774.1358927</t>
         </is>
       </c>
-      <c r="DO6" t="inlineStr">
+      <c r="DP6" t="inlineStr">
         <is>
           <t>-30081162.67330933</t>
         </is>
       </c>
-      <c r="DP6" t="inlineStr">
+      <c r="DQ6" t="inlineStr">
         <is>
           <t>59167379273.0</t>
         </is>
       </c>
-      <c r="DQ6" t="inlineStr">
+      <c r="DR6" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="DR6" t="inlineStr">
+      <c r="DS6" t="inlineStr">
         <is>
           <t>2440.0</t>
         </is>
       </c>
-      <c r="DS6" t="inlineStr">
+      <c r="DT6" t="inlineStr">
         <is>
           <t>2026/09/01</t>
         </is>
       </c>
-      <c r="DT6" t="inlineStr">
+      <c r="DU6" t="inlineStr">
         <is>
           <t>4.51</t>
         </is>
       </c>
-      <c r="DU6" t="inlineStr">
+      <c r="DV6" t="inlineStr">
         <is>
           <t>台積電</t>
         </is>
       </c>
-      <c r="DV6" t="inlineStr">
+      <c r="DW6" t="inlineStr">
         <is>
           <t>台積電</t>
         </is>
       </c>
-      <c r="DW6" t="inlineStr">
+      <c r="DX6" t="inlineStr">
         <is>
           <t>半導體業</t>
         </is>
       </c>
-      <c r="DX6" t="inlineStr">
+      <c r="DY6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY6" t="inlineStr">
+      <c r="DZ6" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="DZ6" t="inlineStr">
+      <c r="EA6" t="inlineStr">
         <is>
           <t>-1.075787644781405</t>
         </is>
       </c>
-      <c r="EA6" t="inlineStr">
+      <c r="EB6" t="inlineStr">
         <is>
           <t>17.49541246663658</t>
         </is>
       </c>
-      <c r="EB6" t="inlineStr">
+      <c r="EC6" t="inlineStr">
         <is>
           <t>29.94631425482932</t>
         </is>
       </c>
-      <c r="EC6" t="inlineStr">
+      <c r="ED6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED6" t="inlineStr">
+      <c r="EE6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE6" t="inlineStr">
+      <c r="EF6" t="inlineStr">
         <is>
           <t>10.28</t>
         </is>
       </c>
-      <c r="EF6" t="inlineStr">
+      <c r="EG6" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="EG6" t="inlineStr">
+      <c r="EH6" t="inlineStr">
         <is>
           <t>48.99</t>
         </is>
       </c>
-      <c r="EH6" t="inlineStr">
+      <c r="EI6" t="inlineStr">
         <is>
           <t>29.56</t>
         </is>
       </c>
-      <c r="EI6" t="inlineStr">
+      <c r="EJ6" t="inlineStr">
         <is>
           <t>67.72%</t>
         </is>
       </c>
-      <c r="EJ6" t="inlineStr">
+      <c r="EK6" t="inlineStr">
         <is>
           <t>60.34%</t>
         </is>
       </c>
-      <c r="EK6" t="inlineStr">
+      <c r="EL6" t="inlineStr">
         <is>
           <t>54.58</t>
         </is>
       </c>
-      <c r="EL6" t="inlineStr">
+      <c r="EM6" t="inlineStr">
         <is>
           <t>66127544</t>
         </is>
       </c>
-      <c r="EM6" t="inlineStr">
+      <c r="EN6" t="inlineStr">
         <is>
           <t>晶圓-5奈米30.98%、晶圓-3奈米20.85%、其他14.08%、晶圓-7奈米12.06%、晶圓-28奈米5.91%、晶圓-16奈米5.66%、晶圓-65奈米3.16%、晶圓-40及45奈米2.51%、晶圓-0.15及0.18微米2.32%、晶圓-0.11及0.13微米1.28%、晶圓-90奈米0.56%、晶圓-0.25微米以上0.51%、晶圓-20奈米0.11% (2025年)</t>
         </is>
       </c>
-      <c r="EN6" t="inlineStr">
+      <c r="EO6" t="inlineStr">
         <is>
           <t>台積電-半導體業-上市</t>
         </is>
       </c>
-      <c r="EO6" t="inlineStr">
+      <c r="EP6" t="inlineStr">
         <is>
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="EP6" t="inlineStr">
+      <c r="EQ6" t="inlineStr">
         <is>
           <t>2550.0</t>
         </is>
       </c>
-      <c r="EQ6" t="inlineStr">
+      <c r="ER6" t="inlineStr">
         <is>
           <t>2575.0</t>
         </is>
       </c>
-      <c r="ER6" t="inlineStr">
+      <c r="ES6" t="inlineStr">
         <is>
           <t>2550.0</t>
         </is>
       </c>
-      <c r="ES6" t="inlineStr">
+      <c r="ET6" t="inlineStr">
         <is>
           <t>2550.0</t>
         </is>
       </c>
-      <c r="ET6" t="inlineStr">
+      <c r="EU6" t="inlineStr">
         <is>
           <t>1410.0</t>
         </is>
       </c>
-      <c r="EU6" t="inlineStr">
+      <c r="EV6" t="inlineStr">
         <is>
           <t>248.05</t>
         </is>
       </c>
-      <c r="EV6" t="inlineStr">
+      <c r="EW6" t="inlineStr">
         <is>
           <t>** 半導體 - 晶圓製造</t>
         </is>
       </c>
-      <c r="EW6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX6" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY6" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="EY6" t="inlineStr">
+      <c r="EZ6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ6" t="inlineStr">
+      <c r="FA6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="FA6" t="inlineStr">
+      <c r="FB6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FB6" t="inlineStr">
+      <c r="FC6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="FC6" t="inlineStr">
+      <c r="FD6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FE6" t="inlineStr">
         <is>
           <t>0</t>
@@ -6246,12 +6271,12 @@
       </c>
       <c r="FF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
@@ -6271,170 +6296,175 @@
       </c>
       <c r="FK6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL6" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL6" t="inlineStr">
+      <c r="FM6" t="inlineStr">
         <is>
           <t>1270380.0</t>
         </is>
       </c>
-      <c r="FM6" t="inlineStr">
+      <c r="FN6" t="inlineStr">
         <is>
           <t>410070.0</t>
         </is>
       </c>
-      <c r="FN6" t="inlineStr">
+      <c r="FO6" t="inlineStr">
         <is>
           <t>860311.0</t>
         </is>
       </c>
-      <c r="FO6" t="inlineStr">
+      <c r="FP6" t="inlineStr">
         <is>
           <t>67.72</t>
         </is>
       </c>
-      <c r="FP6" t="inlineStr">
+      <c r="FQ6" t="inlineStr">
         <is>
           <t>766603.0</t>
         </is>
       </c>
-      <c r="FQ6" t="inlineStr">
+      <c r="FR6" t="inlineStr">
         <is>
           <t>60.34%</t>
         </is>
       </c>
-      <c r="FR6" t="inlineStr">
+      <c r="FS6" t="inlineStr">
         <is>
           <t>95827.0</t>
         </is>
       </c>
-      <c r="FS6" t="inlineStr">
+      <c r="FT6" t="inlineStr">
         <is>
           <t>862430.0</t>
         </is>
       </c>
-      <c r="FT6" t="inlineStr">
+      <c r="FU6" t="inlineStr">
         <is>
           <t>706562.0</t>
         </is>
       </c>
-      <c r="FU6" t="inlineStr">
+      <c r="FV6" t="inlineStr">
         <is>
           <t>27.25</t>
         </is>
       </c>
-      <c r="FV6" t="inlineStr">
+      <c r="FW6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW6" t="inlineStr">
+      <c r="FX6" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX6" t="inlineStr">
+      <c r="FY6" t="inlineStr">
         <is>
           <t>17.82375</t>
         </is>
       </c>
-      <c r="FY6" t="inlineStr">
+      <c r="FZ6" t="inlineStr">
         <is>
           <t>61.24875</t>
         </is>
       </c>
-      <c r="FZ6" t="inlineStr">
+      <c r="GA6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA6" t="inlineStr">
+      <c r="GB6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB6" t="inlineStr">
+      <c r="GC6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC6" t="inlineStr">
+      <c r="GD6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GD6" t="inlineStr">
+      <c r="GE6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE6" t="inlineStr">
+      <c r="GF6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GF6" t="inlineStr">
+      <c r="GG6" t="inlineStr">
         <is>
           <t>5.170000000000002</t>
         </is>
       </c>
-      <c r="GG6" t="inlineStr">
+      <c r="GH6" t="inlineStr">
         <is>
           <t>0.2341485507246377</t>
         </is>
       </c>
-      <c r="GH6" t="inlineStr">
+      <c r="GI6" t="inlineStr">
         <is>
           <t>1.469999999999999</t>
         </is>
       </c>
-      <c r="GI6" t="inlineStr">
+      <c r="GJ6" t="inlineStr">
         <is>
           <t>0.02218867924528301</t>
         </is>
       </c>
-      <c r="GJ6" t="inlineStr">
+      <c r="GK6" t="inlineStr">
         <is>
           <t>11.89</t>
         </is>
       </c>
-      <c r="GK6" t="inlineStr">
+      <c r="GL6" t="inlineStr">
         <is>
           <t>0.7740885416666667</t>
         </is>
       </c>
-      <c r="GL6" t="inlineStr">
+      <c r="GM6" t="inlineStr">
         <is>
           <t>9.100000000000001</t>
         </is>
       </c>
-      <c r="GM6" t="inlineStr">
+      <c r="GN6" t="inlineStr">
         <is>
           <t>0.1552371204367111</t>
         </is>
       </c>
-      <c r="GN6" t="inlineStr">
+      <c r="GO6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO6" t="inlineStr">
+      <c r="GP6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP6" t="inlineStr">
+      <c r="GQ6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GQ6" t="inlineStr">
+      <c r="GR6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR6" t="inlineStr">
+      <c r="GS6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -6833,399 +6863,399 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
           <t>2026-09-04 00:00:00</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>12.84</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>-1.02</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>LV.1-3｜AI晶片｜晶圓代工（成熟）｜成熟製程AI受惠</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>2,161</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>83054</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="CJ7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
           <t>2.38</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>-2.64</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>12.54</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>-5.02</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>151.5</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>154.1</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>150.45</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>133.68</t>
         </is>
       </c>
-      <c r="CS7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>140.75</t>
         </is>
       </c>
-      <c r="CT7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
           <t>-0.01814646791963714</t>
         </is>
       </c>
-      <c r="CV7" t="inlineStr">
+      <c r="CW7" t="inlineStr">
         <is>
           <t>-0.008046346958480832</t>
         </is>
       </c>
-      <c r="CW7" t="inlineStr">
+      <c r="CX7" t="inlineStr">
         <is>
           <t>0.003501750875437581</t>
         </is>
       </c>
-      <c r="CX7" t="inlineStr">
+      <c r="CY7" t="inlineStr">
         <is>
           <t>0.005112781954887291</t>
         </is>
       </c>
-      <c r="CY7" t="inlineStr">
+      <c r="CZ7" t="inlineStr">
         <is>
           <t>0.001244887070958711</t>
         </is>
       </c>
-      <c r="CZ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
           <t>-24.69</t>
         </is>
       </c>
-      <c r="DB7" t="inlineStr">
+      <c r="DC7" t="inlineStr">
         <is>
           <t>4.65</t>
         </is>
       </c>
-      <c r="DC7" t="inlineStr">
+      <c r="DD7" t="inlineStr">
         <is>
           <t>6.18</t>
         </is>
       </c>
-      <c r="DD7" t="inlineStr">
+      <c r="DE7" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="DE7" t="inlineStr">
+      <c r="DF7" t="inlineStr">
         <is>
           <t>-58.81</t>
         </is>
       </c>
-      <c r="DF7" t="inlineStr">
+      <c r="DG7" t="inlineStr">
         <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="DG7" t="inlineStr">
+      <c r="DH7" t="inlineStr">
         <is>
           <t>30255835064.26087</t>
         </is>
       </c>
-      <c r="DH7" t="inlineStr">
+      <c r="DI7" t="inlineStr">
         <is>
           <t>12302705841.0</t>
         </is>
       </c>
-      <c r="DI7" t="inlineStr">
+      <c r="DJ7" t="inlineStr">
         <is>
           <t>29479277578.0</t>
         </is>
       </c>
-      <c r="DJ7" t="inlineStr">
+      <c r="DK7" t="inlineStr">
         <is>
           <t>24290813101.6</t>
         </is>
       </c>
-      <c r="DK7" t="inlineStr">
+      <c r="DL7" t="inlineStr">
         <is>
           <t>26550495475.36666</t>
         </is>
       </c>
-      <c r="DL7" t="inlineStr">
+      <c r="DM7" t="inlineStr">
         <is>
           <t>23668438226.34</t>
         </is>
       </c>
-      <c r="DM7" t="inlineStr">
+      <c r="DN7" t="inlineStr">
         <is>
           <t>26835087505.4375</t>
         </is>
       </c>
-      <c r="DN7" t="inlineStr">
+      <c r="DO7" t="inlineStr">
         <is>
           <t>468751968.9198247</t>
         </is>
       </c>
-      <c r="DO7" t="inlineStr">
+      <c r="DP7" t="inlineStr">
         <is>
           <t>-287080406.1218262</t>
         </is>
       </c>
-      <c r="DP7" t="inlineStr">
+      <c r="DQ7" t="inlineStr">
         <is>
           <t>12302705841.0</t>
         </is>
       </c>
-      <c r="DQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
           <t>142.0</t>
         </is>
       </c>
-      <c r="DS7" t="inlineStr">
+      <c r="DT7" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="DT7" t="inlineStr">
+      <c r="DU7" t="inlineStr">
         <is>
           <t>3.87</t>
         </is>
       </c>
-      <c r="DU7" t="inlineStr">
+      <c r="DV7" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="DV7" t="inlineStr">
+      <c r="DW7" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="DW7" t="inlineStr">
+      <c r="DX7" t="inlineStr">
         <is>
           <t>半導體業</t>
         </is>
       </c>
-      <c r="DX7" t="inlineStr">
+      <c r="DY7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY7" t="inlineStr">
+      <c r="DZ7" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="DZ7" t="inlineStr">
+      <c r="EA7" t="inlineStr">
         <is>
           <t>8.801074917287652</t>
         </is>
       </c>
-      <c r="EA7" t="inlineStr">
+      <c r="EB7" t="inlineStr">
         <is>
           <t>10.80159260564775</t>
         </is>
       </c>
-      <c r="EB7" t="inlineStr">
+      <c r="EC7" t="inlineStr">
         <is>
           <t>6.880500672891759</t>
         </is>
       </c>
-      <c r="EC7" t="inlineStr">
+      <c r="ED7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED7" t="inlineStr">
+      <c r="EE7" t="inlineStr">
         <is>
           <t>價漲量縮</t>
         </is>
       </c>
-      <c r="EE7" t="inlineStr">
+      <c r="EF7" t="inlineStr">
         <is>
           <t>4.17</t>
         </is>
       </c>
-      <c r="EF7" t="inlineStr">
+      <c r="EG7" t="inlineStr">
         <is>
           <t>1.77</t>
         </is>
       </c>
-      <c r="EG7" t="inlineStr">
+      <c r="EH7" t="inlineStr">
         <is>
           <t>5.48</t>
         </is>
       </c>
-      <c r="EH7" t="inlineStr">
+      <c r="EI7" t="inlineStr">
         <is>
           <t>22.18</t>
         </is>
       </c>
-      <c r="EI7" t="inlineStr">
+      <c r="EJ7" t="inlineStr">
         <is>
           <t>32.48%</t>
         </is>
       </c>
-      <c r="EJ7" t="inlineStr">
+      <c r="EK7" t="inlineStr">
         <is>
           <t>21.75%</t>
         </is>
       </c>
-      <c r="EK7" t="inlineStr">
+      <c r="EL7" t="inlineStr">
         <is>
           <t>54.58</t>
         </is>
       </c>
-      <c r="EL7" t="inlineStr">
+      <c r="EM7" t="inlineStr">
         <is>
           <t>1854089</t>
         </is>
       </c>
-      <c r="EM7" t="inlineStr">
+      <c r="EN7" t="inlineStr">
         <is>
           <t>晶圓95.81%、其他4.19% (2025年)</t>
         </is>
       </c>
-      <c r="EN7" t="inlineStr">
+      <c r="EO7" t="inlineStr">
         <is>
           <t>聯電-半導體業-上市</t>
         </is>
       </c>
-      <c r="EO7" t="inlineStr">
+      <c r="EP7" t="inlineStr">
         <is>
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="EP7" t="inlineStr">
+      <c r="EQ7" t="inlineStr">
         <is>
           <t>147.5</t>
         </is>
       </c>
-      <c r="EQ7" t="inlineStr">
+      <c r="ER7" t="inlineStr">
         <is>
           <t>149.5</t>
         </is>
       </c>
-      <c r="ER7" t="inlineStr">
+      <c r="ES7" t="inlineStr">
         <is>
           <t>147.0</t>
         </is>
       </c>
-      <c r="ES7" t="inlineStr">
+      <c r="ET7" t="inlineStr">
         <is>
           <t>147.5</t>
         </is>
       </c>
-      <c r="ET7" t="inlineStr">
+      <c r="EU7" t="inlineStr">
         <is>
           <t>46.5</t>
         </is>
       </c>
-      <c r="EU7" t="inlineStr">
+      <c r="EV7" t="inlineStr">
         <is>
           <t>35.38</t>
         </is>
       </c>
-      <c r="EV7" t="inlineStr">
+      <c r="EW7" t="inlineStr">
         <is>
           <t>** 半導體 - 晶圓製造</t>
         </is>
       </c>
-      <c r="EW7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX7" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="EY7" t="inlineStr">
+      <c r="EZ7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ7" t="inlineStr">
+      <c r="FA7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FA7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB7" t="inlineStr">
         <is>
           <t>0</t>
@@ -7248,19 +7278,19 @@
       </c>
       <c r="FF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="FH7" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="FH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FI7" t="inlineStr">
         <is>
           <t>0</t>
@@ -7273,170 +7303,175 @@
       </c>
       <c r="FK7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL7" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL7" t="inlineStr">
+      <c r="FM7" t="inlineStr">
         <is>
           <t>68733.0</t>
         </is>
       </c>
-      <c r="FM7" t="inlineStr">
+      <c r="FN7" t="inlineStr">
         <is>
           <t>46410.0</t>
         </is>
       </c>
-      <c r="FN7" t="inlineStr">
+      <c r="FO7" t="inlineStr">
         <is>
           <t>22323.0</t>
         </is>
       </c>
-      <c r="FO7" t="inlineStr">
+      <c r="FP7" t="inlineStr">
         <is>
           <t>32.48</t>
         </is>
       </c>
-      <c r="FP7" t="inlineStr">
+      <c r="FQ7" t="inlineStr">
         <is>
           <t>14950.0</t>
         </is>
       </c>
-      <c r="FQ7" t="inlineStr">
+      <c r="FR7" t="inlineStr">
         <is>
           <t>21.75%</t>
         </is>
       </c>
-      <c r="FR7" t="inlineStr">
+      <c r="FS7" t="inlineStr">
         <is>
           <t>30236.0</t>
         </is>
       </c>
-      <c r="FS7" t="inlineStr">
+      <c r="FT7" t="inlineStr">
         <is>
           <t>45186.0</t>
         </is>
       </c>
-      <c r="FT7" t="inlineStr">
+      <c r="FU7" t="inlineStr">
         <is>
           <t>42260.0</t>
         </is>
       </c>
-      <c r="FU7" t="inlineStr">
+      <c r="FV7" t="inlineStr">
         <is>
           <t>3.39</t>
         </is>
       </c>
-      <c r="FV7" t="inlineStr">
+      <c r="FW7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW7" t="inlineStr">
+      <c r="FX7" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX7" t="inlineStr">
+      <c r="FY7" t="inlineStr">
         <is>
           <t>1.2325</t>
         </is>
       </c>
-      <c r="FY7" t="inlineStr">
+      <c r="FZ7" t="inlineStr">
         <is>
           <t>30.21625</t>
         </is>
       </c>
-      <c r="FZ7" t="inlineStr">
+      <c r="GA7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA7" t="inlineStr">
+      <c r="GB7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB7" t="inlineStr">
+      <c r="GC7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE7" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG7" t="inlineStr">
+        <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="GG7" t="inlineStr">
+      <c r="GH7" t="inlineStr">
         <is>
           <t>1.627906976744186</t>
         </is>
       </c>
-      <c r="GH7" t="inlineStr">
+      <c r="GI7" t="inlineStr">
         <is>
           <t>3.289999999999996</t>
         </is>
       </c>
-      <c r="GI7" t="inlineStr">
+      <c r="GJ7" t="inlineStr">
         <is>
           <t>0.1127098321342923</t>
         </is>
       </c>
-      <c r="GJ7" t="inlineStr">
+      <c r="GK7" t="inlineStr">
         <is>
           <t>2.68</t>
         </is>
       </c>
-      <c r="GK7" t="inlineStr">
+      <c r="GL7" t="inlineStr">
         <is>
           <t>3.774647887323944</t>
         </is>
       </c>
-      <c r="GL7" t="inlineStr">
+      <c r="GM7" t="inlineStr">
         <is>
           <t>3.759999999999998</t>
         </is>
       </c>
-      <c r="GM7" t="inlineStr">
+      <c r="GN7" t="inlineStr">
         <is>
           <t>0.1309192200557103</t>
         </is>
       </c>
-      <c r="GN7" t="inlineStr">
+      <c r="GO7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO7" t="inlineStr">
+      <c r="GP7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP7" t="inlineStr">
+      <c r="GQ7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GQ7" t="inlineStr">
+      <c r="GR7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR7" t="inlineStr">
+      <c r="GS7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -7835,399 +7870,399 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
           <t>2026-09-09 00:00:00</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>7.46</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>NA｜居家生活｜居家/生活｜</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>60.0</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>-1.06</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>-2.72</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>-0.79</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>17.93</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>17.985</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>18.12</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>18.63</t>
         </is>
       </c>
-      <c r="CS8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>18.78</t>
         </is>
       </c>
-      <c r="CT8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CV8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
           <t>-0.0002779321845470806</t>
         </is>
       </c>
-      <c r="CW8" t="inlineStr">
+      <c r="CX8" t="inlineStr">
         <is>
           <t>-0.003573883161512081</t>
         </is>
       </c>
-      <c r="CX8" t="inlineStr">
+      <c r="CY8" t="inlineStr">
         <is>
           <t>-0.0004828585224528892</t>
         </is>
       </c>
-      <c r="CY8" t="inlineStr">
+      <c r="CZ8" t="inlineStr">
         <is>
           <t>-0.0007649328189437421</t>
         </is>
       </c>
-      <c r="CZ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="DB8" t="inlineStr">
+      <c r="DC8" t="inlineStr">
         <is>
           <t>-0.24</t>
         </is>
       </c>
-      <c r="DC8" t="inlineStr">
+      <c r="DD8" t="inlineStr">
         <is>
           <t>-0.24</t>
         </is>
       </c>
-      <c r="DD8" t="inlineStr">
+      <c r="DE8" t="inlineStr">
         <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="DE8" t="inlineStr">
+      <c r="DF8" t="inlineStr">
         <is>
           <t>-158.82</t>
         </is>
       </c>
-      <c r="DF8" t="inlineStr">
+      <c r="DG8" t="inlineStr">
         <is>
           <t>2026/10/08</t>
         </is>
       </c>
-      <c r="DG8" t="inlineStr">
+      <c r="DH8" t="inlineStr">
         <is>
           <t>9396003.601449275</t>
         </is>
       </c>
-      <c r="DH8" t="inlineStr">
+      <c r="DI8" t="inlineStr">
         <is>
           <t>3450592.0</t>
         </is>
       </c>
-      <c r="DI8" t="inlineStr">
+      <c r="DJ8" t="inlineStr">
         <is>
           <t>2440714.0</t>
         </is>
       </c>
-      <c r="DJ8" t="inlineStr">
+      <c r="DK8" t="inlineStr">
         <is>
           <t>2023209.7</t>
         </is>
       </c>
-      <c r="DK8" t="inlineStr">
+      <c r="DL8" t="inlineStr">
         <is>
           <t>3142711.533333333</t>
         </is>
       </c>
-      <c r="DL8" t="inlineStr">
+      <c r="DM8" t="inlineStr">
         <is>
           <t>3188222.26</t>
         </is>
       </c>
-      <c r="DM8" t="inlineStr">
+      <c r="DN8" t="inlineStr">
         <is>
           <t>3647072.1</t>
         </is>
       </c>
-      <c r="DN8" t="inlineStr">
+      <c r="DO8" t="inlineStr">
         <is>
           <t>-208146.619398799</t>
         </is>
       </c>
-      <c r="DO8" t="inlineStr">
+      <c r="DP8" t="inlineStr">
         <is>
           <t>-121237.3567116326</t>
         </is>
       </c>
-      <c r="DP8" t="inlineStr">
+      <c r="DQ8" t="inlineStr">
         <is>
           <t>3450592.0</t>
         </is>
       </c>
-      <c r="DQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
           <t>19.05</t>
         </is>
       </c>
-      <c r="DS8" t="inlineStr">
+      <c r="DT8" t="inlineStr">
         <is>
           <t>2026/09/02</t>
         </is>
       </c>
-      <c r="DT8" t="inlineStr">
+      <c r="DU8" t="inlineStr">
         <is>
           <t>-5.51</t>
         </is>
       </c>
-      <c r="DU8" t="inlineStr">
+      <c r="DV8" t="inlineStr">
         <is>
           <t>橋椿</t>
         </is>
       </c>
-      <c r="DV8" t="inlineStr">
+      <c r="DW8" t="inlineStr">
         <is>
           <t>橋椿</t>
         </is>
       </c>
-      <c r="DW8" t="inlineStr">
+      <c r="DX8" t="inlineStr">
         <is>
           <t>居家生活</t>
         </is>
       </c>
-      <c r="DX8" t="inlineStr">
+      <c r="DY8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY8" t="inlineStr">
+      <c r="DZ8" t="inlineStr">
         <is>
           <t>0.32</t>
         </is>
       </c>
-      <c r="DZ8" t="inlineStr">
+      <c r="EA8" t="inlineStr">
         <is>
           <t>-8.059489496969482</t>
         </is>
       </c>
-      <c r="EA8" t="inlineStr">
+      <c r="EB8" t="inlineStr">
         <is>
           <t>23.1771123011648</t>
         </is>
       </c>
-      <c r="EB8" t="inlineStr">
+      <c r="EC8" t="inlineStr">
         <is>
           <t>10.98087113345613</t>
         </is>
       </c>
-      <c r="EC8" t="inlineStr">
+      <c r="ED8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
-      <c r="ED8" t="inlineStr">
+      <c r="EE8" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="EE8" t="inlineStr">
+      <c r="EF8" t="inlineStr">
         <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="EF8" t="inlineStr">
+      <c r="EG8" t="inlineStr">
         <is>
           <t>5.56</t>
         </is>
       </c>
-      <c r="EG8" t="inlineStr">
+      <c r="EH8" t="inlineStr">
         <is>
           <t>9.29</t>
         </is>
       </c>
-      <c r="EH8" t="inlineStr">
+      <c r="EI8" t="inlineStr">
         <is>
           <t>64.29</t>
         </is>
       </c>
-      <c r="EI8" t="inlineStr">
+      <c r="EJ8" t="inlineStr">
         <is>
           <t>11.60%</t>
         </is>
       </c>
-      <c r="EJ8" t="inlineStr">
+      <c r="EK8" t="inlineStr">
         <is>
           <t>3.90%</t>
         </is>
       </c>
-      <c r="EK8" t="inlineStr">
+      <c r="EL8" t="inlineStr">
         <is>
           <t>20.16</t>
         </is>
       </c>
-      <c r="EL8" t="inlineStr">
+      <c r="EM8" t="inlineStr">
         <is>
           <t>3600</t>
         </is>
       </c>
-      <c r="EM8" t="inlineStr">
+      <c r="EN8" t="inlineStr">
         <is>
           <t>水龍頭零配件56.01%、水龍頭組裝件33.50%、其他10.49% (2025年)</t>
         </is>
       </c>
-      <c r="EN8" t="inlineStr">
+      <c r="EO8" t="inlineStr">
         <is>
           <t>橋椿-居家生活-上市</t>
         </is>
       </c>
-      <c r="EO8" t="inlineStr">
+      <c r="EP8" t="inlineStr">
         <is>
           <t>居家生活右下上市</t>
         </is>
       </c>
-      <c r="EP8" t="inlineStr">
+      <c r="EQ8" t="inlineStr">
         <is>
           <t>17.85</t>
         </is>
       </c>
-      <c r="EQ8" t="inlineStr">
+      <c r="ER8" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="ER8" t="inlineStr">
+      <c r="ES8" t="inlineStr">
         <is>
           <t>17.85</t>
         </is>
       </c>
-      <c r="ES8" t="inlineStr">
+      <c r="ET8" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="ET8" t="inlineStr">
+      <c r="EU8" t="inlineStr">
         <is>
           <t>17.85</t>
         </is>
       </c>
-      <c r="EU8" t="inlineStr">
+      <c r="EV8" t="inlineStr">
         <is>
           <t>38.31</t>
         </is>
       </c>
-      <c r="EV8" t="inlineStr">
+      <c r="EW8" t="inlineStr">
         <is>
           <t>** 其他 - 其他</t>
         </is>
       </c>
-      <c r="EW8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX8" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="EY8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FA8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB8" t="inlineStr">
         <is>
           <t>0</t>
@@ -8235,14 +8270,14 @@
       </c>
       <c r="FC8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FE8" t="inlineStr">
         <is>
           <t>0</t>
@@ -8250,12 +8285,12 @@
       </c>
       <c r="FF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
@@ -8275,94 +8310,94 @@
       </c>
       <c r="FK8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL8" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL8" t="inlineStr">
+      <c r="FM8" t="inlineStr">
         <is>
           <t>1857.0</t>
         </is>
       </c>
-      <c r="FM8" t="inlineStr">
+      <c r="FN8" t="inlineStr">
         <is>
           <t>1642.0</t>
         </is>
       </c>
-      <c r="FN8" t="inlineStr">
+      <c r="FO8" t="inlineStr">
         <is>
           <t>215.0</t>
         </is>
       </c>
-      <c r="FO8" t="inlineStr">
+      <c r="FP8" t="inlineStr">
         <is>
           <t>11.6</t>
         </is>
       </c>
-      <c r="FP8" t="inlineStr">
+      <c r="FQ8" t="inlineStr">
         <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="FQ8" t="inlineStr">
+      <c r="FR8" t="inlineStr">
         <is>
           <t>3.90%</t>
         </is>
       </c>
-      <c r="FR8" t="inlineStr">
+      <c r="FS8" t="inlineStr">
         <is>
           <t>-28.0</t>
         </is>
       </c>
-      <c r="FS8" t="inlineStr">
+      <c r="FT8" t="inlineStr">
         <is>
           <t>44.0</t>
         </is>
       </c>
-      <c r="FT8" t="inlineStr">
+      <c r="FU8" t="inlineStr">
         <is>
           <t>39.0</t>
         </is>
       </c>
-      <c r="FU8" t="inlineStr">
+      <c r="FV8" t="inlineStr">
         <is>
           <t>0.19</t>
         </is>
       </c>
-      <c r="FV8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FW8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="FX8" t="inlineStr">
+        <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX8" t="inlineStr">
+      <c r="FY8" t="inlineStr">
         <is>
           <t>0.18875</t>
         </is>
       </c>
-      <c r="FY8" t="inlineStr">
+      <c r="FZ8" t="inlineStr">
         <is>
           <t>10.89125</t>
         </is>
       </c>
-      <c r="FZ8" t="inlineStr">
+      <c r="GA8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA8" t="inlineStr">
+      <c r="GB8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GC8" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8370,75 +8405,80 @@
       </c>
       <c r="GD8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE8" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG8" t="inlineStr">
+        <is>
           <t>0.19</t>
         </is>
       </c>
-      <c r="GG8" t="inlineStr">
+      <c r="GH8" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="GH8" t="inlineStr">
+      <c r="GI8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GI8" t="inlineStr">
+      <c r="GJ8" t="inlineStr">
         <is>
           <t>0.09433962264150941</t>
         </is>
       </c>
-      <c r="GJ8" t="inlineStr">
+      <c r="GK8" t="inlineStr">
         <is>
           <t>0.07</t>
         </is>
       </c>
-      <c r="GK8" t="inlineStr">
+      <c r="GL8" t="inlineStr">
         <is>
           <t>0.5833333333333335</t>
         </is>
       </c>
-      <c r="GL8" t="inlineStr">
+      <c r="GM8" t="inlineStr">
         <is>
           <t>3.279999999999999</t>
         </is>
       </c>
-      <c r="GM8" t="inlineStr">
+      <c r="GN8" t="inlineStr">
         <is>
           <t>0.3942307692307692</t>
         </is>
       </c>
-      <c r="GN8" t="inlineStr">
+      <c r="GO8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO8" t="inlineStr">
+      <c r="GP8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP8" t="inlineStr">
+      <c r="GQ8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GQ8" t="inlineStr">
+      <c r="GR8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR8" t="inlineStr">
+      <c r="GS8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -8837,49 +8877,49 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
           <t>2026-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>10.31</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>-0.66</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>NA｜電機機械｜機械設備｜</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="CJ9" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8887,349 +8927,349 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
           <t>-1.61</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>-0.81</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>-0.74</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>-0.19</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>22.92</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>22.99</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>23.11</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>23.28</t>
         </is>
       </c>
-      <c r="CS9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>23.32</t>
         </is>
       </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
           <t>-0.004776378636561107</t>
         </is>
       </c>
-      <c r="CV9" t="inlineStr">
+      <c r="CW9" t="inlineStr">
         <is>
           <t>-0.002386634844868563</t>
         </is>
       </c>
-      <c r="CW9" t="inlineStr">
+      <c r="CX9" t="inlineStr">
         <is>
           <t>-0.0008647713760674414</t>
         </is>
       </c>
-      <c r="CX9" t="inlineStr">
+      <c r="CY9" t="inlineStr">
         <is>
           <t>-0.001586893120604005</t>
         </is>
       </c>
-      <c r="CY9" t="inlineStr">
+      <c r="CZ9" t="inlineStr">
         <is>
           <t>-0.0004821084208272985</t>
         </is>
       </c>
-      <c r="CZ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
           <t>-63.96</t>
         </is>
       </c>
-      <c r="DB9" t="inlineStr">
+      <c r="DC9" t="inlineStr">
         <is>
           <t>-0.1</t>
         </is>
       </c>
-      <c r="DC9" t="inlineStr">
+      <c r="DD9" t="inlineStr">
         <is>
           <t>-0.06</t>
         </is>
       </c>
-      <c r="DD9" t="inlineStr">
+      <c r="DE9" t="inlineStr">
         <is>
           <t>0.61</t>
         </is>
       </c>
-      <c r="DE9" t="inlineStr">
+      <c r="DF9" t="inlineStr">
         <is>
           <t>-110.44</t>
         </is>
       </c>
-      <c r="DF9" t="inlineStr">
+      <c r="DG9" t="inlineStr">
         <is>
           <t>2026/10/01</t>
         </is>
       </c>
-      <c r="DG9" t="inlineStr">
+      <c r="DH9" t="inlineStr">
         <is>
           <t>1701.68115942029</t>
         </is>
       </c>
-      <c r="DH9" t="inlineStr">
+      <c r="DI9" t="inlineStr">
         <is>
           <t>749.0</t>
         </is>
       </c>
-      <c r="DI9" t="inlineStr">
+      <c r="DJ9" t="inlineStr">
         <is>
           <t>445.4</t>
         </is>
       </c>
-      <c r="DJ9" t="inlineStr">
+      <c r="DK9" t="inlineStr">
         <is>
           <t>372.5</t>
         </is>
       </c>
-      <c r="DK9" t="inlineStr">
+      <c r="DL9" t="inlineStr">
         <is>
           <t>465.9</t>
         </is>
       </c>
-      <c r="DL9" t="inlineStr">
+      <c r="DM9" t="inlineStr">
         <is>
           <t>525.1</t>
         </is>
       </c>
-      <c r="DM9" t="inlineStr">
+      <c r="DN9" t="inlineStr">
         <is>
           <t>1009.8875</t>
         </is>
       </c>
-      <c r="DN9" t="inlineStr">
+      <c r="DO9" t="inlineStr">
         <is>
           <t>-21.35520336809556</t>
         </is>
       </c>
-      <c r="DO9" t="inlineStr">
+      <c r="DP9" t="inlineStr">
         <is>
           <t>1.295471372300199</t>
         </is>
       </c>
-      <c r="DP9" t="inlineStr">
+      <c r="DQ9" t="inlineStr">
         <is>
           <t>749.0</t>
         </is>
       </c>
-      <c r="DQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
           <t>23.6</t>
         </is>
       </c>
-      <c r="DS9" t="inlineStr">
+      <c r="DT9" t="inlineStr">
         <is>
           <t>2026/08/10</t>
         </is>
       </c>
-      <c r="DT9" t="inlineStr">
+      <c r="DU9" t="inlineStr">
         <is>
           <t>-4.45</t>
         </is>
       </c>
-      <c r="DU9" t="inlineStr">
+      <c r="DV9" t="inlineStr">
         <is>
           <t>宏佳騰</t>
         </is>
       </c>
-      <c r="DV9" t="inlineStr">
+      <c r="DW9" t="inlineStr">
         <is>
           <t>宏佳騰</t>
         </is>
       </c>
-      <c r="DW9" t="inlineStr">
+      <c r="DX9" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="DX9" t="inlineStr">
+      <c r="DY9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="DY9" t="inlineStr">
+      <c r="DZ9" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="DZ9" t="inlineStr">
+      <c r="EA9" t="inlineStr">
         <is>
           <t>-35.72299191484175</t>
         </is>
       </c>
-      <c r="EA9" t="inlineStr">
+      <c r="EB9" t="inlineStr">
         <is>
           <t>7.998607394462345</t>
         </is>
       </c>
-      <c r="EB9" t="inlineStr">
+      <c r="EC9" t="inlineStr">
         <is>
           <t>23.8755208552221</t>
         </is>
       </c>
-      <c r="EC9" t="inlineStr">
+      <c r="ED9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED9" t="inlineStr">
+      <c r="EE9" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="EE9" t="inlineStr">
+      <c r="EF9" t="inlineStr">
         <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="EF9" t="inlineStr">
+      <c r="EG9" t="inlineStr">
         <is>
           <t>2.22</t>
         </is>
       </c>
-      <c r="EG9" t="inlineStr">
+      <c r="EH9" t="inlineStr">
         <is>
           <t>6.11</t>
         </is>
       </c>
-      <c r="EH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EI9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
           <t>20.97%</t>
         </is>
       </c>
-      <c r="EJ9" t="inlineStr">
+      <c r="EK9" t="inlineStr">
         <is>
           <t>-7.57%</t>
         </is>
       </c>
-      <c r="EK9" t="inlineStr">
+      <c r="EL9" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="EL9" t="inlineStr">
+      <c r="EM9" t="inlineStr">
         <is>
           <t>1647</t>
         </is>
       </c>
-      <c r="EM9" t="inlineStr">
+      <c r="EN9" t="inlineStr">
         <is>
           <t>ATV/ UTV71.35%、摩托車13.07%、電動機車8.10%、零組件及其他7.48% (2025年)</t>
         </is>
       </c>
-      <c r="EN9" t="inlineStr">
+      <c r="EO9" t="inlineStr">
         <is>
           <t>宏佳騰-電機機械-上櫃</t>
         </is>
       </c>
-      <c r="EO9" t="inlineStr">
+      <c r="EP9" t="inlineStr">
         <is>
           <t>電機機械右下上櫃</t>
         </is>
       </c>
-      <c r="EP9" t="inlineStr">
+      <c r="EQ9" t="inlineStr">
         <is>
           <t>22.65</t>
         </is>
       </c>
-      <c r="EQ9" t="inlineStr">
+      <c r="ER9" t="inlineStr">
         <is>
           <t>22.75</t>
         </is>
       </c>
-      <c r="ER9" t="inlineStr">
+      <c r="ES9" t="inlineStr">
         <is>
           <t>22.5</t>
         </is>
       </c>
-      <c r="ES9" t="inlineStr">
+      <c r="ET9" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="ET9" t="inlineStr">
+      <c r="EU9" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="EU9" t="inlineStr">
+      <c r="EV9" t="inlineStr">
         <is>
           <t>25.66</t>
         </is>
       </c>
-      <c r="EV9" t="inlineStr">
+      <c r="EW9" t="inlineStr">
         <is>
           <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
         </is>
       </c>
-      <c r="EW9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX9" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="EY9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA9" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FA9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB9" t="inlineStr">
         <is>
           <t>0</t>
@@ -9237,14 +9277,14 @@
       </c>
       <c r="FC9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FE9" t="inlineStr">
         <is>
           <t>0</t>
@@ -9252,12 +9292,12 @@
       </c>
       <c r="FF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
@@ -9277,94 +9317,94 @@
       </c>
       <c r="FK9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL9" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL9" t="inlineStr">
+      <c r="FM9" t="inlineStr">
         <is>
           <t>440.0</t>
         </is>
       </c>
-      <c r="FM9" t="inlineStr">
+      <c r="FN9" t="inlineStr">
         <is>
           <t>348.0</t>
         </is>
       </c>
-      <c r="FN9" t="inlineStr">
+      <c r="FO9" t="inlineStr">
         <is>
           <t>92.0</t>
         </is>
       </c>
-      <c r="FO9" t="inlineStr">
+      <c r="FP9" t="inlineStr">
         <is>
           <t>20.97</t>
         </is>
       </c>
-      <c r="FP9" t="inlineStr">
+      <c r="FQ9" t="inlineStr">
         <is>
           <t>-33.0</t>
         </is>
       </c>
-      <c r="FQ9" t="inlineStr">
+      <c r="FR9" t="inlineStr">
         <is>
           <t>-7.57%</t>
         </is>
       </c>
-      <c r="FR9" t="inlineStr">
+      <c r="FS9" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="FS9" t="inlineStr">
+      <c r="FT9" t="inlineStr">
         <is>
           <t>-24.0</t>
         </is>
       </c>
-      <c r="FT9" t="inlineStr">
+      <c r="FU9" t="inlineStr">
         <is>
           <t>-14.0</t>
         </is>
       </c>
-      <c r="FU9" t="inlineStr">
+      <c r="FV9" t="inlineStr">
         <is>
           <t>-0.19</t>
         </is>
       </c>
-      <c r="FV9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FW9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="FX9" t="inlineStr">
+        <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX9" t="inlineStr">
+      <c r="FY9" t="inlineStr">
         <is>
           <t>0.10625</t>
         </is>
       </c>
-      <c r="FY9" t="inlineStr">
+      <c r="FZ9" t="inlineStr">
         <is>
           <t>20.42875</t>
         </is>
       </c>
-      <c r="FZ9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GA9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GB9" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GC9" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9382,65 +9422,70 @@
       </c>
       <c r="GF9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG9" t="inlineStr">
+        <is>
           <t>-0.47</t>
         </is>
       </c>
-      <c r="GG9" t="inlineStr">
+      <c r="GH9" t="inlineStr">
         <is>
           <t>-1.678571428571428</t>
         </is>
       </c>
-      <c r="GH9" t="inlineStr">
+      <c r="GI9" t="inlineStr">
         <is>
           <t>-1.050000000000001</t>
         </is>
       </c>
-      <c r="GI9" t="inlineStr">
+      <c r="GJ9" t="inlineStr">
         <is>
           <t>-0.04768392370572205</t>
         </is>
       </c>
-      <c r="GJ9" t="inlineStr">
+      <c r="GK9" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="GK9" t="inlineStr">
+      <c r="GL9" t="inlineStr">
         <is>
           <t>-0.6984126984126984</t>
         </is>
       </c>
-      <c r="GL9" t="inlineStr">
+      <c r="GM9" t="inlineStr">
         <is>
           <t>0.1600000000000001</t>
         </is>
       </c>
-      <c r="GM9" t="inlineStr">
+      <c r="GN9" t="inlineStr">
         <is>
           <t>0.007688611244593968</t>
         </is>
       </c>
-      <c r="GN9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GO9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GP9" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GR9" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR9" t="inlineStr">
+      <c r="GS9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -9839,399 +9884,399 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
           <t>2026-08-28 00:00:00</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>5.34</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>-0.29</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>LV.2-1｜AI電力基建｜變壓器｜</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>1034</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>28.57</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>49.8</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>-0.37</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>-1.22</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>-2.00</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>694.6</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>694.5</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>703.15</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>709.12</t>
         </is>
       </c>
-      <c r="CS10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>723.62</t>
         </is>
       </c>
-      <c r="CT10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
           <t>0.001153070049005667</t>
         </is>
       </c>
-      <c r="CV10" t="inlineStr">
+      <c r="CW10" t="inlineStr">
         <is>
           <t>-0.002871500358937573</t>
         </is>
       </c>
-      <c r="CW10" t="inlineStr">
+      <c r="CX10" t="inlineStr">
         <is>
           <t>-0.002553372579615631</t>
         </is>
       </c>
-      <c r="CX10" t="inlineStr">
+      <c r="CY10" t="inlineStr">
         <is>
           <t>0.0006773538044706484</t>
         </is>
       </c>
-      <c r="CY10" t="inlineStr">
+      <c r="CZ10" t="inlineStr">
         <is>
           <t>-0.001707220334891013</t>
         </is>
       </c>
-      <c r="CZ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
           <t>-9.14</t>
         </is>
       </c>
-      <c r="DB10" t="inlineStr">
+      <c r="DC10" t="inlineStr">
         <is>
           <t>-7.21</t>
         </is>
       </c>
-      <c r="DC10" t="inlineStr">
+      <c r="DD10" t="inlineStr">
         <is>
           <t>-6.61</t>
         </is>
       </c>
-      <c r="DD10" t="inlineStr">
+      <c r="DE10" t="inlineStr">
         <is>
           <t>64.73</t>
         </is>
       </c>
-      <c r="DE10" t="inlineStr">
+      <c r="DF10" t="inlineStr">
         <is>
           <t>-110.21</t>
         </is>
       </c>
-      <c r="DF10" t="inlineStr">
+      <c r="DG10" t="inlineStr">
         <is>
           <t>2026/07/24</t>
         </is>
       </c>
-      <c r="DG10" t="inlineStr">
+      <c r="DH10" t="inlineStr">
         <is>
           <t>4381147211.188406</t>
         </is>
       </c>
-      <c r="DH10" t="inlineStr">
+      <c r="DI10" t="inlineStr">
         <is>
           <t>716825302.0</t>
         </is>
       </c>
-      <c r="DI10" t="inlineStr">
+      <c r="DJ10" t="inlineStr">
         <is>
           <t>873811612.2</t>
         </is>
       </c>
-      <c r="DJ10" t="inlineStr">
+      <c r="DK10" t="inlineStr">
         <is>
           <t>758303340.5</t>
         </is>
       </c>
-      <c r="DK10" t="inlineStr">
+      <c r="DL10" t="inlineStr">
         <is>
           <t>1198343846.133333</t>
         </is>
       </c>
-      <c r="DL10" t="inlineStr">
+      <c r="DM10" t="inlineStr">
         <is>
           <t>1122138161.56</t>
         </is>
       </c>
-      <c r="DM10" t="inlineStr">
+      <c r="DN10" t="inlineStr">
         <is>
           <t>1287935013.9625</t>
         </is>
       </c>
-      <c r="DN10" t="inlineStr">
+      <c r="DO10" t="inlineStr">
         <is>
           <t>-76782888.13361648</t>
         </is>
       </c>
-      <c r="DO10" t="inlineStr">
+      <c r="DP10" t="inlineStr">
         <is>
           <t>-17492349.43699038</t>
         </is>
       </c>
-      <c r="DP10" t="inlineStr">
+      <c r="DQ10" t="inlineStr">
         <is>
           <t>716825302.0</t>
         </is>
       </c>
-      <c r="DQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS10" t="inlineStr">
+        <is>
           <t>722.0</t>
         </is>
       </c>
-      <c r="DS10" t="inlineStr">
+      <c r="DT10" t="inlineStr">
         <is>
           <t>2026/09/03</t>
         </is>
       </c>
-      <c r="DT10" t="inlineStr">
+      <c r="DU10" t="inlineStr">
         <is>
           <t>-4.16</t>
         </is>
       </c>
-      <c r="DU10" t="inlineStr">
+      <c r="DV10" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="DV10" t="inlineStr">
+      <c r="DW10" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="DW10" t="inlineStr">
+      <c r="DX10" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="DX10" t="inlineStr">
+      <c r="DY10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY10" t="inlineStr">
+      <c r="DZ10" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="DZ10" t="inlineStr">
+      <c r="EA10" t="inlineStr">
         <is>
           <t>10.43024464544995</t>
         </is>
       </c>
-      <c r="EA10" t="inlineStr">
+      <c r="EB10" t="inlineStr">
         <is>
           <t>6.384573975418948</t>
         </is>
       </c>
-      <c r="EB10" t="inlineStr">
+      <c r="EC10" t="inlineStr">
         <is>
           <t>7.195183288405167</t>
         </is>
       </c>
-      <c r="EC10" t="inlineStr">
+      <c r="ED10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
-      <c r="ED10" t="inlineStr">
+      <c r="EE10" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE10" t="inlineStr">
+      <c r="EF10" t="inlineStr">
         <is>
           <t>23.75</t>
         </is>
       </c>
-      <c r="EF10" t="inlineStr">
+      <c r="EG10" t="inlineStr">
         <is>
           <t>1.73</t>
         </is>
       </c>
-      <c r="EG10" t="inlineStr">
+      <c r="EH10" t="inlineStr">
         <is>
           <t>15.7</t>
         </is>
       </c>
-      <c r="EH10" t="inlineStr">
+      <c r="EI10" t="inlineStr">
         <is>
           <t>45.29</t>
         </is>
       </c>
-      <c r="EI10" t="inlineStr">
+      <c r="EJ10" t="inlineStr">
         <is>
           <t>43.50%</t>
         </is>
       </c>
-      <c r="EJ10" t="inlineStr">
+      <c r="EK10" t="inlineStr">
         <is>
           <t>22.11%</t>
         </is>
       </c>
-      <c r="EK10" t="inlineStr">
+      <c r="EL10" t="inlineStr">
         <is>
           <t>34.62</t>
         </is>
       </c>
-      <c r="EL10" t="inlineStr">
+      <c r="EM10" t="inlineStr">
         <is>
           <t>240448</t>
         </is>
       </c>
-      <c r="EM10" t="inlineStr">
+      <c r="EN10" t="inlineStr">
         <is>
           <t>變壓器73.61%、其他9.67%、配電盤7.29%、工程承包5.69%、配電器材3.69%、電力0.05% (2025年)</t>
         </is>
       </c>
-      <c r="EN10" t="inlineStr">
+      <c r="EO10" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="EO10" t="inlineStr">
+      <c r="EP10" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="EP10" t="inlineStr">
+      <c r="EQ10" t="inlineStr">
         <is>
           <t>694.0</t>
         </is>
       </c>
-      <c r="EQ10" t="inlineStr">
+      <c r="ER10" t="inlineStr">
         <is>
           <t>697.0</t>
         </is>
       </c>
-      <c r="ER10" t="inlineStr">
+      <c r="ES10" t="inlineStr">
         <is>
           <t>689.0</t>
         </is>
       </c>
-      <c r="ES10" t="inlineStr">
+      <c r="ET10" t="inlineStr">
         <is>
           <t>692.0</t>
         </is>
       </c>
-      <c r="ET10" t="inlineStr">
+      <c r="EU10" t="inlineStr">
         <is>
           <t>653.0</t>
         </is>
       </c>
-      <c r="EU10" t="inlineStr">
+      <c r="EV10" t="inlineStr">
         <is>
           <t>29.14</t>
         </is>
       </c>
-      <c r="EV10" t="inlineStr">
+      <c r="EW10" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="EW10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX10" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY10" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="EY10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA10" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FA10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB10" t="inlineStr">
         <is>
           <t>0</t>
@@ -10254,12 +10299,12 @@
       </c>
       <c r="FF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
@@ -10279,94 +10324,94 @@
       </c>
       <c r="FK10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL10" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL10" t="inlineStr">
+      <c r="FM10" t="inlineStr">
         <is>
           <t>5456.0</t>
         </is>
       </c>
-      <c r="FM10" t="inlineStr">
+      <c r="FN10" t="inlineStr">
         <is>
           <t>3082.0</t>
         </is>
       </c>
-      <c r="FN10" t="inlineStr">
+      <c r="FO10" t="inlineStr">
         <is>
           <t>2373.0</t>
         </is>
       </c>
-      <c r="FO10" t="inlineStr">
+      <c r="FP10" t="inlineStr">
         <is>
           <t>43.5</t>
         </is>
       </c>
-      <c r="FP10" t="inlineStr">
+      <c r="FQ10" t="inlineStr">
         <is>
           <t>1206.0</t>
         </is>
       </c>
-      <c r="FQ10" t="inlineStr">
+      <c r="FR10" t="inlineStr">
         <is>
           <t>22.11%</t>
         </is>
       </c>
-      <c r="FR10" t="inlineStr">
+      <c r="FS10" t="inlineStr">
         <is>
           <t>82.0</t>
         </is>
       </c>
-      <c r="FS10" t="inlineStr">
+      <c r="FT10" t="inlineStr">
         <is>
           <t>1288.0</t>
         </is>
       </c>
-      <c r="FT10" t="inlineStr">
+      <c r="FU10" t="inlineStr">
         <is>
           <t>1021.0</t>
         </is>
       </c>
-      <c r="FU10" t="inlineStr">
+      <c r="FV10" t="inlineStr">
         <is>
           <t>3.23</t>
         </is>
       </c>
-      <c r="FV10" t="inlineStr">
+      <c r="FW10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW10" t="inlineStr">
+      <c r="FX10" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX10" t="inlineStr">
+      <c r="FY10" t="inlineStr">
         <is>
           <t>3.81375</t>
         </is>
       </c>
-      <c r="FY10" t="inlineStr">
+      <c r="FZ10" t="inlineStr">
         <is>
           <t>40.245</t>
         </is>
       </c>
-      <c r="FZ10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GA10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GB10" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GC10" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -10384,65 +10429,70 @@
       </c>
       <c r="GF10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG10" t="inlineStr">
+        <is>
           <t>-0.06000000000000005</t>
         </is>
       </c>
-      <c r="GG10" t="inlineStr">
+      <c r="GH10" t="inlineStr">
         <is>
           <t>-0.01823708206686936</t>
         </is>
       </c>
-      <c r="GH10" t="inlineStr">
+      <c r="GI10" t="inlineStr">
         <is>
           <t>-0.1099999999999994</t>
         </is>
       </c>
-      <c r="GI10" t="inlineStr">
+      <c r="GJ10" t="inlineStr">
         <is>
           <t>-0.002522357257509711</t>
         </is>
       </c>
-      <c r="GJ10" t="inlineStr">
+      <c r="GK10" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="GK10" t="inlineStr">
+      <c r="GL10" t="inlineStr">
         <is>
           <t>0.292</t>
         </is>
       </c>
-      <c r="GL10" t="inlineStr">
+      <c r="GM10" t="inlineStr">
         <is>
           <t>3.130000000000003</t>
         </is>
       </c>
-      <c r="GM10" t="inlineStr">
+      <c r="GN10" t="inlineStr">
         <is>
           <t>0.07753282140203122</t>
         </is>
       </c>
-      <c r="GN10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GO10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GP10" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GR10" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR10" t="inlineStr">
+      <c r="GS10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -10841,434 +10891,434 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
           <t>2026-09-30 00:00:00</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>5.93</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>NA｜水泥｜水泥製造｜台灣水泥龍頭，跨足綠能</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>241</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>33061</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>53.85</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>43.15</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>1.79</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>25.35</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>24.58</t>
         </is>
       </c>
-      <c r="CS11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>24.31</t>
         </is>
       </c>
-      <c r="CT11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV11" t="inlineStr">
+        <is>
           <t>0.001184834123222789</t>
         </is>
       </c>
-      <c r="CV11" t="inlineStr">
+      <c r="CW11" t="inlineStr">
         <is>
           <t>0.004533806426177955</t>
         </is>
       </c>
-      <c r="CW11" t="inlineStr">
+      <c r="CX11" t="inlineStr">
         <is>
           <t>0.002818602778336787</t>
         </is>
       </c>
-      <c r="CX11" t="inlineStr">
+      <c r="CY11" t="inlineStr">
         <is>
           <t>0.000732839345330305</t>
         </is>
       </c>
-      <c r="CY11" t="inlineStr">
+      <c r="CZ11" t="inlineStr">
         <is>
           <t>0.0005916246527422064</t>
         </is>
       </c>
-      <c r="CZ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB11" t="inlineStr">
+        <is>
           <t>21.83</t>
         </is>
       </c>
-      <c r="DB11" t="inlineStr">
+      <c r="DC11" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="DC11" t="inlineStr">
+      <c r="DD11" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="DD11" t="inlineStr">
+      <c r="DE11" t="inlineStr">
         <is>
           <t>0.78</t>
         </is>
       </c>
-      <c r="DE11" t="inlineStr">
+      <c r="DF11" t="inlineStr">
         <is>
           <t>-68.05</t>
         </is>
       </c>
-      <c r="DF11" t="inlineStr">
+      <c r="DG11" t="inlineStr">
         <is>
           <t>2026/09/23</t>
         </is>
       </c>
-      <c r="DG11" t="inlineStr">
+      <c r="DH11" t="inlineStr">
         <is>
           <t>1270336075.971014</t>
         </is>
       </c>
-      <c r="DH11" t="inlineStr">
+      <c r="DI11" t="inlineStr">
         <is>
           <t>851041282.0</t>
         </is>
       </c>
-      <c r="DI11" t="inlineStr">
+      <c r="DJ11" t="inlineStr">
         <is>
           <t>740015180.2</t>
         </is>
       </c>
-      <c r="DJ11" t="inlineStr">
+      <c r="DK11" t="inlineStr">
         <is>
           <t>1298632502.3</t>
         </is>
       </c>
-      <c r="DK11" t="inlineStr">
+      <c r="DL11" t="inlineStr">
         <is>
           <t>1331124271.866667</t>
         </is>
       </c>
-      <c r="DL11" t="inlineStr">
+      <c r="DM11" t="inlineStr">
         <is>
           <t>1068480973.82</t>
         </is>
       </c>
-      <c r="DM11" t="inlineStr">
+      <c r="DN11" t="inlineStr">
         <is>
           <t>942963756.375</t>
         </is>
       </c>
-      <c r="DN11" t="inlineStr">
+      <c r="DO11" t="inlineStr">
         <is>
           <t>-15007570.7738959</t>
         </is>
       </c>
-      <c r="DO11" t="inlineStr">
+      <c r="DP11" t="inlineStr">
         <is>
           <t>-59748391.87172389</t>
         </is>
       </c>
-      <c r="DP11" t="inlineStr">
+      <c r="DQ11" t="inlineStr">
         <is>
           <t>851041282.0</t>
         </is>
       </c>
-      <c r="DQ11" t="inlineStr">
+      <c r="DR11" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="DR11" t="inlineStr">
+      <c r="DS11" t="inlineStr">
         <is>
           <t>24.65</t>
         </is>
       </c>
-      <c r="DS11" t="inlineStr">
+      <c r="DT11" t="inlineStr">
         <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="DT11" t="inlineStr">
+      <c r="DU11" t="inlineStr">
         <is>
           <t>4.26</t>
         </is>
       </c>
-      <c r="DU11" t="inlineStr">
+      <c r="DV11" t="inlineStr">
         <is>
           <t>台泥</t>
         </is>
       </c>
-      <c r="DV11" t="inlineStr">
+      <c r="DW11" t="inlineStr">
         <is>
           <t>台泥</t>
         </is>
       </c>
-      <c r="DW11" t="inlineStr">
+      <c r="DX11" t="inlineStr">
         <is>
           <t>水泥工業</t>
         </is>
       </c>
-      <c r="DX11" t="inlineStr">
+      <c r="DY11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY11" t="inlineStr">
+      <c r="DZ11" t="inlineStr">
         <is>
           <t>0.34</t>
         </is>
       </c>
-      <c r="DZ11" t="inlineStr">
+      <c r="EA11" t="inlineStr">
         <is>
           <t>-1.608351096530149</t>
         </is>
       </c>
-      <c r="EA11" t="inlineStr">
+      <c r="EB11" t="inlineStr">
         <is>
           <t>-3.691438066611057</t>
         </is>
       </c>
-      <c r="EB11" t="inlineStr">
+      <c r="EC11" t="inlineStr">
         <is>
           <t>-4.576639672381974</t>
         </is>
       </c>
-      <c r="EC11" t="inlineStr">
+      <c r="ED11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
-      <c r="ED11" t="inlineStr">
+      <c r="EE11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE11" t="inlineStr">
+      <c r="EF11" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="EF11" t="inlineStr">
+      <c r="EG11" t="inlineStr">
         <is>
           <t>3.11</t>
         </is>
       </c>
-      <c r="EG11" t="inlineStr">
+      <c r="EH11" t="inlineStr">
         <is>
           <t>4.96</t>
         </is>
       </c>
-      <c r="EH11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EI11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="EJ11" t="inlineStr">
+        <is>
           <t>17.79%</t>
         </is>
       </c>
-      <c r="EJ11" t="inlineStr">
+      <c r="EK11" t="inlineStr">
         <is>
           <t>6.24%</t>
         </is>
       </c>
-      <c r="EK11" t="inlineStr">
+      <c r="EL11" t="inlineStr">
         <is>
           <t>14.75</t>
         </is>
       </c>
-      <c r="EL11" t="inlineStr">
+      <c r="EM11" t="inlineStr">
         <is>
           <t>193346</t>
         </is>
       </c>
-      <c r="EM11" t="inlineStr">
+      <c r="EN11" t="inlineStr">
         <is>
           <t>水泥,預拌混擬土80.05%、電力供給及儲能,可充式鋰離16.70%、海陸運輸3.25% (2025年)</t>
         </is>
       </c>
-      <c r="EN11" t="inlineStr">
+      <c r="EO11" t="inlineStr">
         <is>
           <t>台泥-水泥工業-上市</t>
         </is>
       </c>
-      <c r="EO11" t="inlineStr">
+      <c r="EP11" t="inlineStr">
         <is>
           <t>水泥工業右上上市</t>
         </is>
       </c>
-      <c r="EP11" t="inlineStr">
+      <c r="EQ11" t="inlineStr">
         <is>
           <t>25.5</t>
         </is>
       </c>
-      <c r="EQ11" t="inlineStr">
+      <c r="ER11" t="inlineStr">
         <is>
           <t>25.9</t>
         </is>
       </c>
-      <c r="ER11" t="inlineStr">
+      <c r="ES11" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="ES11" t="inlineStr">
+      <c r="ET11" t="inlineStr">
         <is>
           <t>25.7</t>
         </is>
       </c>
-      <c r="ET11" t="inlineStr">
+      <c r="EU11" t="inlineStr">
         <is>
           <t>22.2</t>
         </is>
       </c>
-      <c r="EU11" t="inlineStr">
+      <c r="EV11" t="inlineStr">
         <is>
           <t>30.86</t>
         </is>
       </c>
-      <c r="EV11" t="inlineStr">
+      <c r="EW11" t="inlineStr">
         <is>
           <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
-      <c r="EW11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX11" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY11" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EY11" t="inlineStr">
+      <c r="EZ11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EZ11" t="inlineStr">
+      <c r="FA11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="FA11" t="inlineStr">
+      <c r="FB11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="FB11" t="inlineStr">
+      <c r="FC11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="FC11" t="inlineStr">
+      <c r="FD11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FD11" t="inlineStr">
+      <c r="FE11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FE11" t="inlineStr">
+      <c r="FF11" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="FF11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FG11" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="FH11" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="FH11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FI11" t="inlineStr">
         <is>
           <t>0</t>
@@ -11281,94 +11331,94 @@
       </c>
       <c r="FK11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL11" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL11" t="inlineStr">
+      <c r="FM11" t="inlineStr">
         <is>
           <t>38122.0</t>
         </is>
       </c>
-      <c r="FM11" t="inlineStr">
+      <c r="FN11" t="inlineStr">
         <is>
           <t>31338.0</t>
         </is>
       </c>
-      <c r="FN11" t="inlineStr">
+      <c r="FO11" t="inlineStr">
         <is>
           <t>6783.0</t>
         </is>
       </c>
-      <c r="FO11" t="inlineStr">
+      <c r="FP11" t="inlineStr">
         <is>
           <t>17.79</t>
         </is>
       </c>
-      <c r="FP11" t="inlineStr">
+      <c r="FQ11" t="inlineStr">
         <is>
           <t>2378.0</t>
         </is>
       </c>
-      <c r="FQ11" t="inlineStr">
+      <c r="FR11" t="inlineStr">
         <is>
           <t>6.24%</t>
         </is>
       </c>
-      <c r="FR11" t="inlineStr">
+      <c r="FS11" t="inlineStr">
         <is>
           <t>2124.0</t>
         </is>
       </c>
-      <c r="FS11" t="inlineStr">
+      <c r="FT11" t="inlineStr">
         <is>
           <t>4502.0</t>
         </is>
       </c>
-      <c r="FT11" t="inlineStr">
+      <c r="FU11" t="inlineStr">
         <is>
           <t>2562.0</t>
         </is>
       </c>
-      <c r="FU11" t="inlineStr">
+      <c r="FV11" t="inlineStr">
         <is>
           <t>0.29</t>
         </is>
       </c>
-      <c r="FV11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="FW11" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="FX11" t="inlineStr">
+        <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX11" t="inlineStr">
+      <c r="FY11" t="inlineStr">
         <is>
           <t>-0.035</t>
         </is>
       </c>
-      <c r="FY11" t="inlineStr">
+      <c r="FZ11" t="inlineStr">
         <is>
           <t>19.6475</t>
         </is>
       </c>
-      <c r="FZ11" t="inlineStr">
+      <c r="GA11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA11" t="inlineStr">
+      <c r="GB11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GC11" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11376,75 +11426,80 @@
       </c>
       <c r="GD11" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE11" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF11" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG11" t="inlineStr">
+        <is>
           <t>0.19</t>
         </is>
       </c>
-      <c r="GG11" t="inlineStr">
+      <c r="GH11" t="inlineStr">
         <is>
           <t>1.899999999999999</t>
         </is>
       </c>
-      <c r="GH11" t="inlineStr">
+      <c r="GI11" t="inlineStr">
         <is>
           <t>-0.9299999999999997</t>
         </is>
       </c>
-      <c r="GI11" t="inlineStr">
+      <c r="GJ11" t="inlineStr">
         <is>
           <t>-0.04967948717948711</t>
         </is>
       </c>
-      <c r="GJ11" t="inlineStr">
+      <c r="GK11" t="inlineStr">
         <is>
           <t>0.29</t>
         </is>
       </c>
-      <c r="GK11" t="inlineStr">
+      <c r="GL11" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="GL11" t="inlineStr">
+      <c r="GM11" t="inlineStr">
         <is>
           <t>2.67</t>
         </is>
       </c>
-      <c r="GM11" t="inlineStr">
+      <c r="GN11" t="inlineStr">
         <is>
           <t>0.1765873015873016</t>
         </is>
       </c>
-      <c r="GN11" t="inlineStr">
+      <c r="GO11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO11" t="inlineStr">
+      <c r="GP11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GQ11" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GR11" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR11" t="inlineStr">
+      <c r="GS11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EW11"/>
+  <dimension ref="A1:EX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -761,435 +761,440 @@
       </c>
       <c r="BO1" s="1" t="inlineStr">
         <is>
+          <t>量起_K</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>MA_20</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>MA_50</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>MA_5_斜率</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>MA_10_斜率</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>MA_20_斜率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_5</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_10</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_30</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_50</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>量短5長30比</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>季別</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>營業收入</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>毛利率</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>營業利益</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>營益率</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>業外收支</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>稅前淨利</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>EPS(元)</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>EPS_前8季全為正</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>去年同季比較</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>EPS_MA_8</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>GM_MA_8</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>EPS_維持</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>毛利率_維持</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>EPS_創新高</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>毛利率_創新高</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>財報健康</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>財報強勢</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>EPS_QoQ</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>EPS_QoQ_%</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>GM_QoQ</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>GM_QoQ_%</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY_%</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>GM_YoY</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>GM_YoY_%</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>EPS_成長</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY成長</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>毛利率成長</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>毛利率YoY成長</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>財報動能強</t>
         </is>
@@ -1218,12 +1223,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5963.0</t>
+          <t>4687.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1233,7 +1238,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1248,12 +1253,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1278,12 +1283,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1298,12 +1303,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1328,14 +1333,14 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>8.0</t>
@@ -1343,17 +1348,17 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1428,12 +1433,12 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>639878.0</t>
+          <t>-438943.0</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1443,17 +1448,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1528,349 +1533,349 @@
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>82.48</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>84.13</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>148.25</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>152.28</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.009090909090909038</t>
+          <t>151.56</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.00564034505640354</t>
+          <t>-0.003856041131105381</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.003044654939106772</t>
+          <t>0.003581895148160097</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>165.35</t>
+          <t>0.002341920374707485</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>2330.66</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>2026/09/10</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>2096440.446132597</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>926189.0</t>
+          <t>2092601.48630137</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>1264690.4</t>
+          <t>723393.0</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>1150918.0</t>
+          <t>1006498.4</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>951902.6333333333</t>
+          <t>1204498.5</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>1113685.32</t>
+          <t>984966.1666666666</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>39866.22838596605</t>
+          <t>1047645.88</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30813.17231586394</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
           <t>2026/05/13</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>-28.60</t>
-        </is>
-      </c>
       <c r="CP2" t="inlineStr">
         <is>
+          <t>-28.84</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
           <t>元太</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>元太</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
       <c r="CU2" t="inlineStr">
         <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
           <t>4.850467566339402</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>13.53765084612085</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>-1.081107922304614</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="CY2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
           <t>8.85</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>14.93</t>
-        </is>
-      </c>
       <c r="DD2" t="inlineStr">
         <is>
+          <t>15.18</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
           <t>58.72</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>34.67</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
-      </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>177293</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
+          <t>180180</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
           <t>消費性電子產品56.39%、物聯網應用43.61% (2025年)</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>元太-光電業-上櫃</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>光電業右下上櫃</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>156.5</t>
-        </is>
-      </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>158.5</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
           <t>65.6</t>
         </is>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 面板、電子書</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>1.328592185496283</t>
+          <t>False</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
+          <t>1.021860886253792</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="DT2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>10216.0</t>
         </is>
       </c>
-      <c r="DU2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>58.72</t>
         </is>
       </c>
-      <c r="DV2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>3542.0</t>
         </is>
       </c>
-      <c r="DW2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>34.67%</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>1033.0</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>4575.0</t>
         </is>
       </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>3.23</t>
         </is>
       </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EB2" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
           <t>EPS成長 / 毛利率衰退</t>
         </is>
       </c>
-      <c r="EC2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="ED2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
         <is>
           <t>54.665</t>
         </is>
       </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EF2" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -1878,7 +1883,7 @@
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
@@ -1888,59 +1893,59 @@
       </c>
       <c r="EI2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
           <t>0.8199999999999998</t>
         </is>
       </c>
-      <c r="EL2" t="inlineStr">
+      <c r="EM2" t="inlineStr">
         <is>
           <t>0.3402489626556016</t>
         </is>
       </c>
-      <c r="EM2" t="inlineStr">
+      <c r="EN2" t="inlineStr">
         <is>
           <t>-0.9299999999999997</t>
         </is>
       </c>
-      <c r="EN2" t="inlineStr">
+      <c r="EO2" t="inlineStr">
         <is>
           <t>-0.01559094719195309</t>
         </is>
       </c>
-      <c r="EO2" t="inlineStr">
+      <c r="EP2" t="inlineStr">
         <is>
           <t>0.6499999999999999</t>
         </is>
       </c>
-      <c r="EP2" t="inlineStr">
+      <c r="EQ2" t="inlineStr">
         <is>
           <t>0.251937984496124</t>
         </is>
       </c>
-      <c r="EQ2" t="inlineStr">
+      <c r="ER2" t="inlineStr">
         <is>
           <t>-1.57</t>
         </is>
       </c>
-      <c r="ER2" t="inlineStr">
+      <c r="ES2" t="inlineStr">
         <is>
           <t>-0.02604080278653176</t>
         </is>
       </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="ET2" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -1948,7 +1953,7 @@
       </c>
       <c r="EU2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EV2" t="inlineStr">
@@ -1957,6 +1962,11 @@
         </is>
       </c>
       <c r="EW2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="EX2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -1985,12 +1995,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1264.785</t>
+          <t>1176.927</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2000,7 +2010,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2335.0</t>
+          <t>2425.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2015,12 +2025,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2045,12 +2055,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>4.666666666666667</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2070,57 +2080,57 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -2130,7 +2140,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>強勢</t>
+          <t>盤整</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -2195,12 +2205,12 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>-63757.0</t>
+          <t>140673.0</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2210,17 +2220,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -2295,349 +2305,349 @@
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>59</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>79.36</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>2369.25</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>2183.6</t>
+          <t>2344.5</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.01932367149758463</t>
+          <t>2217.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>-0.005243609351103351</t>
+          <t>0.01150895140664954</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>-0.001685452438639046</t>
+          <t>0.009415371140792717</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>-32.83</t>
+          <t>-0.00223428024257899</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>39.67</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>2026/09/22</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>4786799063.080111</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3021026515.0</t>
+          <t>4782455355.410959</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>4107416659.0</t>
+          <t>2855972570.0</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>3517038862.5</t>
+          <t>3218407511.0</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>3641564516.1</t>
+          <t>3271675647.0</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>3783642989.56</t>
+          <t>3672955981.433333</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>-16797870.86255595</t>
+          <t>3687283094.36</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-63475301.81948109</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
           <t>2026/08/19</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>29.72</t>
-        </is>
-      </c>
       <c r="CP3" t="inlineStr">
         <is>
+          <t>34.72</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="CS3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
       <c r="CU3" t="inlineStr">
         <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
           <t>5.566013969998855</t>
         </is>
       </c>
-      <c r="CV3" t="inlineStr">
+      <c r="CW3" t="inlineStr">
         <is>
           <t>32.17438109017265</t>
         </is>
       </c>
-      <c r="CW3" t="inlineStr">
+      <c r="CX3" t="inlineStr">
         <is>
           <t>47.25725810073954</t>
         </is>
       </c>
-      <c r="CX3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
           <t>54.55</t>
         </is>
       </c>
-      <c r="DC3" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="DD3" t="inlineStr">
         <is>
+          <t>52.62</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
           <t>34.05</t>
         </is>
       </c>
-      <c r="DE3" t="inlineStr">
+      <c r="DF3" t="inlineStr">
         <is>
           <t>27.90</t>
         </is>
       </c>
-      <c r="DF3" t="inlineStr">
-        <is>
-          <t>49.42</t>
-        </is>
-      </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>160071</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
+          <t>168640</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
           <t>折疊式手機轉軸56.42%、伺服器產品組件36.29%、筆記型電腦轉軸6.41%、其他0.88% (2025年)</t>
         </is>
       </c>
-      <c r="DI3" t="inlineStr">
+      <c r="DJ3" t="inlineStr">
         <is>
           <t>富世達-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="DJ3" t="inlineStr">
+      <c r="DK3" t="inlineStr">
         <is>
           <t>電子零組件業右上上市</t>
         </is>
       </c>
-      <c r="DK3" t="inlineStr">
+      <c r="DL3" t="inlineStr">
         <is>
           <t>2490.0</t>
         </is>
       </c>
-      <c r="DL3" t="inlineStr">
-        <is>
-          <t>2515.0</t>
-        </is>
-      </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>2310.0</t>
+          <t>2490.0</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>2335.0</t>
+          <t>2380.0</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
+          <t>2425.0</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
           <t>121.86</t>
         </is>
       </c>
-      <c r="DP3" t="inlineStr">
+      <c r="DQ3" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 機構樞紐</t>
         </is>
       </c>
-      <c r="DQ3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="DT3" t="inlineStr">
+      <c r="DU3" t="inlineStr">
         <is>
           <t>3740.0</t>
         </is>
       </c>
-      <c r="DU3" t="inlineStr">
+      <c r="DV3" t="inlineStr">
         <is>
           <t>34.05</t>
         </is>
       </c>
-      <c r="DV3" t="inlineStr">
+      <c r="DW3" t="inlineStr">
         <is>
           <t>1043.0</t>
         </is>
       </c>
-      <c r="DW3" t="inlineStr">
+      <c r="DX3" t="inlineStr">
         <is>
           <t>27.90%</t>
         </is>
       </c>
-      <c r="DX3" t="inlineStr">
+      <c r="DY3" t="inlineStr">
         <is>
           <t>32.0</t>
         </is>
       </c>
-      <c r="DY3" t="inlineStr">
+      <c r="DZ3" t="inlineStr">
         <is>
           <t>1075.0</t>
         </is>
       </c>
-      <c r="DZ3" t="inlineStr">
+      <c r="EA3" t="inlineStr">
         <is>
           <t>12.39</t>
         </is>
       </c>
-      <c r="EA3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EB3" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="EC3" t="inlineStr">
+      <c r="ED3" t="inlineStr">
         <is>
           <t>8.457500000000001</t>
         </is>
       </c>
-      <c r="ED3" t="inlineStr">
+      <c r="EE3" t="inlineStr">
         <is>
           <t>26.60125</t>
         </is>
       </c>
-      <c r="EE3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EF3" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -2645,12 +2655,12 @@
       </c>
       <c r="EG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
@@ -2660,57 +2670,57 @@
       </c>
       <c r="EJ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EK3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
           <t>-0.9900000000000002</t>
         </is>
       </c>
-      <c r="EL3" t="inlineStr">
+      <c r="EM3" t="inlineStr">
         <is>
           <t>-0.07399103139013452</t>
         </is>
       </c>
-      <c r="EM3" t="inlineStr">
+      <c r="EN3" t="inlineStr">
         <is>
           <t>1.739999999999995</t>
         </is>
       </c>
-      <c r="EN3" t="inlineStr">
+      <c r="EO3" t="inlineStr">
         <is>
           <t>0.05385329619312884</t>
         </is>
       </c>
-      <c r="EO3" t="inlineStr">
+      <c r="EP3" t="inlineStr">
         <is>
           <t>7.57</t>
         </is>
       </c>
-      <c r="EP3" t="inlineStr">
+      <c r="EQ3" t="inlineStr">
         <is>
           <t>1.570539419087137</t>
         </is>
       </c>
-      <c r="EQ3" t="inlineStr">
+      <c r="ER3" t="inlineStr">
         <is>
           <t>9.979999999999997</t>
         </is>
       </c>
-      <c r="ER3" t="inlineStr">
+      <c r="ES3" t="inlineStr">
         <is>
           <t>0.4146240132945573</t>
         </is>
       </c>
-      <c r="ES3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
@@ -2724,6 +2734,11 @@
         </is>
       </c>
       <c r="EW3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EX3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -2752,12 +2767,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9394.568</t>
+          <t>3566.476</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2767,7 +2782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>227.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2782,12 +2797,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2817,7 +2832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>16.66666666666667</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2832,12 +2847,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2862,17 +2877,17 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -2897,7 +2912,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>強勢</t>
+          <t>盤整</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -2962,12 +2977,12 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>-2803202.0</t>
+          <t>-1923859.0</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -2977,17 +2992,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13.97</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>-8.70</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -3062,349 +3077,349 @@
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>244.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>239.99</t>
+          <t>244.15</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>-0.00889607763849587</t>
+          <t>238.79</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>-0.01094091903719907</t>
+          <t>-0.01682793437105601</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>-0.0008169100377820593</t>
+          <t>-0.00781732153877801</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-46.67</t>
+          <t>-0.002145703484213723</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-202.54</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>2026/09/22</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>3643317979.330111</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>2253583542.0</t>
+          <t>3627289414.878082</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>2781360805.0</t>
+          <t>818668875.0</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>2402325737.6</t>
+          <t>1942561898.2</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>1530269322.9</t>
+          <t>2030416565.4</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>1342235944.68</t>
+          <t>1581456057.866667</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>224312411.2117022</t>
+          <t>1304527148.2</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>143115566.5815876</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
           <t>2026/10/16</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
-        <is>
-          <t>-9.80</t>
-        </is>
-      </c>
       <c r="CP4" t="inlineStr">
         <is>
+          <t>-10.78</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
           <t>啟碁</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>啟碁</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="CS4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
       <c r="CU4" t="inlineStr">
         <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
           <t>2.391556252540383</t>
         </is>
       </c>
-      <c r="CV4" t="inlineStr">
+      <c r="CW4" t="inlineStr">
         <is>
           <t>64.04751148579548</t>
         </is>
       </c>
-      <c r="CW4" t="inlineStr">
+      <c r="CX4" t="inlineStr">
         <is>
           <t>40.91440689091394</t>
         </is>
       </c>
-      <c r="CX4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="DB4" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
           <t>81.57</t>
         </is>
       </c>
-      <c r="DC4" t="inlineStr">
-        <is>
-          <t>25.19</t>
-        </is>
-      </c>
       <c r="DD4" t="inlineStr">
         <is>
+          <t>25.9</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
           <t>13.00</t>
         </is>
       </c>
-      <c r="DE4" t="inlineStr">
+      <c r="DF4" t="inlineStr">
         <is>
           <t>5.25</t>
         </is>
       </c>
-      <c r="DF4" t="inlineStr">
-        <is>
-          <t>83.28</t>
-        </is>
-      </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>111191</t>
+          <t>84.29</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
+          <t>114334</t>
+        </is>
+      </c>
+      <c r="DI4" t="inlineStr">
+        <is>
           <t>無線通訊產品96.85%、其他3.15% (2025年)</t>
         </is>
       </c>
-      <c r="DI4" t="inlineStr">
+      <c r="DJ4" t="inlineStr">
         <is>
           <t>啟碁-通信網路業-上市</t>
         </is>
       </c>
-      <c r="DJ4" t="inlineStr">
+      <c r="DK4" t="inlineStr">
         <is>
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="DK4" t="inlineStr">
-        <is>
-          <t>248.0</t>
-        </is>
-      </c>
       <c r="DL4" t="inlineStr">
         <is>
-          <t>250.5</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>229.5</t>
+          <t>236.5</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>226.5</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
+          <t>227.5</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
           <t>74.05</t>
         </is>
       </c>
-      <c r="DP4" t="inlineStr">
+      <c r="DQ4" t="inlineStr">
         <is>
           <t>** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 太空衛星科技 - 天線/射頻基頻</t>
         </is>
       </c>
-      <c r="DQ4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="DR4" t="inlineStr">
         <is>
-          <t>1.817562937045008</t>
+          <t>False</t>
         </is>
       </c>
       <c r="DS4" t="inlineStr">
         <is>
+          <t>1.228337574437859</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="DT4" t="inlineStr">
+      <c r="DU4" t="inlineStr">
         <is>
           <t>39438.0</t>
         </is>
       </c>
-      <c r="DU4" t="inlineStr">
+      <c r="DV4" t="inlineStr">
         <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="DV4" t="inlineStr">
+      <c r="DW4" t="inlineStr">
         <is>
           <t>2069.0</t>
         </is>
       </c>
-      <c r="DW4" t="inlineStr">
+      <c r="DX4" t="inlineStr">
         <is>
           <t>5.25%</t>
         </is>
       </c>
-      <c r="DX4" t="inlineStr">
+      <c r="DY4" t="inlineStr">
         <is>
           <t>-43.0</t>
         </is>
       </c>
-      <c r="DY4" t="inlineStr">
+      <c r="DZ4" t="inlineStr">
         <is>
           <t>2027.0</t>
         </is>
       </c>
-      <c r="DZ4" t="inlineStr">
+      <c r="EA4" t="inlineStr">
         <is>
           <t>3.39</t>
         </is>
       </c>
-      <c r="EA4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EB4" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="EC4" t="inlineStr">
+      <c r="ED4" t="inlineStr">
         <is>
           <t>1.92375</t>
         </is>
       </c>
-      <c r="ED4" t="inlineStr">
+      <c r="EE4" t="inlineStr">
         <is>
           <t>12.61875</t>
         </is>
       </c>
-      <c r="EE4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EF4" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -3417,64 +3432,64 @@
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EJ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EK4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="EL4" t="inlineStr">
+      <c r="EM4" t="inlineStr">
         <is>
           <t>0.4364406779661019</t>
         </is>
       </c>
-      <c r="EM4" t="inlineStr">
+      <c r="EN4" t="inlineStr">
         <is>
           <t>-0.7599999999999998</t>
         </is>
       </c>
-      <c r="EN4" t="inlineStr">
+      <c r="EO4" t="inlineStr">
         <is>
           <t>-0.05523255813953487</t>
         </is>
       </c>
-      <c r="EO4" t="inlineStr">
+      <c r="EP4" t="inlineStr">
         <is>
           <t>2.36</t>
         </is>
       </c>
-      <c r="EP4" t="inlineStr">
+      <c r="EQ4" t="inlineStr">
         <is>
           <t>2.29126213592233</t>
         </is>
       </c>
-      <c r="EQ4" t="inlineStr">
+      <c r="ER4" t="inlineStr">
         <is>
           <t>1.449999999999999</t>
         </is>
       </c>
-      <c r="ER4" t="inlineStr">
+      <c r="ES4" t="inlineStr">
         <is>
           <t>0.1255411255411254</t>
         </is>
       </c>
-      <c r="ES4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="ET4" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -3482,15 +3497,20 @@
       </c>
       <c r="EU4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EV4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EW4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EX4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -3519,12 +3539,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33736.166</t>
+          <t>9365.342</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3534,7 +3554,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>262.5</t>
+          <t>269.5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3549,12 +3569,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -3584,7 +3604,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>26.66666666666667</t>
+          <t>17.33333333333333</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3599,7 +3619,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -3639,17 +3659,17 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -3659,7 +3679,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>弱勢</t>
+          <t>盤整</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -3729,12 +3749,12 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>-11872285.0</t>
+          <t>-2598628.0</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -3744,17 +3764,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -3829,349 +3849,349 @@
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>1,524</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>33736</t>
+          <t>332</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>54.05</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>41.19</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>291.02</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>271.32</t>
+          <t>285.23</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>-0.007047477744807296</t>
+          <t>272.47</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.01296653232871925</t>
+          <t>0.007426661715558946</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>-0.006655858008362658</t>
+          <t>-0.01286931303244521</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-184.81</t>
+          <t>-0.007222415593456266</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-14683.88</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>2026/08/10</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>9945965614.156078</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9146457935.0</t>
+          <t>9918006059.613699</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>6279083229.2</t>
+          <t>2533120140.0</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>9803814363.0</t>
+          <t>5702386718.0</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>8236146970.033334</t>
+          <t>7390263535.0</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>7282218608.42</t>
+          <t>8296192048.866667</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>124308180.0817399</t>
+          <t>7206485611.72</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-181941392.9124753</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
           <t>2026/09/18</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
-        <is>
-          <t>-9.95</t>
-        </is>
-      </c>
       <c r="CP5" t="inlineStr">
         <is>
+          <t>-7.55</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
           <t>京元電子</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>京元電子</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>半導體業</t>
         </is>
       </c>
-      <c r="CS5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="CT5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>1.59</t>
         </is>
       </c>
-      <c r="CU5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>-0.2114902773049536</t>
         </is>
       </c>
-      <c r="CV5" t="inlineStr">
+      <c r="CW5" t="inlineStr">
         <is>
           <t>24.45997070281453</t>
         </is>
       </c>
-      <c r="CW5" t="inlineStr">
+      <c r="CX5" t="inlineStr">
         <is>
           <t>34.07545706498113</t>
         </is>
       </c>
-      <c r="CX5" t="inlineStr">
+      <c r="CY5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CY5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="DB5" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="DC5" t="inlineStr">
+        <is>
           <t>8.68</t>
         </is>
       </c>
-      <c r="DC5" t="inlineStr">
-        <is>
-          <t>34.4</t>
-        </is>
-      </c>
       <c r="DD5" t="inlineStr">
         <is>
+          <t>36.37</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
           <t>39.49</t>
         </is>
       </c>
-      <c r="DE5" t="inlineStr">
+      <c r="DF5" t="inlineStr">
         <is>
           <t>25.38</t>
         </is>
       </c>
-      <c r="DF5" t="inlineStr">
-        <is>
-          <t>48.71</t>
-        </is>
-      </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>337019</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
+          <t>356277</t>
+        </is>
+      </c>
+      <c r="DI5" t="inlineStr">
+        <is>
           <t>積體電路(IC)測試66.43%、晶圓測試30.56%、其他3.01% (2025年)</t>
         </is>
       </c>
-      <c r="DI5" t="inlineStr">
+      <c r="DJ5" t="inlineStr">
         <is>
           <t>京元電子-半導體業-上市</t>
         </is>
       </c>
-      <c r="DJ5" t="inlineStr">
+      <c r="DK5" t="inlineStr">
         <is>
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="DK5" t="inlineStr">
-        <is>
-          <t>281.5</t>
-        </is>
-      </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>284.5</t>
+          <t>276.5</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>262.0</t>
+          <t>276.5</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>262.5</t>
+          <t>268.0</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
+          <t>269.5</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
           <t>51.25</t>
         </is>
       </c>
-      <c r="DP5" t="inlineStr">
+      <c r="DQ5" t="inlineStr">
         <is>
           <t>** 半導體 - IC封裝測試</t>
         </is>
       </c>
-      <c r="DQ5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DT5" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="DT5" t="inlineStr">
+      <c r="DU5" t="inlineStr">
         <is>
           <t>11142.0</t>
         </is>
       </c>
-      <c r="DU5" t="inlineStr">
+      <c r="DV5" t="inlineStr">
         <is>
           <t>39.49</t>
         </is>
       </c>
-      <c r="DV5" t="inlineStr">
+      <c r="DW5" t="inlineStr">
         <is>
           <t>2828.0</t>
         </is>
       </c>
-      <c r="DW5" t="inlineStr">
+      <c r="DX5" t="inlineStr">
         <is>
           <t>25.38%</t>
         </is>
       </c>
-      <c r="DX5" t="inlineStr">
+      <c r="DY5" t="inlineStr">
         <is>
           <t>248.0</t>
         </is>
       </c>
-      <c r="DY5" t="inlineStr">
+      <c r="DZ5" t="inlineStr">
         <is>
           <t>3076.0</t>
         </is>
       </c>
-      <c r="DZ5" t="inlineStr">
+      <c r="EA5" t="inlineStr">
         <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EA5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EB5" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="EC5" t="inlineStr">
+      <c r="ED5" t="inlineStr">
         <is>
           <t>2.07625</t>
         </is>
       </c>
-      <c r="ED5" t="inlineStr">
+      <c r="EE5" t="inlineStr">
         <is>
           <t>36.5775</t>
         </is>
       </c>
-      <c r="EE5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EF5" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -4179,7 +4199,7 @@
       </c>
       <c r="EG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EH5" t="inlineStr">
@@ -4189,59 +4209,59 @@
       </c>
       <c r="EI5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EJ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EK5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
           <t>0.1699999999999999</t>
         </is>
       </c>
-      <c r="EL5" t="inlineStr">
+      <c r="EM5" t="inlineStr">
         <is>
           <t>0.09090909090909083</t>
         </is>
       </c>
-      <c r="EM5" t="inlineStr">
+      <c r="EN5" t="inlineStr">
         <is>
           <t>-0.25</t>
         </is>
       </c>
-      <c r="EN5" t="inlineStr">
+      <c r="EO5" t="inlineStr">
         <is>
           <t>-0.006290890790135895</t>
         </is>
       </c>
-      <c r="EO5" t="inlineStr">
+      <c r="EP5" t="inlineStr">
         <is>
           <t>0.26</t>
         </is>
       </c>
-      <c r="EP5" t="inlineStr">
+      <c r="EQ5" t="inlineStr">
         <is>
           <t>0.146067415730337</t>
         </is>
       </c>
-      <c r="EQ5" t="inlineStr">
+      <c r="ER5" t="inlineStr">
         <is>
           <t>3.950000000000003</t>
         </is>
       </c>
-      <c r="ER5" t="inlineStr">
+      <c r="ES5" t="inlineStr">
         <is>
           <t>0.1111423747889702</t>
         </is>
       </c>
-      <c r="ES5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="ET5" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -4249,15 +4269,20 @@
       </c>
       <c r="EU5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EV5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EW5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EX5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -4286,12 +4311,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29796.59</t>
+          <t>18257.916</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4301,7 +4326,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2385.0</t>
+          <t>2415.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4316,12 +4341,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -4346,12 +4371,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4366,12 +4391,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -4406,22 +4431,22 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -4496,12 +4521,12 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>-10149175.0</t>
+          <t>162942.0</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -4511,17 +4536,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>17.42</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -4596,349 +4621,349 @@
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>6,965</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>29797</t>
+          <t>2,009</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21867</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>35.64</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>2485.25</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>2441.5</t>
+          <t>2475.5</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>-0.004543577034283319</t>
+          <t>2441.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>-0.008077544426494332</t>
+          <t>0.0008309098462817577</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>-0.001907630522088311</t>
+          <t>-0.003087054949578061</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-206.41</t>
+          <t>-0.001210409521888223</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-624.80</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>-13.96</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>-1.93</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>2026/09/21</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>93610213427.75967</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>71536783195.0</t>
+          <t>93614313192.34932</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>72402428869.2</t>
+          <t>43964130370.0</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>79581552737.0</t>
+          <t>65054135136.2</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>62995250469.53333</t>
+          <t>76334561018.9</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>57191785082.06</t>
+          <t>63791533970.8</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>3501308707.157251</t>
+          <t>57869754288.66</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2362138979.269216</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
           <t>2026/09/01</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
-        <is>
-          <t>-2.25</t>
-        </is>
-      </c>
       <c r="CP6" t="inlineStr">
         <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
           <t>台積電</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>台積電</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>半導體業</t>
         </is>
       </c>
-      <c r="CS6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
       <c r="CU6" t="inlineStr">
         <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
           <t>-0.5726315925897248</t>
         </is>
       </c>
-      <c r="CV6" t="inlineStr">
+      <c r="CW6" t="inlineStr">
         <is>
           <t>54.64861207105231</t>
         </is>
       </c>
-      <c r="CW6" t="inlineStr">
+      <c r="CX6" t="inlineStr">
         <is>
           <t>41.10669499309349</t>
         </is>
       </c>
-      <c r="CX6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="DB6" t="inlineStr">
         <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="DC6" t="inlineStr">
+        <is>
           <t>48.99</t>
         </is>
       </c>
-      <c r="DC6" t="inlineStr">
-        <is>
-          <t>27.65</t>
-        </is>
-      </c>
       <c r="DD6" t="inlineStr">
         <is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
           <t>67.72</t>
         </is>
       </c>
-      <c r="DE6" t="inlineStr">
+      <c r="DF6" t="inlineStr">
         <is>
           <t>60.34</t>
         </is>
       </c>
-      <c r="DF6" t="inlineStr">
-        <is>
-          <t>48.71</t>
-        </is>
-      </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>61848702</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
+          <t>62885997</t>
+        </is>
+      </c>
+      <c r="DI6" t="inlineStr">
+        <is>
           <t>晶圓-5奈米30.98%、晶圓-3奈米20.85%、其他14.08%、晶圓-7奈米12.06%、晶圓-28奈米5.91%、晶圓-16奈米5.66%、晶圓-65奈米3.16%、晶圓-40及45奈米2.51%、晶圓-0.15及0.18微米2.32%、晶圓-0.11及0.13微米1.28%、晶圓-90奈米0.56%、晶圓-0.25微米以上0.51%、晶圓-20奈米0.11% (2025年)</t>
         </is>
       </c>
-      <c r="DI6" t="inlineStr">
+      <c r="DJ6" t="inlineStr">
         <is>
           <t>台積電-半導體業-上市</t>
         </is>
       </c>
-      <c r="DJ6" t="inlineStr">
+      <c r="DK6" t="inlineStr">
         <is>
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="DK6" t="inlineStr">
-        <is>
-          <t>2435.0</t>
-        </is>
-      </c>
       <c r="DL6" t="inlineStr">
         <is>
-          <t>2435.0</t>
+          <t>2420.0</t>
         </is>
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>2385.0</t>
+          <t>2425.0</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>2385.0</t>
+          <t>2390.0</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
+          <t>2415.0</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
           <t>248.05</t>
         </is>
       </c>
-      <c r="DP6" t="inlineStr">
+      <c r="DQ6" t="inlineStr">
         <is>
           <t>** 半導體 - 晶圓製造</t>
         </is>
       </c>
-      <c r="DQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="DR6" t="inlineStr">
         <is>
-          <t>1.149331550070053</t>
+          <t>False</t>
         </is>
       </c>
       <c r="DS6" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="DT6" t="inlineStr">
+      <c r="DU6" t="inlineStr">
         <is>
           <t>1270380.0</t>
         </is>
       </c>
-      <c r="DU6" t="inlineStr">
+      <c r="DV6" t="inlineStr">
         <is>
           <t>67.72</t>
         </is>
       </c>
-      <c r="DV6" t="inlineStr">
+      <c r="DW6" t="inlineStr">
         <is>
           <t>766603.0</t>
         </is>
       </c>
-      <c r="DW6" t="inlineStr">
+      <c r="DX6" t="inlineStr">
         <is>
           <t>60.34%</t>
         </is>
       </c>
-      <c r="DX6" t="inlineStr">
+      <c r="DY6" t="inlineStr">
         <is>
           <t>95827.0</t>
         </is>
       </c>
-      <c r="DY6" t="inlineStr">
+      <c r="DZ6" t="inlineStr">
         <is>
           <t>862430.0</t>
         </is>
       </c>
-      <c r="DZ6" t="inlineStr">
+      <c r="EA6" t="inlineStr">
         <is>
           <t>27.25</t>
         </is>
       </c>
-      <c r="EA6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EB6" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="EC6" t="inlineStr">
+      <c r="ED6" t="inlineStr">
         <is>
           <t>17.82375</t>
         </is>
       </c>
-      <c r="ED6" t="inlineStr">
+      <c r="EE6" t="inlineStr">
         <is>
           <t>61.24875</t>
         </is>
       </c>
-      <c r="EE6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EF6" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -4966,49 +4991,49 @@
       </c>
       <c r="EK6" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
+        <is>
           <t>5.170000000000002</t>
         </is>
       </c>
-      <c r="EL6" t="inlineStr">
+      <c r="EM6" t="inlineStr">
         <is>
           <t>0.2341485507246377</t>
         </is>
       </c>
-      <c r="EM6" t="inlineStr">
+      <c r="EN6" t="inlineStr">
         <is>
           <t>1.469999999999999</t>
         </is>
       </c>
-      <c r="EN6" t="inlineStr">
+      <c r="EO6" t="inlineStr">
         <is>
           <t>0.02218867924528301</t>
         </is>
       </c>
-      <c r="EO6" t="inlineStr">
+      <c r="EP6" t="inlineStr">
         <is>
           <t>11.89</t>
         </is>
       </c>
-      <c r="EP6" t="inlineStr">
+      <c r="EQ6" t="inlineStr">
         <is>
           <t>0.7740885416666667</t>
         </is>
       </c>
-      <c r="EQ6" t="inlineStr">
+      <c r="ER6" t="inlineStr">
         <is>
           <t>9.100000000000001</t>
         </is>
       </c>
-      <c r="ER6" t="inlineStr">
+      <c r="ES6" t="inlineStr">
         <is>
           <t>0.1552371204367111</t>
         </is>
       </c>
-      <c r="ES6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="ET6" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -5025,6 +5050,11 @@
         </is>
       </c>
       <c r="EW6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EX6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -5053,12 +5083,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-10.25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>88575.441</t>
+          <t>350078.013</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5068,7 +5098,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -5083,12 +5113,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -5098,7 +5128,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -5118,7 +5148,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>41.33333333333334</t>
+          <t>32.66666666666666</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -5133,7 +5163,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -5178,29 +5208,29 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
           <t>盤整</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
       <c r="AI7" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -5263,12 +5293,12 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>-16155711.0</t>
+          <t>-158489367.0</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -5278,17 +5308,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>54.13</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -5363,349 +5393,349 @@
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>2,229</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>88575</t>
+          <t>2,722</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>90788</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>-11.52</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>145.43</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>136.78</t>
+          <t>140.02</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>-0.01225114854517606</t>
+          <t>136.69</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>-0.01669085631349787</t>
+          <t>-0.01822503961965127</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>-0.01071428571428568</t>
+          <t>-0.01980952380952372</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-705.29</t>
+          <t>-0.01356111306798158</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-110.18</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>-2.76</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>19118870924.68094</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>11280077221.0</t>
+          <t>19242377844.18493</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>12802068643.8</t>
+          <t>40961075315.0</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>15445296221.5</t>
+          <t>17815209467.6</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>23543115677.63334</t>
+          <t>17705943304.5</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>21789861971.9</t>
+          <t>22561480943.6</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>-1340654373.939099</t>
+          <t>22222814634.22</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1346099116.809028</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
-        <is>
-          <t>-11.62</t>
-        </is>
-      </c>
       <c r="CP7" t="inlineStr">
         <is>
+          <t>-18.66</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>聯電</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>半導體業</t>
         </is>
       </c>
-      <c r="CS7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="CT7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="CU7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>1.220979769684061</t>
         </is>
       </c>
-      <c r="CV7" t="inlineStr">
+      <c r="CW7" t="inlineStr">
         <is>
           <t>27.21537799512475</t>
         </is>
       </c>
-      <c r="CW7" t="inlineStr">
+      <c r="CX7" t="inlineStr">
         <is>
           <t>16.08366865980834</t>
         </is>
       </c>
-      <c r="CX7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DB7" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="DC7" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="DD7" t="inlineStr">
         <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>33.95</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>25.11</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>50.02</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>1608972</t>
+        </is>
+      </c>
+      <c r="DI7" t="inlineStr">
+        <is>
+          <t>晶圓95.81%、其他4.19% (2025年)</t>
+        </is>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>聯電-半導體業-上市</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>半導體業右上上市</t>
+        </is>
+      </c>
+      <c r="DL7" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>115.5</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>115.5</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
+          <t>** 半導體 - 晶圓製造</t>
+        </is>
+      </c>
+      <c r="DR7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DT7" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="DU7" t="inlineStr">
+        <is>
+          <t>68733.0</t>
+        </is>
+      </c>
+      <c r="DV7" t="inlineStr">
+        <is>
           <t>32.48</t>
         </is>
       </c>
-      <c r="DE7" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
-      </c>
-      <c r="DF7" t="inlineStr">
-        <is>
-          <t>48.71</t>
-        </is>
-      </c>
-      <c r="DG7" t="inlineStr">
-        <is>
-          <t>1577547</t>
-        </is>
-      </c>
-      <c r="DH7" t="inlineStr">
-        <is>
-          <t>晶圓95.81%、其他4.19% (2025年)</t>
-        </is>
-      </c>
-      <c r="DI7" t="inlineStr">
-        <is>
-          <t>聯電-半導體業-上市</t>
-        </is>
-      </c>
-      <c r="DJ7" t="inlineStr">
-        <is>
-          <t>半導體業右上上市</t>
-        </is>
-      </c>
-      <c r="DK7" t="inlineStr">
-        <is>
-          <t>129.0</t>
-        </is>
-      </c>
-      <c r="DL7" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="DM7" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="DN7" t="inlineStr">
-        <is>
-          <t>125.5</t>
-        </is>
-      </c>
-      <c r="DO7" t="inlineStr">
-        <is>
-          <t>35.38</t>
-        </is>
-      </c>
-      <c r="DP7" t="inlineStr">
-        <is>
-          <t>** 半導體 - 晶圓製造</t>
-        </is>
-      </c>
-      <c r="DQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="DR7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="DS7" t="inlineStr">
-        <is>
-          <t>115.2Q</t>
-        </is>
-      </c>
-      <c r="DT7" t="inlineStr">
-        <is>
-          <t>68733.0</t>
-        </is>
-      </c>
-      <c r="DU7" t="inlineStr">
-        <is>
-          <t>32.48</t>
-        </is>
-      </c>
-      <c r="DV7" t="inlineStr">
+      <c r="DW7" t="inlineStr">
         <is>
           <t>14950.0</t>
         </is>
       </c>
-      <c r="DW7" t="inlineStr">
+      <c r="DX7" t="inlineStr">
         <is>
           <t>21.75%</t>
         </is>
       </c>
-      <c r="DX7" t="inlineStr">
+      <c r="DY7" t="inlineStr">
         <is>
           <t>30236.0</t>
         </is>
       </c>
-      <c r="DY7" t="inlineStr">
+      <c r="DZ7" t="inlineStr">
         <is>
           <t>45186.0</t>
         </is>
       </c>
-      <c r="DZ7" t="inlineStr">
+      <c r="EA7" t="inlineStr">
         <is>
           <t>3.39</t>
         </is>
       </c>
-      <c r="EA7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EB7" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr">
+        <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="EC7" t="inlineStr">
+      <c r="ED7" t="inlineStr">
         <is>
           <t>1.2325</t>
         </is>
       </c>
-      <c r="ED7" t="inlineStr">
+      <c r="EE7" t="inlineStr">
         <is>
           <t>30.21625</t>
         </is>
       </c>
-      <c r="EE7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EF7" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -5718,64 +5748,64 @@
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EJ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EK7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="EL7" t="inlineStr">
+        <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="EL7" t="inlineStr">
+      <c r="EM7" t="inlineStr">
         <is>
           <t>1.627906976744186</t>
         </is>
       </c>
-      <c r="EM7" t="inlineStr">
+      <c r="EN7" t="inlineStr">
         <is>
           <t>3.289999999999996</t>
         </is>
       </c>
-      <c r="EN7" t="inlineStr">
+      <c r="EO7" t="inlineStr">
         <is>
           <t>0.1127098321342923</t>
         </is>
       </c>
-      <c r="EO7" t="inlineStr">
+      <c r="EP7" t="inlineStr">
         <is>
           <t>2.68</t>
         </is>
       </c>
-      <c r="EP7" t="inlineStr">
+      <c r="EQ7" t="inlineStr">
         <is>
           <t>3.774647887323944</t>
         </is>
       </c>
-      <c r="EQ7" t="inlineStr">
+      <c r="ER7" t="inlineStr">
         <is>
           <t>3.759999999999998</t>
         </is>
       </c>
-      <c r="ER7" t="inlineStr">
+      <c r="ES7" t="inlineStr">
         <is>
           <t>0.1309192200557103</t>
         </is>
       </c>
-      <c r="ES7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="ET7" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -5792,6 +5822,11 @@
         </is>
       </c>
       <c r="EW7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EX7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -5820,12 +5855,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>156.42</t>
+          <t>80.552</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5835,7 +5870,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -5855,7 +5890,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -5900,12 +5935,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -5950,12 +5985,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -6030,7 +6065,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-17860.0</t>
+          <t>-5540.0</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -6045,17 +6080,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -6130,349 +6165,349 @@
       </c>
       <c r="BO8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>18.49</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>-0.002229654403567594</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>-0.0002782415136339811</t>
+          <t>-0.002244668911335679</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>-0.0006948304613674239</t>
+          <t>-0.001953670108847172</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>-0.001114206128133732</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
           <t>-0.16</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>2026/10/08</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>11088725.76381215</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>2784759.0</t>
+          <t>11018164.30684932</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>1401879.2</t>
+          <t>1430473.0</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>1906496.1</t>
+          <t>1714107.8</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>2891107.566666667</t>
+          <t>1681710.0</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>2709121.96</t>
+          <t>2158277.7</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>-202780.4576974912</t>
+          <t>2652340.06</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-176583.2125559539</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
           <t>2026/09/02</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
-        <is>
-          <t>-6.56</t>
-        </is>
-      </c>
       <c r="CP8" t="inlineStr">
         <is>
+          <t>-7.09</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
           <t>橋椿</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>橋椿</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>居家生活</t>
         </is>
       </c>
-      <c r="CS8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="CT8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>0.32</t>
         </is>
       </c>
-      <c r="CU8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>-10.10297295235127</t>
         </is>
       </c>
-      <c r="CV8" t="inlineStr">
+      <c r="CW8" t="inlineStr">
         <is>
           <t>-5.02770684087132</t>
         </is>
       </c>
-      <c r="CW8" t="inlineStr">
+      <c r="CX8" t="inlineStr">
         <is>
           <t>12.15292366833959</t>
         </is>
       </c>
-      <c r="CX8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
           <t>0.46</t>
         </is>
       </c>
-      <c r="DA8" t="inlineStr">
-        <is>
-          <t>5.62</t>
-        </is>
-      </c>
       <c r="DB8" t="inlineStr">
         <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="DC8" t="inlineStr">
+        <is>
           <t>9.29</t>
         </is>
       </c>
-      <c r="DC8" t="inlineStr">
-        <is>
-          <t>63.57</t>
-        </is>
-      </c>
       <c r="DD8" t="inlineStr">
         <is>
+          <t>63.75</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
           <t>11.60</t>
         </is>
       </c>
-      <c r="DE8" t="inlineStr">
+      <c r="DF8" t="inlineStr">
         <is>
           <t>3.90</t>
         </is>
       </c>
-      <c r="DF8" t="inlineStr">
-        <is>
-          <t>19.87</t>
-        </is>
-      </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
+          <t>3570</t>
+        </is>
+      </c>
+      <c r="DI8" t="inlineStr">
+        <is>
           <t>水龍頭零配件56.01%、水龍頭組裝件33.50%、其他10.49% (2025年)</t>
         </is>
       </c>
-      <c r="DI8" t="inlineStr">
+      <c r="DJ8" t="inlineStr">
         <is>
           <t>橋椿-居家生活-上市</t>
         </is>
       </c>
-      <c r="DJ8" t="inlineStr">
+      <c r="DK8" t="inlineStr">
         <is>
           <t>居家生活右下上市</t>
         </is>
       </c>
-      <c r="DK8" t="inlineStr">
+      <c r="DL8" t="inlineStr">
         <is>
           <t>17.85</t>
         </is>
       </c>
-      <c r="DL8" t="inlineStr">
+      <c r="DM8" t="inlineStr">
         <is>
           <t>17.85</t>
         </is>
       </c>
-      <c r="DM8" t="inlineStr">
+      <c r="DN8" t="inlineStr">
         <is>
           <t>17.7</t>
         </is>
       </c>
-      <c r="DN8" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
       <c r="DO8" t="inlineStr">
         <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
           <t>38.31</t>
         </is>
       </c>
-      <c r="DP8" t="inlineStr">
+      <c r="DQ8" t="inlineStr">
         <is>
           <t>** 其他 - 其他</t>
         </is>
       </c>
-      <c r="DQ8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="DR8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="DS8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DT8" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="DT8" t="inlineStr">
+      <c r="DU8" t="inlineStr">
         <is>
           <t>1857.0</t>
         </is>
       </c>
-      <c r="DU8" t="inlineStr">
+      <c r="DV8" t="inlineStr">
         <is>
           <t>11.6</t>
         </is>
       </c>
-      <c r="DV8" t="inlineStr">
+      <c r="DW8" t="inlineStr">
         <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="DW8" t="inlineStr">
+      <c r="DX8" t="inlineStr">
         <is>
           <t>3.90%</t>
         </is>
       </c>
-      <c r="DX8" t="inlineStr">
+      <c r="DY8" t="inlineStr">
         <is>
           <t>-28.0</t>
         </is>
       </c>
-      <c r="DY8" t="inlineStr">
+      <c r="DZ8" t="inlineStr">
         <is>
           <t>44.0</t>
         </is>
       </c>
-      <c r="DZ8" t="inlineStr">
+      <c r="EA8" t="inlineStr">
         <is>
           <t>0.19</t>
         </is>
       </c>
-      <c r="EA8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="EB8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="EC8" t="inlineStr">
+      <c r="ED8" t="inlineStr">
         <is>
           <t>0.18875</t>
         </is>
       </c>
-      <c r="ED8" t="inlineStr">
+      <c r="EE8" t="inlineStr">
         <is>
           <t>10.89125</t>
         </is>
       </c>
-      <c r="EE8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EF8" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -6480,7 +6515,7 @@
       </c>
       <c r="EG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EH8" t="inlineStr">
@@ -6490,59 +6525,59 @@
       </c>
       <c r="EI8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EJ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EK8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="EL8" t="inlineStr">
+        <is>
           <t>0.19</t>
         </is>
       </c>
-      <c r="EL8" t="inlineStr">
+      <c r="EM8" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="EM8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EN8" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EO8" t="inlineStr">
+        <is>
           <t>0.09433962264150941</t>
         </is>
       </c>
-      <c r="EO8" t="inlineStr">
+      <c r="EP8" t="inlineStr">
         <is>
           <t>0.07</t>
         </is>
       </c>
-      <c r="EP8" t="inlineStr">
+      <c r="EQ8" t="inlineStr">
         <is>
           <t>0.5833333333333335</t>
         </is>
       </c>
-      <c r="EQ8" t="inlineStr">
+      <c r="ER8" t="inlineStr">
         <is>
           <t>3.279999999999999</t>
         </is>
       </c>
-      <c r="ER8" t="inlineStr">
+      <c r="ES8" t="inlineStr">
         <is>
           <t>0.3942307692307692</t>
         </is>
       </c>
-      <c r="ES8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="ET8" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -6559,6 +6594,11 @@
         </is>
       </c>
       <c r="EW8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EX8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -6587,12 +6627,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6622,7 +6662,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -6672,7 +6712,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -6712,7 +6752,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -6797,12 +6837,12 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>-1000.0</t>
+          <t>-2000.0</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -6812,12 +6852,12 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -6897,357 +6937,357 @@
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>-0.0004405286343611703</t>
+          <t>22.97</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-0.001103996467211599</t>
+          <t>-0.0008857395925597755</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>-0.001421386398425595</t>
+          <t>0.0002210433244915766</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-0.001097574360662823</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
+          <t>-3.69</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>2026/10/01</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>1665.120165745856</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>452.0</t>
+          <t>1655.301369863014</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>377.6</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>452.9</t>
+          <t>332.4</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>435.1333333333333</t>
+          <t>337.2</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>462.4</t>
+          <t>436.6</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>-10.12558910795111</t>
+          <t>447.5</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13.77528335671957</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
           <t>2026/08/10</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>-4.45</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>宏佳騰</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>宏佳騰</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="CS9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="CT9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="CU9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>-14.61727178476478</t>
         </is>
       </c>
-      <c r="CV9" t="inlineStr">
+      <c r="CW9" t="inlineStr">
         <is>
           <t>32.07138736430949</t>
         </is>
       </c>
-      <c r="CW9" t="inlineStr">
+      <c r="CX9" t="inlineStr">
         <is>
           <t>27.88148209128266</t>
         </is>
       </c>
-      <c r="CX9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
       <c r="CY9" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CZ9" t="inlineStr">
+      <c r="DA9" t="inlineStr">
         <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="DA9" t="inlineStr">
+      <c r="DB9" t="inlineStr">
         <is>
           <t>2.22</t>
         </is>
       </c>
-      <c r="DB9" t="inlineStr">
+      <c r="DC9" t="inlineStr">
         <is>
           <t>6.11</t>
         </is>
       </c>
-      <c r="DC9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DD9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
           <t>20.97</t>
         </is>
       </c>
-      <c r="DE9" t="inlineStr">
+      <c r="DF9" t="inlineStr">
         <is>
           <t>-7.57</t>
         </is>
       </c>
-      <c r="DF9" t="inlineStr">
-        <is>
-          <t>47.69</t>
-        </is>
-      </c>
       <c r="DG9" t="inlineStr">
         <is>
+          <t>48.47</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
           <t>1647</t>
         </is>
       </c>
-      <c r="DH9" t="inlineStr">
+      <c r="DI9" t="inlineStr">
         <is>
           <t>ATV/ UTV71.35%、摩托車13.07%、電動機車8.10%、零組件及其他7.48% (2025年)</t>
         </is>
       </c>
-      <c r="DI9" t="inlineStr">
+      <c r="DJ9" t="inlineStr">
         <is>
           <t>宏佳騰-電機機械-上櫃</t>
         </is>
       </c>
-      <c r="DJ9" t="inlineStr">
+      <c r="DK9" t="inlineStr">
         <is>
           <t>電機機械右下上櫃</t>
         </is>
       </c>
-      <c r="DK9" t="inlineStr">
+      <c r="DL9" t="inlineStr">
         <is>
           <t>22.85</t>
         </is>
       </c>
-      <c r="DL9" t="inlineStr">
+      <c r="DM9" t="inlineStr">
         <is>
           <t>22.85</t>
         </is>
       </c>
-      <c r="DM9" t="inlineStr">
+      <c r="DN9" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="DN9" t="inlineStr">
+      <c r="DO9" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="DO9" t="inlineStr">
+      <c r="DP9" t="inlineStr">
         <is>
           <t>25.66</t>
         </is>
       </c>
-      <c r="DP9" t="inlineStr">
+      <c r="DQ9" t="inlineStr">
         <is>
           <t>** 休閒娛樂 - 休閒車業** 電動車輛產業 - 電動汽車、電動機車、電動自行車</t>
         </is>
       </c>
-      <c r="DQ9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="DR9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="DS9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="DT9" t="inlineStr">
+      <c r="DU9" t="inlineStr">
         <is>
           <t>440.0</t>
         </is>
       </c>
-      <c r="DU9" t="inlineStr">
+      <c r="DV9" t="inlineStr">
         <is>
           <t>20.97</t>
         </is>
       </c>
-      <c r="DV9" t="inlineStr">
+      <c r="DW9" t="inlineStr">
         <is>
           <t>-33.0</t>
         </is>
       </c>
-      <c r="DW9" t="inlineStr">
+      <c r="DX9" t="inlineStr">
         <is>
           <t>-7.57%</t>
         </is>
       </c>
-      <c r="DX9" t="inlineStr">
+      <c r="DY9" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="DY9" t="inlineStr">
+      <c r="DZ9" t="inlineStr">
         <is>
           <t>-24.0</t>
         </is>
       </c>
-      <c r="DZ9" t="inlineStr">
+      <c r="EA9" t="inlineStr">
         <is>
           <t>-0.19</t>
         </is>
       </c>
-      <c r="EA9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="EB9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="EC9" t="inlineStr">
+      <c r="ED9" t="inlineStr">
         <is>
           <t>0.10625</t>
         </is>
       </c>
-      <c r="ED9" t="inlineStr">
+      <c r="EE9" t="inlineStr">
         <is>
           <t>20.42875</t>
         </is>
       </c>
-      <c r="EE9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EH9" t="inlineStr">
@@ -7267,65 +7307,70 @@
       </c>
       <c r="EK9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
+        <is>
           <t>-0.47</t>
         </is>
       </c>
-      <c r="EL9" t="inlineStr">
+      <c r="EM9" t="inlineStr">
         <is>
           <t>-1.678571428571428</t>
         </is>
       </c>
-      <c r="EM9" t="inlineStr">
+      <c r="EN9" t="inlineStr">
         <is>
           <t>-1.050000000000001</t>
         </is>
       </c>
-      <c r="EN9" t="inlineStr">
+      <c r="EO9" t="inlineStr">
         <is>
           <t>-0.04768392370572205</t>
         </is>
       </c>
-      <c r="EO9" t="inlineStr">
+      <c r="EP9" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="EP9" t="inlineStr">
+      <c r="EQ9" t="inlineStr">
         <is>
           <t>-0.6984126984126984</t>
         </is>
       </c>
-      <c r="EQ9" t="inlineStr">
+      <c r="ER9" t="inlineStr">
         <is>
           <t>0.1600000000000001</t>
         </is>
       </c>
-      <c r="ER9" t="inlineStr">
+      <c r="ES9" t="inlineStr">
         <is>
           <t>0.007688611244593968</t>
         </is>
       </c>
-      <c r="ES9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="ET9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EU9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EV9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EW9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EX9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -7354,12 +7399,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>844.166</t>
+          <t>1749.174</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -7369,7 +7414,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>615.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -7384,12 +7429,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -7399,7 +7444,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -7489,7 +7534,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -7564,12 +7609,12 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-102028.0</t>
+          <t>-655824.0</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -7579,17 +7624,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-4.80</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -7654,27 +7699,27 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>失效</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -7684,337 +7729,337 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-6.40</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>677.75</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>705.06</t>
+          <t>659.0</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>-0.01060511540860898</t>
+          <t>697.0</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-0.01302980380410368</t>
+          <t>-0.02230239422761549</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>-0.007541367696588086</t>
+          <t>-0.01574555188159343</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>-49.50</t>
+          <t>-0.01021327726043852</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-21.81</t>
+          <t>-47.46</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-31.96</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>-21.68</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>2026/10/12</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>4217213886.522099</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>525637213.0</t>
+          <t>4196030804.272603</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>666219039.6</t>
+          <t>1000492278.0</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>1487829503.9</t>
+          <t>895177741.0</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>997705111.0333333</t>
+          <t>1049009592.9</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>1237594491.4</t>
+          <t>1015050980.0</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>36989409.18136586</t>
+          <t>1217418960.6</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>580179.7072205395</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
           <t>2026/09/03</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
-        <is>
-          <t>-14.82</t>
-        </is>
-      </c>
       <c r="CP10" t="inlineStr">
         <is>
+          <t>-22.02</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="CS10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="CT10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="CU10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>5.85010543057471</t>
         </is>
       </c>
-      <c r="CV10" t="inlineStr">
+      <c r="CW10" t="inlineStr">
         <is>
           <t>7.188148611574929</t>
         </is>
       </c>
-      <c r="CW10" t="inlineStr">
+      <c r="CX10" t="inlineStr">
         <is>
           <t>-0.7314022008951365</t>
         </is>
       </c>
-      <c r="CX10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>19.32</t>
         </is>
       </c>
       <c r="DB10" t="inlineStr">
         <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="DC10" t="inlineStr">
+        <is>
           <t>15.7</t>
         </is>
       </c>
-      <c r="DC10" t="inlineStr">
-        <is>
-          <t>40.25</t>
-        </is>
-      </c>
       <c r="DD10" t="inlineStr">
         <is>
+          <t>38.74</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
           <t>43.50</t>
         </is>
       </c>
-      <c r="DE10" t="inlineStr">
+      <c r="DF10" t="inlineStr">
         <is>
           <t>22.11</t>
         </is>
       </c>
-      <c r="DF10" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
       <c r="DG10" t="inlineStr">
         <is>
-          <t>213693</t>
+          <t>33.83</t>
         </is>
       </c>
       <c r="DH10" t="inlineStr">
         <is>
+          <t>205701</t>
+        </is>
+      </c>
+      <c r="DI10" t="inlineStr">
+        <is>
           <t>變壓器73.61%、其他9.67%、配電盤7.29%、工程承包5.69%、配電器材3.69%、電力0.05% (2025年)</t>
         </is>
       </c>
-      <c r="DI10" t="inlineStr">
+      <c r="DJ10" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="DJ10" t="inlineStr">
+      <c r="DK10" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="DK10" t="inlineStr">
-        <is>
-          <t>633.0</t>
-        </is>
-      </c>
       <c r="DL10" t="inlineStr">
         <is>
-          <t>634.0</t>
+          <t>588.0</t>
         </is>
       </c>
       <c r="DM10" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>590.0</t>
         </is>
       </c>
       <c r="DN10" t="inlineStr">
         <is>
-          <t>615.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="DO10" t="inlineStr">
         <is>
+          <t>563.0</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
           <t>29.14</t>
         </is>
       </c>
-      <c r="DP10" t="inlineStr">
+      <c r="DQ10" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="DQ10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="DR10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="DS10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="DT10" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="DT10" t="inlineStr">
+      <c r="DU10" t="inlineStr">
         <is>
           <t>5456.0</t>
         </is>
       </c>
-      <c r="DU10" t="inlineStr">
+      <c r="DV10" t="inlineStr">
         <is>
           <t>43.5</t>
         </is>
       </c>
-      <c r="DV10" t="inlineStr">
+      <c r="DW10" t="inlineStr">
         <is>
           <t>1206.0</t>
         </is>
       </c>
-      <c r="DW10" t="inlineStr">
+      <c r="DX10" t="inlineStr">
         <is>
           <t>22.11%</t>
         </is>
       </c>
-      <c r="DX10" t="inlineStr">
+      <c r="DY10" t="inlineStr">
         <is>
           <t>82.0</t>
         </is>
       </c>
-      <c r="DY10" t="inlineStr">
+      <c r="DZ10" t="inlineStr">
         <is>
           <t>1288.0</t>
         </is>
       </c>
-      <c r="DZ10" t="inlineStr">
+      <c r="EA10" t="inlineStr">
         <is>
           <t>3.23</t>
         </is>
       </c>
-      <c r="EA10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EB10" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="EC10" t="inlineStr">
+      <c r="ED10" t="inlineStr">
         <is>
           <t>3.81375</t>
         </is>
       </c>
-      <c r="ED10" t="inlineStr">
+      <c r="EE10" t="inlineStr">
         <is>
           <t>40.245</t>
         </is>
       </c>
-      <c r="EE10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="EF10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EH10" t="inlineStr">
@@ -8034,65 +8079,70 @@
       </c>
       <c r="EK10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
+        <is>
           <t>-0.06000000000000005</t>
         </is>
       </c>
-      <c r="EL10" t="inlineStr">
+      <c r="EM10" t="inlineStr">
         <is>
           <t>-0.01823708206686936</t>
         </is>
       </c>
-      <c r="EM10" t="inlineStr">
+      <c r="EN10" t="inlineStr">
         <is>
           <t>-0.1099999999999994</t>
         </is>
       </c>
-      <c r="EN10" t="inlineStr">
+      <c r="EO10" t="inlineStr">
         <is>
           <t>-0.002522357257509711</t>
         </is>
       </c>
-      <c r="EO10" t="inlineStr">
+      <c r="EP10" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="EP10" t="inlineStr">
+      <c r="EQ10" t="inlineStr">
         <is>
           <t>0.292</t>
         </is>
       </c>
-      <c r="EQ10" t="inlineStr">
+      <c r="ER10" t="inlineStr">
         <is>
           <t>3.130000000000003</t>
         </is>
       </c>
-      <c r="ER10" t="inlineStr">
+      <c r="ES10" t="inlineStr">
         <is>
           <t>0.07753282140203122</t>
         </is>
       </c>
-      <c r="ES10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="ET10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EU10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EV10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EW10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EX10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -8101,7 +8151,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -8121,12 +8171,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>103437.782</t>
+          <t>31963.999</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8136,7 +8186,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8151,12 +8201,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -8181,12 +8231,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>34.66666666666666</t>
+          <t>55.33333333333334</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -8206,7 +8256,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -8231,7 +8281,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -8246,17 +8296,17 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -8266,7 +8316,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>盤整</t>
+          <t>強勢</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -8331,12 +8381,12 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>33359013.0</t>
+          <t>4196252.0</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -8346,17 +8396,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8411,7 +8461,7 @@
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
@@ -8421,359 +8471,359 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>✓確認</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>漲4.3%·上影22%</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>103438</t>
+          <t>262</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>36018</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>80.32</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>97.44</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>26.13</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0.008527994067482503</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.009194970913867673</t>
+          <t>0.01017072284780252</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>0.007325301204819112</t>
+          <t>0.006793977230995285</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>0.005582363515942657</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>2026/09/23</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>1223807078.347646</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>2880485345.0</t>
+          <t>1227718723.982143</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>1390747610.6</t>
+          <t>896876493.0</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>1602753441.5</t>
+          <t>1415429128.8</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>1139038000.966667</t>
+          <t>1367396339.1</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>1252669685.02</t>
+          <t>1194171402.466667</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>39340668.95350628</t>
+          <t>1285813668.38</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>32719331.83628437</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
           <t>2026/08/11</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
-        <is>
-          <t>13.39</t>
-        </is>
-      </c>
       <c r="CP11" t="inlineStr">
         <is>
+          <t>14.40</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
           <t>台泥</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>台泥</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>水泥工業</t>
         </is>
       </c>
-      <c r="CS11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="CT11" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
       <c r="CU11" t="inlineStr">
         <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="CV11" t="inlineStr">
+        <is>
           <t>5.963671135746468</t>
         </is>
       </c>
-      <c r="CV11" t="inlineStr">
+      <c r="CW11" t="inlineStr">
         <is>
           <t>7.626848357921993</t>
         </is>
       </c>
-      <c r="CW11" t="inlineStr">
+      <c r="CX11" t="inlineStr">
         <is>
           <t>3.298870778298021</t>
         </is>
       </c>
-      <c r="CX11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
+          <t>價跌量縮</t>
+        </is>
+      </c>
+      <c r="DA11" t="inlineStr">
+        <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="DA11" t="inlineStr">
+      <c r="DB11" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="DB11" t="inlineStr">
+      <c r="DC11" t="inlineStr">
         <is>
           <t>4.96</t>
         </is>
       </c>
-      <c r="DC11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DD11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DE11" t="inlineStr">
+        <is>
           <t>17.79</t>
         </is>
       </c>
-      <c r="DE11" t="inlineStr">
+      <c r="DF11" t="inlineStr">
         <is>
           <t>6.24</t>
         </is>
       </c>
-      <c r="DF11" t="inlineStr">
-        <is>
-          <t>14.84</t>
-        </is>
-      </c>
       <c r="DG11" t="inlineStr">
         <is>
-          <t>210273</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="DH11" t="inlineStr">
         <is>
+          <t>210649</t>
+        </is>
+      </c>
+      <c r="DI11" t="inlineStr">
+        <is>
           <t>水泥,預拌混擬土80.05%、電力供給及儲能,可充式鋰離16.70%、海陸運輸3.25% (2025年)</t>
         </is>
       </c>
-      <c r="DI11" t="inlineStr">
+      <c r="DJ11" t="inlineStr">
         <is>
           <t>台泥-水泥工業-上市</t>
         </is>
       </c>
-      <c r="DJ11" t="inlineStr">
+      <c r="DK11" t="inlineStr">
         <is>
           <t>水泥工業右上上市</t>
         </is>
       </c>
-      <c r="DK11" t="inlineStr">
-        <is>
-          <t>27.15</t>
-        </is>
-      </c>
       <c r="DL11" t="inlineStr">
         <is>
+          <t>27.85</t>
+        </is>
+      </c>
+      <c r="DM11" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="DN11" t="inlineStr">
+        <is>
+          <t>27.7</t>
+        </is>
+      </c>
+      <c r="DO11" t="inlineStr">
+        <is>
           <t>28.2</t>
         </is>
       </c>
-      <c r="DM11" t="inlineStr">
-        <is>
-          <t>27.05</t>
-        </is>
-      </c>
-      <c r="DN11" t="inlineStr">
-        <is>
-          <t>27.95</t>
-        </is>
-      </c>
-      <c r="DO11" t="inlineStr">
+      <c r="DP11" t="inlineStr">
         <is>
           <t>30.86</t>
         </is>
       </c>
-      <c r="DP11" t="inlineStr">
+      <c r="DQ11" t="inlineStr">
         <is>
           <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
-      <c r="DQ11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="DR11" t="inlineStr">
         <is>
-          <t>1.220984382803484</t>
+          <t>False</t>
         </is>
       </c>
       <c r="DS11" t="inlineStr">
         <is>
+          <t>1.185281380776918</t>
+        </is>
+      </c>
+      <c r="DT11" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="DT11" t="inlineStr">
+      <c r="DU11" t="inlineStr">
         <is>
           <t>38122.0</t>
         </is>
       </c>
-      <c r="DU11" t="inlineStr">
+      <c r="DV11" t="inlineStr">
         <is>
           <t>17.79</t>
         </is>
       </c>
-      <c r="DV11" t="inlineStr">
+      <c r="DW11" t="inlineStr">
         <is>
           <t>2378.0</t>
         </is>
       </c>
-      <c r="DW11" t="inlineStr">
+      <c r="DX11" t="inlineStr">
         <is>
           <t>6.24%</t>
         </is>
       </c>
-      <c r="DX11" t="inlineStr">
+      <c r="DY11" t="inlineStr">
         <is>
           <t>2124.0</t>
         </is>
       </c>
-      <c r="DY11" t="inlineStr">
+      <c r="DZ11" t="inlineStr">
         <is>
           <t>4502.0</t>
         </is>
       </c>
-      <c r="DZ11" t="inlineStr">
+      <c r="EA11" t="inlineStr">
         <is>
           <t>0.29</t>
         </is>
       </c>
-      <c r="EA11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="EB11" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="EC11" t="inlineStr">
+        <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="EC11" t="inlineStr">
+      <c r="ED11" t="inlineStr">
         <is>
           <t>-0.035</t>
         </is>
       </c>
-      <c r="ED11" t="inlineStr">
+      <c r="EE11" t="inlineStr">
         <is>
           <t>19.6475</t>
         </is>
       </c>
-      <c r="EE11" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="EF11" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -8781,7 +8831,7 @@
       </c>
       <c r="EG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EH11" t="inlineStr">
@@ -8791,59 +8841,59 @@
       </c>
       <c r="EI11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EJ11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EK11" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="EL11" t="inlineStr">
+        <is>
           <t>0.19</t>
         </is>
       </c>
-      <c r="EL11" t="inlineStr">
+      <c r="EM11" t="inlineStr">
         <is>
           <t>1.899999999999999</t>
         </is>
       </c>
-      <c r="EM11" t="inlineStr">
+      <c r="EN11" t="inlineStr">
         <is>
           <t>-0.9299999999999997</t>
         </is>
       </c>
-      <c r="EN11" t="inlineStr">
+      <c r="EO11" t="inlineStr">
         <is>
           <t>-0.04967948717948711</t>
         </is>
       </c>
-      <c r="EO11" t="inlineStr">
+      <c r="EP11" t="inlineStr">
         <is>
           <t>0.29</t>
         </is>
       </c>
-      <c r="EP11" t="inlineStr">
+      <c r="EQ11" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="EQ11" t="inlineStr">
+      <c r="ER11" t="inlineStr">
         <is>
           <t>2.67</t>
         </is>
       </c>
-      <c r="ER11" t="inlineStr">
+      <c r="ES11" t="inlineStr">
         <is>
           <t>0.1765873015873016</t>
         </is>
       </c>
-      <c r="ES11" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="ET11" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -8851,15 +8901,20 @@
       </c>
       <c r="EU11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="EV11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EW11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="EX11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>

--- a/Result/checkmy.xlsx
+++ b/Result/checkmy.xlsx
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4687.0</t>
+          <t>6636.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1253,214 +1253,214 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>27.33333333333333</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-05-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>43.8</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>C1 循環・高峰</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>高峰</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>動能轉弱</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>-25136.0</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>-0.54</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>2026-10-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>10.72</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026-05-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>C1 循環・高峰</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>高峰</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>動能轉弱</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>-438943.0</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>-0.37</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>2026-10-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>7.57</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>-2.61</t>
-        </is>
-      </c>
       <c r="BA2" t="inlineStr">
         <is>
           <t>False</t>
@@ -1538,82 +1538,82 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>84.13</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>150.12</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>151.56</t>
+          <t>151.23</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>-0.003856041131105381</t>
+          <t>-0.008387096774193581</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.003581895148160097</t>
+          <t>-0.001622323166774797</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.002341920374707485</t>
+          <t>0.002169559412549926</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>2330.66</t>
+          <t>298.26</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1623,37 +1623,37 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>2092601.48630137</t>
+          <t>2090927.331967213</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>723393.0</t>
+          <t>986574.0</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>1006498.4</t>
+          <t>1034299.4</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>1204498.5</t>
+          <t>1176415.6</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>984966.1666666666</t>
+          <t>1000630.833333333</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>1047645.88</t>
+          <t>1003036.96</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>30813.17231586394</t>
+          <t>23058.26931531857</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-30.70</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
@@ -1713,22 +1713,22 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>33.76</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>180180</t>
+          <t>176715</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
@@ -1778,22 +1778,22 @@
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>1.021860886253792</t>
+          <t>1.03364734080251</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr">
@@ -1975,7 +1975,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1176.927</t>
+          <t>1760.379</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2425.0</t>
+          <t>2385.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2025,17 +2025,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>4.666666666666667</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>140673.0</t>
+          <t>277520.0</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2220,22 +2220,22 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -2310,127 +2310,127 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>33</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>79.36</t>
+          <t>84.71</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>13.86</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>2344.5</t>
+          <t>2338.0</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2217.2</t>
+          <t>2228.8</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.01150895140664954</t>
+          <t>-0.0008428150021070335</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.009415371140792717</t>
+          <t>0.008242950108459768</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>-0.00223428024257899</t>
+          <t>-0.002772446150565155</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>2026/09/22</t>
+          <t>2026/10/30</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>4782455355.410959</t>
+          <t>4786296472.971312</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>2855972570.0</t>
+          <t>4125536255.0</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>3218407511.0</t>
+          <t>3132638406.0</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>3271675647.0</t>
+          <t>3524124015.0</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>3672955981.433333</t>
+          <t>3737165684.933333</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>3687283094.36</t>
+          <t>3726390812.76</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>-63475301.81948109</t>
+          <t>-65405023.48898303</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>32.50</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
@@ -2485,22 +2485,22 @@
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>168640</t>
+          <t>166241</t>
         </is>
       </c>
       <c r="DI3" t="inlineStr">
@@ -2550,22 +2550,22 @@
       </c>
       <c r="DL3" t="inlineStr">
         <is>
-          <t>2490.0</t>
+          <t>2250.0</t>
         </is>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>2490.0</t>
+          <t>2410.0</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>2380.0</t>
+          <t>2225.0</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>2425.0</t>
+          <t>2385.0</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3566.476</t>
+          <t>5240.47</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>227.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>16.66666666666667</t>
+          <t>15.33333333333333</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2907,14 +2907,14 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
           <t>盤整</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>62.5</t>
@@ -2977,12 +2977,12 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>-1923859.0</t>
+          <t>-903365.0</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>129</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -3102,62 +3102,62 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>244.15</t>
+          <t>243.18</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>238.79</t>
+          <t>238.15</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>-0.01682793437105601</t>
+          <t>-0.02866923406076161</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>-0.00781732153877801</t>
+          <t>-0.0165871863985072</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-0.002145703484213723</t>
+          <t>-0.00399344665164858</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>-202.54</t>
+          <t>-960.12</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -3167,37 +3167,37 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3627289414.878082</t>
+          <t>3621984184.192623</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>818668875.0</t>
+          <t>1123716656.0</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>1942561898.2</t>
+          <t>1352730428.0</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>2030416565.4</t>
+          <t>2004738310.4</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>1581456057.866667</t>
+          <t>1599507062.4</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>1304527148.2</t>
+          <t>1304738393.58</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>143115566.5815876</t>
+          <t>103191471.8674866</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-16.47</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
@@ -3262,17 +3262,17 @@
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="DB4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="DC4" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="DE4" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>84.29</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>114334</t>
+          <t>109983</t>
         </is>
       </c>
       <c r="DI4" t="inlineStr">
@@ -3322,22 +3322,22 @@
       </c>
       <c r="DL4" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>236.5</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>226.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>227.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="DS4" t="inlineStr">
         <is>
-          <t>1.228337574437859</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="DT4" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9365.342</t>
+          <t>17739.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>269.5</t>
+          <t>253.5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>17.33333333333333</t>
+          <t>13.33333333333333</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -3664,29 +3664,29 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
           <t>盤整</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>62.5</t>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>-2598628.0</t>
+          <t>-899477.0</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -3764,17 +3764,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -3854,82 +3854,82 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>387</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>54.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>41.19</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>285.23</t>
+          <t>283.18</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>272.47</t>
+          <t>272.6</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.007426661715558946</t>
+          <t>-0.01806118687799496</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>-0.01286931303244521</t>
+          <t>-0.01579140653690791</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-0.007222415593456266</t>
+          <t>-0.007187308265404591</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-14683.88</t>
+          <t>-391.18</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -3939,37 +3939,37 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>9918006059.613699</t>
+          <t>9909339105.409836</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>2533120140.0</t>
+          <t>4497267214.0</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>5702386718.0</t>
+          <t>5346432954.4</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>7390263535.0</t>
+          <t>6160051752.1</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>8296192048.866667</t>
+          <t>8290735596.866667</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>7206485611.72</t>
+          <t>7211088231.08</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>-181941392.9124753</t>
+          <t>-293656514.891171</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-13.04</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
@@ -4029,22 +4029,22 @@
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>36.37</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>356277</t>
+          <t>346006</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
@@ -4089,27 +4089,27 @@
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>半導體業右上上市</t>
+          <t>半導體業平上市</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>276.5</t>
+          <t>258.0</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>276.5</t>
+          <t>259.5</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>268.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>269.5</t>
+          <t>253.5</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18257.916</t>
+          <t>34900.231</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2415.0</t>
+          <t>2370.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>38.66666666666666</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>162942.0</t>
+          <t>-5856145.0</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -4536,17 +4536,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -4626,82 +4626,82 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>2,009</t>
+          <t>1,537</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>21867</t>
+          <t>18404</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>35.64</t>
+          <t>30.88</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>2475.5</t>
+          <t>2470.25</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2441.4</t>
+          <t>2440.9</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.0008309098462817577</t>
+          <t>-0.00415110004151098</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>-0.003087054949578061</t>
+          <t>-0.004954582989265099</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-0.001210409521888223</t>
+          <t>-0.002120783680064631</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>-624.80</t>
+          <t>-250.80</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>-13.96</t>
+          <t>-18.12</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -4711,37 +4711,37 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>93614313192.34932</t>
+          <t>93699189510.09016</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>43964130370.0</t>
+          <t>82766867140.0</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>65054135136.2</t>
+          <t>68574836618.2</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>76334561018.9</t>
+          <t>77597908305.6</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>63791533970.8</t>
+          <t>64860508045.73333</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>57869754288.66</t>
+          <t>58508946936.74</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2362138979.269216</t>
+          <t>2004872180.331103</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
@@ -4801,17 +4801,17 @@
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="DB6" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="DD6" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>27.99</t>
         </is>
       </c>
       <c r="DE6" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>62885997</t>
+          <t>62626674</t>
         </is>
       </c>
       <c r="DI6" t="inlineStr">
@@ -4866,22 +4866,22 @@
       </c>
       <c r="DL6" t="inlineStr">
         <is>
-          <t>2420.0</t>
+          <t>2380.0</t>
         </is>
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>2425.0</t>
+          <t>2380.0</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>2390.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>2415.0</t>
+          <t>2370.0</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="DS6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.057266411941264</t>
         </is>
       </c>
       <c r="DT6" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-10.25</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>350078.013</t>
+          <t>237895.67</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>32.66666666666666</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>盤整</t>
+          <t>弱勢</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>-158489367.0</t>
+          <t>-30186912.0</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -5308,17 +5308,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>54.13</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>2,722</t>
+          <t>13,363</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>90788</t>
+          <t>350078</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -5418,62 +5418,62 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-11.52</t>
+          <t>-12.56</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>140.02</t>
+          <t>137.93</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>136.69</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>-0.01822503961965127</t>
+          <t>-0.02663438256658601</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>-0.01980952380952372</t>
+          <t>-0.02370773416245642</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-0.01356111306798158</t>
+          <t>-0.01499732190680236</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-110.18</t>
+          <t>-91.79</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -5483,37 +5483,37 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19242377844.18493</t>
+          <t>19296441217.42213</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>40961075315.0</t>
+          <t>26019714966.0</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>17815209467.6</t>
+          <t>21118176889.8</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>17705943304.5</t>
+          <t>18738930857.1</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>22561480943.6</t>
+          <t>22866099938.86666</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>22222814634.22</t>
+          <t>22461910484.06</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>-1346099116.809028</t>
+          <t>-1072038632.202973</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>-18.66</t>
+          <t>-21.48</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
@@ -5573,22 +5573,22 @@
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="DB7" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="DC7" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="DD7" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>17.06</t>
         </is>
       </c>
       <c r="DE7" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="DG7" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
-          <t>1608972</t>
+          <t>1451846</t>
         </is>
       </c>
       <c r="DI7" t="inlineStr">
@@ -5638,27 +5638,27 @@
       </c>
       <c r="DL7" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="DM7" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="DQ7" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>80.552</t>
+          <t>374.147</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.6666666666666666</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -5990,19 +5990,19 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>弱勢</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>56.2</t>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-5540.0</t>
+          <t>-48200.0</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -6080,17 +6080,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>14.54</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
@@ -6155,17 +6155,17 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>量起</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>漲0.3%·上影5%</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
@@ -6175,67 +6175,67 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.92</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>-0.002244668911335679</t>
+          <t>-0.001124859392575894</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>-0.001953670108847172</t>
+          <t>-0.001677852348993314</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-0.001114206128133732</t>
+          <t>-0.0006971556051311723</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -6255,37 +6255,37 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>11018164.30684932</t>
+          <t>11014835.2295082</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>1430473.0</t>
+          <t>6533148.0</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>1714107.8</t>
+          <t>2865080.8</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>1681710.0</t>
+          <t>2206050.7</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>2158277.7</t>
+          <t>2278299.433333333</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>2652340.06</t>
+          <t>2758799.08</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>-176583.2125559539</t>
+          <t>-114379.43395753</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="DB8" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="DC8" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="DD8" t="inlineStr">
         <is>
-          <t>63.75</t>
+          <t>63.21</t>
         </is>
       </c>
       <c r="DE8" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>19.89</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="DI8" t="inlineStr">
@@ -6410,22 +6410,22 @@
       </c>
       <c r="DL8" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="DM8" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
@@ -6607,7 +6607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -6757,14 +6757,14 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
           <t>弱勢</t>
@@ -6837,12 +6837,12 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>-2000.0</t>
+          <t>-1000.0</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -6852,17 +6852,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -6947,257 +6947,257 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>22.96</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>-1.110223024625157e-16</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>0.0002209944751381254</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>-0.0008790242830459816</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>2026/10/30</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>1652.266393442623</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>363.0</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>351.2</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>349.4</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>404.0333333333334</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>443.1</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>-14.84935148985541</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>2026/08/10</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>宏佳騰</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>宏佳騰</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>-14.61727178476478</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>32.07138736430949</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>27.88148209128266</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="DC9" t="inlineStr">
+        <is>
+          <t>6.11</t>
+        </is>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>20.97</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>-7.57</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>47.62</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="DI9" t="inlineStr">
+        <is>
+          <t>ATV/ UTV71.35%、摩托車13.07%、電動機車8.10%、零組件及其他7.48% (2025年)</t>
+        </is>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>宏佳騰-電機機械-上櫃</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>電機機械右下上櫃</t>
+        </is>
+      </c>
+      <c r="DL9" t="inlineStr">
+        <is>
           <t>22.75</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>22.97</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>-0.0008857395925597755</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>0.0002210433244915766</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>-0.001097574360662823</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>-3.69</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>2026/10/01</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>1655.301369863014</t>
-        </is>
-      </c>
-      <c r="CH9" t="inlineStr">
-        <is>
-          <t>183.0</t>
-        </is>
-      </c>
-      <c r="CI9" t="inlineStr">
-        <is>
-          <t>332.4</t>
-        </is>
-      </c>
-      <c r="CJ9" t="inlineStr">
-        <is>
-          <t>337.2</t>
-        </is>
-      </c>
-      <c r="CK9" t="inlineStr">
-        <is>
-          <t>436.6</t>
-        </is>
-      </c>
-      <c r="CL9" t="inlineStr">
-        <is>
-          <t>447.5</t>
-        </is>
-      </c>
-      <c r="CM9" t="inlineStr">
-        <is>
-          <t>-13.77528335671957</t>
-        </is>
-      </c>
-      <c r="CN9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CO9" t="inlineStr">
-        <is>
-          <t>2026/08/10</t>
-        </is>
-      </c>
-      <c r="CP9" t="inlineStr">
-        <is>
-          <t>-4.45</t>
-        </is>
-      </c>
-      <c r="CQ9" t="inlineStr">
-        <is>
-          <t>宏佳騰</t>
-        </is>
-      </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>宏佳騰</t>
-        </is>
-      </c>
-      <c r="CS9" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="CU9" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="CV9" t="inlineStr">
-        <is>
-          <t>-14.61727178476478</t>
-        </is>
-      </c>
-      <c r="CW9" t="inlineStr">
-        <is>
-          <t>32.07138736430949</t>
-        </is>
-      </c>
-      <c r="CX9" t="inlineStr">
-        <is>
-          <t>27.88148209128266</t>
-        </is>
-      </c>
-      <c r="CY9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CZ9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="DA9" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="DB9" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="DC9" t="inlineStr">
-        <is>
-          <t>6.11</t>
-        </is>
-      </c>
-      <c r="DD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DE9" t="inlineStr">
-        <is>
-          <t>20.97</t>
-        </is>
-      </c>
-      <c r="DF9" t="inlineStr">
-        <is>
-          <t>-7.57</t>
-        </is>
-      </c>
-      <c r="DG9" t="inlineStr">
-        <is>
-          <t>48.47</t>
-        </is>
-      </c>
-      <c r="DH9" t="inlineStr">
-        <is>
-          <t>1647</t>
-        </is>
-      </c>
-      <c r="DI9" t="inlineStr">
-        <is>
-          <t>ATV/ UTV71.35%、摩托車13.07%、電動機車8.10%、零組件及其他7.48% (2025年)</t>
-        </is>
-      </c>
-      <c r="DJ9" t="inlineStr">
-        <is>
-          <t>宏佳騰-電機機械-上櫃</t>
-        </is>
-      </c>
-      <c r="DK9" t="inlineStr">
-        <is>
-          <t>電機機械右下上櫃</t>
-        </is>
-      </c>
-      <c r="DL9" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
       <c r="DM9" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1749.174</t>
+          <t>2103.688</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>551.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-655824.0</t>
+          <t>59241.0</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -7624,17 +7624,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>223</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -7734,62 +7734,62 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>659.0</t>
+          <t>652.15</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>697.0</t>
+          <t>693.82</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-0.02230239422761549</t>
+          <t>-0.02515934250251595</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>-0.01574555188159343</t>
+          <t>-0.02223644216925291</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>-0.01021327726043852</t>
+          <t>-0.0103945371775418</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-47.46</t>
+          <t>-45.35</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>-31.96</t>
+          <t>-35.54</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>-21.68</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -7799,37 +7799,37 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>4196030804.272603</t>
+          <t>4189289854.569673</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>1000492278.0</t>
+          <t>1152562142.0</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>895177741.0</t>
+          <t>991615422.8</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>1049009592.9</t>
+          <t>971856966.3</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>1015050980.0</t>
+          <t>1033054267.8</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>1217418960.6</t>
+          <t>1220350002.84</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>580179.7072205395</t>
+          <t>-6222796.321741502</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>-22.02</t>
+          <t>-23.68</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
@@ -7889,22 +7889,22 @@
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>19.32</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="DB10" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="DC10" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="DD10" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="DE10" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="DG10" t="inlineStr">
         <is>
-          <t>33.83</t>
+          <t>33.29</t>
         </is>
       </c>
       <c r="DH10" t="inlineStr">
         <is>
-          <t>205701</t>
+          <t>195624</t>
         </is>
       </c>
       <c r="DI10" t="inlineStr">
@@ -7954,22 +7954,22 @@
       </c>
       <c r="DL10" t="inlineStr">
         <is>
-          <t>588.0</t>
+          <t>554.0</t>
         </is>
       </c>
       <c r="DM10" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>558.0</t>
         </is>
       </c>
       <c r="DN10" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>537.0</t>
         </is>
       </c>
       <c r="DO10" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>551.0</t>
         </is>
       </c>
       <c r="DP10" t="inlineStr">
@@ -8171,12 +8171,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31963.999</t>
+          <t>41966.086</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8201,12 +8201,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>55.33333333333334</t>
+          <t>61.33333333333334</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -8256,427 +8256,427 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>43.8</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>C2 循環・中段</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>中段</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>毛利率連2季低於8季均</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>9551046.0</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>2026-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>NA｜水泥｜水泥製造｜台灣水泥龍頭，跨足綠能</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>24.85</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>C2 循環・中段</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>中段</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>毛利率連2季低於8季均</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>4196252.0</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>2026-10-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>5.74</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>✓確認</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>漲4.3%·上影22%</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>31964</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>97.44</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>5.23</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>26.72</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>0.01114706939949639</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>0.004741929600583505</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>0.005739555890101666</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>18.48</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>2026/09/23</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>1229206982.338356</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>1180622016.0</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>1491589505.0</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>1266264181.1</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>1221587051.333333</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>1300116243.9</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>23960677.25220713</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
+        <is>
+          <t>15.01</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
+          <t>水泥工業</t>
+        </is>
+      </c>
+      <c r="CT11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="CU11" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="CV11" t="inlineStr">
+        <is>
+          <t>5.963671135746468</t>
+        </is>
+      </c>
+      <c r="CW11" t="inlineStr">
+        <is>
+          <t>7.626848357921993</t>
+        </is>
+      </c>
+      <c r="CX11" t="inlineStr">
+        <is>
+          <t>3.298870778298021</t>
+        </is>
+      </c>
+      <c r="CY11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CZ11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="DA11" t="inlineStr">
         <is>
           <t>0.92</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>NA｜水泥｜水泥製造｜台灣水泥龍頭，跨足綠能</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>27.05</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>24.85</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>✓確認</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>漲4.3%·上影22%</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>36018</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>97.44</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>4.67</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>4.94</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>26.57</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>25.32</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>0.01017072284780252</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>0.006793977230995285</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>0.005582363515942657</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>20.31</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>2026/09/23</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>1227718723.982143</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
-        <is>
-          <t>896876493.0</t>
-        </is>
-      </c>
-      <c r="CI11" t="inlineStr">
-        <is>
-          <t>1415429128.8</t>
-        </is>
-      </c>
-      <c r="CJ11" t="inlineStr">
-        <is>
-          <t>1367396339.1</t>
-        </is>
-      </c>
-      <c r="CK11" t="inlineStr">
-        <is>
-          <t>1194171402.466667</t>
-        </is>
-      </c>
-      <c r="CL11" t="inlineStr">
-        <is>
-          <t>1285813668.38</t>
-        </is>
-      </c>
-      <c r="CM11" t="inlineStr">
-        <is>
-          <t>32719331.83628437</t>
-        </is>
-      </c>
-      <c r="CN11" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="CO11" t="inlineStr">
-        <is>
-          <t>2026/08/11</t>
-        </is>
-      </c>
-      <c r="CP11" t="inlineStr">
-        <is>
-          <t>14.40</t>
-        </is>
-      </c>
-      <c r="CQ11" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="CS11" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="CT11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="CU11" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="CV11" t="inlineStr">
-        <is>
-          <t>5.963671135746468</t>
-        </is>
-      </c>
-      <c r="CW11" t="inlineStr">
-        <is>
-          <t>7.626848357921993</t>
-        </is>
-      </c>
-      <c r="CX11" t="inlineStr">
-        <is>
-          <t>3.298870778298021</t>
-        </is>
-      </c>
-      <c r="CY11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CZ11" t="inlineStr">
-        <is>
-          <t>價跌量縮</t>
-        </is>
-      </c>
-      <c r="DA11" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
       <c r="DB11" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="DC11" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="DG11" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="DH11" t="inlineStr">
         <is>
-          <t>210649</t>
+          <t>212154</t>
         </is>
       </c>
       <c r="DI11" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="DL11" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="DM11" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="DN11" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="DO11" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="DP11" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="DS11" t="inlineStr">
         <is>
-          <t>1.185281380776918</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="DT11" t="inlineStr">
